--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_前提条件" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'01_見積書'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01_見積書'!$A$1:$F$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'04_教材科目'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05_月額・別途費用'!$A$1:$D$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0&quot;人日&quot;;&quot;▲&quot;#,##0.0&quot;人日&quot;;-"/>
     <numFmt numFmtId="168" formatCode="&quot;¥&quot;#,##0&quot;  （税抜）&quot;"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -238,11 +238,6 @@
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001E6B4A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="001A2430"/>
       <sz val="13"/>
@@ -415,7 +410,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -436,7 +431,7 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -540,10 +535,13 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -615,25 +613,22 @@
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -648,7 +643,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1031,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F40"/>
+  <dimension ref="B2:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1058,7 +1053,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>SP-2026-0002</t>
+          <t>SP-2026-0003</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1065,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026年9月12日</t>
+          <t>2026年9月13日</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1187,7 @@
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="B21" s="9" t="inlineStr">
         <is>
           <t>納入場所</t>
@@ -1200,14 +1195,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>貴社ご指定のAWS環境</t>
+          <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="12" t="n"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="B22" s="9" t="inlineStr">
         <is>
           <t>検収条件</t>
@@ -1222,7 +1217,7 @@
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="12" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="B23" s="9" t="inlineStr">
         <is>
           <t>支払条件</t>
@@ -1230,237 +1225,213 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>ご発注時に全額を一括でお支払いください。本お見積りは当該条件を前提とした金額です。</t>
+          <t>ご発注時に全額を一括でお支払いください。</t>
         </is>
       </c>
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="12" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>月額費用・AWS利用料・ゼウス利用料・教材の改訂費は含みません（シート05）。前回お見積りからの増減はシート02をご参照ください。</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>内訳</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="18" t="inlineStr"/>
-      <c r="B27" s="18" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>金額（税抜）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>システム開発</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
+        </is>
+      </c>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>金額（税抜）</t>
-        </is>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>一式</t>
+        </is>
+      </c>
+      <c r="F27" s="22">
+        <f>'03_見積明細'!F21</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>システム開発</t>
+          <t>教材制作</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
+          <t>特別教育 学科教材 6科目</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
-      <c r="E28" s="21">
-        <f>'03_見積明細'!D21</f>
+      <c r="E28" s="23">
+        <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
       <c r="F28" s="22">
-        <f>'03_見積明細'!F21</f>
+        <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>教材制作</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>特別教育 学科教材 6科目</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="23">
-        <f>'04_教材科目'!$A$17</f>
-        <v/>
-      </c>
-      <c r="F29" s="22">
-        <f>'04_教材科目'!$F$17</f>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>（税抜）</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr"/>
+      <c r="E29" s="26" t="inlineStr"/>
+      <c r="F29" s="27">
+        <f>'03_見積明細'!F26</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>（税抜）</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr"/>
-      <c r="E30" s="26" t="inlineStr"/>
-      <c r="F30" s="27">
-        <f>'03_見積明細'!F26</f>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>値引</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>貴社特別値引き</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr"/>
+      <c r="E30" s="29" t="inlineStr"/>
+      <c r="F30" s="30">
+        <f>'03_見積明細'!F27</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>調整</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>全額一括前払いによる調整</t>
+          <t>差引小計</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>（税抜）</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr"/>
       <c r="E31" s="29" t="inlineStr"/>
-      <c r="F31" s="30">
-        <f>'03_見積明細'!F27</f>
+      <c r="F31" s="32">
+        <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>差引小計</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>（税抜）</t>
-        </is>
-      </c>
+          <t>消費税</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr"/>
       <c r="D32" s="29" t="inlineStr"/>
       <c r="E32" s="29" t="inlineStr"/>
       <c r="F32" s="32">
-        <f>'03_見積明細'!F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>消費税</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr"/>
-      <c r="D33" s="29" t="inlineStr"/>
-      <c r="E33" s="29" t="inlineStr"/>
-      <c r="F33" s="32">
         <f>'03_見積明細'!F29</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>（税込）</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr"/>
-      <c r="E34" s="14" t="inlineStr"/>
-      <c r="F34" s="35">
+      <c r="D33" s="14" t="inlineStr"/>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="35">
         <f>'03_見積明細'!F30</f>
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="37" t="inlineStr">
         <is>
-          <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
+          <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>・AWS 利用料　月額 22,800円程度（推奨構成・受講者数により変動）。聖建様名義でのご契約を推奨します</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="37" t="inlineStr">
-        <is>
-          <t>・株式会社ゼウス　月額 3,000円 ＋ 決済手数料 最大3.5%。聖建様が直接ご契約いただきます</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="37" t="inlineStr">
-        <is>
           <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="22">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="C29:D29"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="C24:F24"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="C20:F20"/>
@@ -1468,10 +1439,10 @@
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="B40:F40"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -1485,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1803,95 +1774,126 @@
     <row r="26">
       <c r="B26" s="64" t="inlineStr">
         <is>
-          <t>■ この表の使い方</t>
+          <t>■ このシートは社内資料です（先方には提出しません）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="65" t="inlineStr">
         <is>
-          <t>単純な値引きではなく、次の3つの対価として金額が下がっていることをご説明いただけます。</t>
+          <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">　① 納品する教材が4科目減ること（成果物の減少）</t>
+          <t>先方向けには「前回からの変更は受講中のランダム顔照合を外すことだけ」と説明し、</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">　② 受講中のランダム照合を実装しないこと（機能の減少）</t>
+          <t>下の④は見積書・注文書の上では「貴社特別値引き（特別値引き）」と表示しています。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　③ 全額を前払いいただくこと（支払条件の対価）</t>
-        </is>
-      </c>
+      <c r="B30" s="65" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="65" t="inlineStr"/>
+      <c r="B31" s="66" t="inlineStr">
+        <is>
+          <t>■ この表の使い方（社内の根拠整理）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="65" t="inlineStr">
         <is>
-          <t>一方で、決済機能（ゼウス連携）は新しいご要望のため増額しています。</t>
+          <t>単純な値引きではなく、次の3つの対価として金額が下がっていることを社内で説明できます。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="66" t="inlineStr">
-        <is>
-          <t>減る理由と増える理由の両方を示すことで、価格の根拠が明確になります。</t>
+      <c r="B33" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 納品する教材が4科目減ること（成果物の減少）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="65" t="inlineStr"/>
+      <c r="B34" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 受講中のランダム照合を実装しないこと（機能の減少）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="64" t="inlineStr">
-        <is>
-          <t>■ 月額費用の変更</t>
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 全額を前払いいただくこと（支払条件の対価）</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="65" t="inlineStr">
-        <is>
-          <t>保守・運用サービス　80,000円 → 60,000円（▲20,000円）</t>
-        </is>
-      </c>
+      <c r="B36" s="65" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="65" t="inlineStr">
         <is>
+          <t>一方で、決済機能（ゼウス連携）は新しいご要望のため増額しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>減る理由と増える理由の両方を示すことで、価格の根拠が明確になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="65" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="66" t="inlineStr">
+        <is>
+          <t>■ 月額費用の変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="65" t="inlineStr">
+        <is>
+          <t>保守・運用サービス　80,000円 → 60,000円（▲20,000円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="65" t="inlineStr">
+        <is>
           <t xml:space="preserve">　受講中のランダム照合を実装しないため、照合結果の目視確認という運用作業がなくなります。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="66" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">　運用工数が実際に減るため、その分を月額に反映しています。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="65" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="65" t="inlineStr">
         <is>
           <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="65" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　　　　　　合計 80,000円／月（サーバー費を除く・税抜）</t>
         </is>
@@ -1936,13 +1938,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>人日単価</t>
         </is>
       </c>
       <c r="B4" s="12" t="n"/>
-      <c r="C4" s="68" t="n">
+      <c r="C4" s="69" t="n">
         <v>50000</v>
       </c>
       <c r="D4" s="31" t="inlineStr">
@@ -1984,7 +1986,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="69" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>1. システム開発</t>
         </is>
@@ -1996,7 +1998,7 @@
       <c r="F7" s="12" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2011,7 +2013,7 @@
           <t>業務フローの確定、データモデル設計、API設計、画面設計、利用規約・特定商取引法表記・個人情報の取扱い方針の整備支援</t>
         </is>
       </c>
-      <c r="D8" s="71" t="n">
+      <c r="D8" s="72" t="n">
         <v>8</v>
       </c>
       <c r="E8" s="22">
@@ -2024,7 +2026,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2039,7 +2041,7 @@
           <t>VPC、EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch の構築とCI/CD</t>
         </is>
       </c>
-      <c r="D9" s="71" t="n">
+      <c r="D9" s="72" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="22">
@@ -2052,7 +2054,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="70" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2067,7 +2069,7 @@
           <t>HLS変換（FFmpeg）、短寿命の署名付きマニフェスト配信、章単位の受講制御、MP4直リンクの排除</t>
         </is>
       </c>
-      <c r="D10" s="71" t="n">
+      <c r="D10" s="72" t="n">
         <v>12</v>
       </c>
       <c r="E10" s="22">
@@ -2080,7 +2082,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2095,7 +2097,7 @@
           <t>heartbeatの受信と検証、未視聴位置へのシーク制限、倍速検知、可視状態の判定、サーバー側での検証済み秒数の集計、異常検知</t>
         </is>
       </c>
-      <c r="D11" s="71" t="n">
+      <c r="D11" s="72" t="n">
         <v>15</v>
       </c>
       <c r="E11" s="22">
@@ -2108,7 +2110,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2123,7 +2125,7 @@
           <t>その場撮影UI（getUserMedia）、ライブネス判定、本人確認書類との突合、顔の1:1照合、運営の審査画面</t>
         </is>
       </c>
-      <c r="D12" s="71" t="n">
+      <c r="D12" s="72" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="22">
@@ -2136,7 +2138,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2151,7 +2153,7 @@
           <t>QRコードとワンタイムURLによる撮影工程の引き継ぎ</t>
         </is>
       </c>
-      <c r="D13" s="71" t="n">
+      <c r="D13" s="72" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="22">
@@ -2164,7 +2166,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="70" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2179,7 +2181,7 @@
           <t>各章の再生開始時に1:1照合を実施。受講中のランダム照合は今回の範囲外とします</t>
         </is>
       </c>
-      <c r="D14" s="71" t="n">
+      <c r="D14" s="72" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="22">
@@ -2192,7 +2194,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="70" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2207,7 +2209,7 @@
           <t>章末問題、修了確認テスト、出題のランダム化、不合格後の再受講制御</t>
         </is>
       </c>
-      <c r="D15" s="71" t="n">
+      <c r="D15" s="72" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="22">
@@ -2220,7 +2222,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="70" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2235,7 +2237,7 @@
           <t>サーバー側での修了条件の再検証、修了記録の作成、修了証PDFの発行・再発行・ダウンロード</t>
         </is>
       </c>
-      <c r="D16" s="71" t="n">
+      <c r="D16" s="72" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="22">
@@ -2248,7 +2250,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="70" t="inlineStr">
+      <c r="A17" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2263,7 +2265,7 @@
           <t>株式会社ゼウスのデータ転送（API）型による決済組み込み。申込から入金確認、受講開始までの自動化。領収書の発行</t>
         </is>
       </c>
-      <c r="D17" s="71" t="n">
+      <c r="D17" s="72" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="22">
@@ -2276,7 +2278,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="70" t="inlineStr">
+      <c r="A18" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2291,7 +2293,7 @@
           <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応</t>
         </is>
       </c>
-      <c r="D18" s="71" t="n">
+      <c r="D18" s="72" t="n">
         <v>9</v>
       </c>
       <c r="E18" s="22">
@@ -2304,7 +2306,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="70" t="inlineStr">
+      <c r="A19" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2319,7 +2321,7 @@
           <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理</t>
         </is>
       </c>
-      <c r="D19" s="71" t="n">
+      <c r="D19" s="72" t="n">
         <v>4</v>
       </c>
       <c r="E19" s="22">
@@ -2332,7 +2334,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="70" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
@@ -2347,7 +2349,7 @@
           <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成</t>
         </is>
       </c>
-      <c r="D20" s="71" t="n">
+      <c r="D20" s="72" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="22">
@@ -2367,7 +2369,7 @@
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr"/>
-      <c r="D21" s="72">
+      <c r="D21" s="73">
         <f>SUM(D8:D20)</f>
         <v/>
       </c>
@@ -2378,7 +2380,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="69" t="inlineStr">
+      <c r="A23" s="70" t="inlineStr">
         <is>
           <t>2. eラーニング教材の制作</t>
         </is>
@@ -2390,7 +2392,7 @@
       <c r="F23" s="12" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="70" t="inlineStr">
+      <c r="A24" s="71" t="inlineStr">
         <is>
           <t>教材</t>
         </is>
@@ -2404,11 +2406,11 @@
         <f>"6科目・学科"&amp;TEXT('04_教材科目'!$D$17,"0.0")&amp;"時間分。構成台本の書き起こし、スライド、図解、ナレーション、バーチャル講師映像、章末問題・修了確認テストの作成"</f>
         <v/>
       </c>
-      <c r="D24" s="73">
+      <c r="D24" s="74">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="E24" s="74">
+      <c r="E24" s="75">
         <f>'04_教材科目'!$D$4</f>
         <v/>
       </c>
@@ -2436,7 +2438,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="75" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
         </is>
@@ -2448,12 +2450,12 @@
       </c>
       <c r="D27" s="29" t="inlineStr"/>
       <c r="E27" s="29" t="inlineStr"/>
-      <c r="F27" s="68" t="n">
+      <c r="F27" s="69" t="n">
         <v>-350000</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="76" t="inlineStr">
+      <c r="B28" s="77" t="inlineStr">
         <is>
           <t>差引 小計（税抜）</t>
         </is>
@@ -2467,7 +2469,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="76" t="inlineStr">
+      <c r="B29" s="77" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
@@ -2477,7 +2479,7 @@
           <t>税率</t>
         </is>
       </c>
-      <c r="D29" s="77" t="n">
+      <c r="D29" s="78" t="n">
         <v>0.1</v>
       </c>
       <c r="E29" s="29" t="inlineStr"/>
@@ -2502,7 +2504,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t>■ 今回の範囲から外したもの（第2次発注のご相談）</t>
         </is>
@@ -2554,7 +2556,7 @@
       <c r="A39" s="65" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="64" t="inlineStr">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>■ 本見積に含まれないもの（別途）</t>
         </is>
@@ -2626,13 +2628,13 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr"/>
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
         <is>
           <t>制作単価（1科目あたり）</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr"/>
-      <c r="D4" s="68" t="n">
+      <c r="D4" s="69" t="n">
         <v>300000</v>
       </c>
       <c r="E4" s="31" t="inlineStr">
@@ -2678,10 +2680,10 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="78" t="n">
+      <c r="A7" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="79" t="n">
+      <c r="B7" s="80" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="43" t="inlineStr">
@@ -2689,7 +2691,7 @@
           <t>フルハーネス型墜落制止用器具</t>
         </is>
       </c>
-      <c r="D7" s="80" t="n">
+      <c r="D7" s="81" t="n">
         <v>4.5</v>
       </c>
       <c r="E7" s="46" t="inlineStr">
@@ -2703,10 +2705,10 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="78" t="n">
+      <c r="A8" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="79" t="n">
+      <c r="B8" s="80" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="43" t="inlineStr">
@@ -2714,7 +2716,7 @@
           <t>足場の組立て・解体・変更</t>
         </is>
       </c>
-      <c r="D8" s="80" t="n">
+      <c r="D8" s="81" t="n">
         <v>6</v>
       </c>
       <c r="E8" s="46" t="inlineStr">
@@ -2728,10 +2730,10 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="78" t="n">
+      <c r="A9" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="79" t="n">
+      <c r="B9" s="80" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="43" t="inlineStr">
@@ -2739,7 +2741,7 @@
           <t>自由研削用といし</t>
         </is>
       </c>
-      <c r="D9" s="80" t="n">
+      <c r="D9" s="81" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="46" t="inlineStr">
@@ -2753,18 +2755,18 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="78" t="n">
+      <c r="A10" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="79" t="n">
+      <c r="B10" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="81" t="inlineStr">
+      <c r="C10" s="82" t="inlineStr">
         <is>
           <t>低圧電気取扱業務</t>
         </is>
       </c>
-      <c r="D10" s="82" t="n">
+      <c r="D10" s="83" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="46" t="inlineStr">
@@ -2778,10 +2780,10 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="78" t="n">
+      <c r="A11" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="79" t="n">
+      <c r="B11" s="80" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="43" t="inlineStr">
@@ -2789,7 +2791,7 @@
           <t>アーク溶接等</t>
         </is>
       </c>
-      <c r="D11" s="80" t="n">
+      <c r="D11" s="81" t="n">
         <v>11</v>
       </c>
       <c r="E11" s="46" t="inlineStr">
@@ -2803,10 +2805,10 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="78" t="n">
+      <c r="A12" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="79" t="n">
+      <c r="B12" s="80" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="43" t="inlineStr">
@@ -2814,7 +2816,7 @@
           <t>石綿使用建築物等の解体・破砕等</t>
         </is>
       </c>
-      <c r="D12" s="80" t="n">
+      <c r="D12" s="81" t="n">
         <v>4.5</v>
       </c>
       <c r="E12" s="46" t="inlineStr">
@@ -2828,10 +2830,10 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="78" t="n">
+      <c r="A13" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="79" t="n">
+      <c r="B13" s="80" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="43" t="inlineStr">
@@ -2839,7 +2841,7 @@
           <t>特定粉じん作業</t>
         </is>
       </c>
-      <c r="D13" s="80" t="n">
+      <c r="D13" s="81" t="n">
         <v>4.5</v>
       </c>
       <c r="E13" s="46" t="inlineStr">
@@ -2853,18 +2855,18 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="78" t="n">
+      <c r="A14" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="B14" s="79" t="n">
+      <c r="B14" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="81" t="inlineStr">
+      <c r="C14" s="82" t="inlineStr">
         <is>
           <t>第2種酸素欠乏危険作業</t>
         </is>
       </c>
-      <c r="D14" s="82" t="n">
+      <c r="D14" s="83" t="n">
         <v>5.5</v>
       </c>
       <c r="E14" s="46" t="inlineStr">
@@ -2878,18 +2880,18 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="78" t="n">
+      <c r="A15" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="B15" s="79" t="n">
+      <c r="B15" s="80" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="81" t="inlineStr">
+      <c r="C15" s="82" t="inlineStr">
         <is>
           <t>高所作業車（10m未満）</t>
         </is>
       </c>
-      <c r="D15" s="82" t="n">
+      <c r="D15" s="83" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="46" t="inlineStr">
@@ -2903,18 +2905,18 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="78" t="n">
+      <c r="A16" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="B16" s="79" t="n">
+      <c r="B16" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="81" t="inlineStr">
+      <c r="C16" s="82" t="inlineStr">
         <is>
           <t>玉掛け（1t未満）</t>
         </is>
       </c>
-      <c r="D16" s="82" t="n">
+      <c r="D16" s="83" t="n">
         <v>5</v>
       </c>
       <c r="E16" s="46" t="inlineStr">
@@ -2928,28 +2930,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="83">
+      <c r="A17" s="84">
         <f>SUM(A7:A16)</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="68" t="inlineStr">
         <is>
           <t>制作対象 合計</t>
         </is>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="85">
         <f>SUMPRODUCT($A7:$A16,$D7:$D16)</f>
         <v/>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="85">
+      <c r="F17" s="86">
         <f>SUM(F7:F16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>■ 選定の考え方</t>
         </is>
@@ -3043,18 +3045,18 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t>弊社へ
 お支払い</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>保守・運用サービス</t>
         </is>
       </c>
-      <c r="C5" s="68" t="n">
+      <c r="C5" s="69" t="n">
         <v>60000</v>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -3065,12 +3067,12 @@
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="26" t="inlineStr"/>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>法令改正監視・通知サービス</t>
         </is>
       </c>
-      <c r="C6" s="68" t="n">
+      <c r="C6" s="69" t="n">
         <v>20000</v>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -3097,18 +3099,18 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t>お客様
 ご負担</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>AWS 利用料（構成B・推奨）</t>
         </is>
       </c>
-      <c r="C9" s="68" t="n">
+      <c r="C9" s="69" t="n">
         <v>22800</v>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -3119,12 +3121,12 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="26" t="inlineStr"/>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>従量課金（顔照合・配信ほか）</t>
         </is>
       </c>
-      <c r="C10" s="87" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>実費</t>
         </is>
@@ -3137,12 +3139,12 @@
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="26" t="inlineStr"/>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>株式会社ゼウス（決済代行）</t>
         </is>
       </c>
-      <c r="C11" s="68" t="n">
+      <c r="C11" s="69" t="n">
         <v>3000</v>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -3152,13 +3154,13 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="86" t="inlineStr">
+      <c r="A13" s="87" t="inlineStr">
         <is>
           <t>都度
 発注</t>
         </is>
       </c>
-      <c r="B13" s="76" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>教材の改訂（法令改正対応）</t>
         </is>
@@ -3175,7 +3177,7 @@
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="26" t="inlineStr"/>
-      <c r="B14" s="76" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>教材の追加制作（第2次）</t>
         </is>
@@ -3198,12 +3200,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="76" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>弊社サービス ＋ AWS ＋ ゼウス月額</t>
         </is>
       </c>
-      <c r="C17" s="88">
+      <c r="C17" s="89">
         <f>'05_月額・別途費用'!C7+C9+C11</f>
         <v/>
       </c>
@@ -3214,7 +3216,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>■ 月額80,000円の根拠</t>
         </is>
@@ -3235,7 +3237,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="66" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">　　目視確認という運用作業がなくなります。その分を減額しています。</t>
         </is>
@@ -3252,7 +3254,7 @@
       <c r="A24" s="65" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>■ ゼウスについて</t>
         </is>
@@ -3280,7 +3282,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="89" t="inlineStr">
+      <c r="A29" s="64" t="inlineStr">
         <is>
           <t>・最新の料金と条件は、ご契約前にゼウス社へ直接ご確認ください。</t>
         </is>
@@ -3299,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F30"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3434,7 +3436,6 @@
       <c r="F16" s="12" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="18" t="inlineStr"/>
       <c r="B18" s="18" t="inlineStr">
         <is>
           <t>区分</t>
@@ -3468,9 +3469,10 @@
           <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
         </is>
       </c>
-      <c r="D19" s="21">
-        <f>'03_見積明細'!D21</f>
-        <v/>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>一式</t>
+        </is>
       </c>
       <c r="E19" s="29" t="inlineStr"/>
       <c r="F19" s="22">
@@ -3514,9 +3516,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="75" t="inlineStr">
-        <is>
-          <t>全額一括前払いによる調整</t>
+      <c r="B22" s="76" t="inlineStr">
+        <is>
+          <t>特別値引き</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr"/>
@@ -3528,7 +3530,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="76" t="inlineStr">
+      <c r="B23" s="77" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
@@ -3558,7 +3560,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="44" customHeight="1">
+    <row r="26" ht="42" customHeight="1">
       <c r="B26" s="9" t="inlineStr">
         <is>
           <t>納期</t>
@@ -3581,7 +3583,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>貴社ご指定のAWS環境</t>
+          <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
       <c r="D27" s="11" t="n"/>
@@ -3618,23 +3620,8 @@
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="12" t="n"/>
     </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>別途契約</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>月額の保守・運用サービスおよび法令改正監視・通知サービス（合計80,000円／月・税抜）は別途契約とします。AWS利用料および株式会社ゼウスとの契約は発注者が直接行うものとします。</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="12" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="B8:D8"/>
@@ -3643,7 +3630,6 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C30:F30"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C27:F27"/>
@@ -3664,7 +3650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C32"/>
+  <dimension ref="B1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3695,7 +3681,7 @@
       </c>
       <c r="C4" s="99" t="inlineStr">
         <is>
-          <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、確認問題、修了判定、修了証の発行、決済（ゼウス連携）、受講者ポータル、運営管理画面の基本機能。</t>
+          <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、確認問題、修了判定、修了証の発行、決済機能、受講者ポータル、運営管理画面の基本機能。</t>
         </is>
       </c>
     </row>
@@ -3723,27 +3709,27 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="98" t="inlineStr">
         <is>
-          <t>AWS環境の構築</t>
+          <t>サーバー環境の構築</t>
         </is>
       </c>
       <c r="C7" s="99" t="inlineStr">
         <is>
-          <t>本番運用に耐える構成で構築します。RDS PostgreSQL は Multi-AZ とし、自動バックアップとPITRを有効にします。</t>
+          <t>本番運用に耐える構成で構築します。データベースは冗長化し、日次のバックアップを取得します。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="B9" s="100" t="inlineStr">
         <is>
-          <t>■ 2. 今回の範囲から外したもの</t>
+          <t>■ 2. 本見積に含まれないもの（別途）</t>
         </is>
       </c>
       <c r="C9" s="97" t="inlineStr"/>
     </row>
-    <row r="10" ht="44" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="B10" s="98" t="inlineStr">
         <is>
           <t>受講中のランダム顔照合</t>
@@ -3751,221 +3737,141 @@
       </c>
       <c r="C10" s="99" t="inlineStr">
         <is>
-          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能。登録時の本人確認と受講開始時の照合は実装するため、替え玉への防御がゼロになるわけではありません。将来の追加実装を想定した設計としておきます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。登録時の本人確認と受講開始時の顔照合は実装します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
       <c r="B11" s="98" t="inlineStr">
         <is>
-          <t>教材 4科目</t>
+          <t>月額サービス</t>
         </is>
       </c>
       <c r="C11" s="99" t="inlineStr">
         <is>
-          <t>低圧電気取扱業務、第2種酸素欠乏危険作業、高所作業車、玉掛け。第2次発注でのご検討をお願いします。</t>
+          <t>保守・運用サービス 60,000円／月、法令改正監視・通知サービス 20,000円／月。合計80,000円／月（税抜）。別途契約とします。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="98" t="inlineStr">
         <is>
-          <t>企業管理ポータル</t>
+          <t>サーバー利用料</t>
         </is>
       </c>
       <c r="C12" s="99" t="inlineStr">
         <is>
-          <t>従業員の一括申込、進捗確認、修了者一覧のCSV出力。</t>
+          <t>貴社のご負担とします。月額20,000円程度（税抜）。貴社名義でのご契約を推奨します。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="98" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>教材の改訂・追加</t>
         </is>
       </c>
       <c r="C13" s="99" t="inlineStr">
         <is>
-          <t>運営管理画面の拡張、質疑応答機能、修了証の真正性検証ページ（QRコード）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="100" t="inlineStr">
-        <is>
-          <t>■ 3. 本見積に含まれないもの（別途）</t>
-        </is>
-      </c>
-      <c r="C15" s="97" t="inlineStr"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="B16" s="98" t="inlineStr">
-        <is>
-          <t>月額サービス</t>
-        </is>
-      </c>
-      <c r="C16" s="99" t="inlineStr">
-        <is>
-          <t>保守・運用サービス 60,000円／月、法令改正監視・通知サービス 20,000円／月。合計80,000円／月（税抜）。別途契約とします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+          <t>1科目300,000円（都度発注）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="98" t="inlineStr">
+        <is>
+          <t>教材の監修</t>
+        </is>
+      </c>
+      <c r="C14" s="99" t="inlineStr">
+        <is>
+          <t>内容の監修は貴社の社内有資格者が担われる前提です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="96" t="inlineStr">
+        <is>
+          <t>■ 3. 責任の分担</t>
+        </is>
+      </c>
+      <c r="C16" s="97" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
       <c r="B17" s="98" t="inlineStr">
         <is>
-          <t>AWS 利用料</t>
+          <t>弊社が保証すること</t>
         </is>
       </c>
       <c r="C17" s="99" t="inlineStr">
         <is>
-          <t>聖建様のご負担とします。推奨構成で月額22,800円程度（税抜）。聖建様名義でのご契約を推奨します。</t>
+          <t>教材が安全衛生特別教育規程の定める科目・範囲・時間を満たすこと（監修者名を明示）。受講記録を証明可能な形で保存・出力できること。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="B18" s="98" t="inlineStr">
         <is>
-          <t>ゼウス利用料</t>
+          <t>弊社が保証しないこと</t>
         </is>
       </c>
       <c r="C18" s="99" t="inlineStr">
         <is>
-          <t>初期費用無料、月額3,000円、決済手数料 最大3.5%。聖建様が直接ご契約いただきます。最新の条件はゼウス社へご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
+          <t>受講者の所属事業者が負う労働安全衛生法第59条第3項の実施義務が果たされたこと。労働災害が発生しないこと。行政機関が個別の事案において本教材を適法と判断すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
       <c r="B19" s="98" t="inlineStr">
         <is>
-          <t>教材の改訂・追加</t>
+          <t>法令改正への対応</t>
         </is>
       </c>
       <c r="C19" s="99" t="inlineStr">
         <is>
-          <t>1科目300,000円（都度発注）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="98" t="inlineStr">
-        <is>
-          <t>教材の監修</t>
-        </is>
-      </c>
-      <c r="C20" s="99" t="inlineStr">
-        <is>
-          <t>内容の監修は聖建様の社内有資格者が担われる前提です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="98" t="inlineStr">
-        <is>
-          <t>実技教育</t>
-        </is>
-      </c>
-      <c r="C21" s="99" t="inlineStr">
-        <is>
-          <t>実技はオンラインで代替できません。受講者の所属事業者が実施する前提です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="96" t="inlineStr">
-        <is>
-          <t>■ 4. 責任の分担</t>
-        </is>
-      </c>
-      <c r="C23" s="97" t="inlineStr"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
+          <t>弊社は官報・通達を監視し、該当しうる改正を自動でメール通知します。その改正が教材のどこに影響するかの判断は、貴社の監修者が行うものとします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="96" t="inlineStr">
+        <is>
+          <t>■ 4. 金額の前提</t>
+        </is>
+      </c>
+      <c r="C21" s="97" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="98" t="inlineStr">
+        <is>
+          <t>教材制作単価</t>
+        </is>
+      </c>
+      <c r="C22" s="99" t="inlineStr">
+        <is>
+          <t>300,000円／科目。貴社ご指定の単価です。改訂・追加時も同額を適用します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="98" t="inlineStr">
+        <is>
+          <t>支払条件</t>
+        </is>
+      </c>
+      <c r="C23" s="99" t="inlineStr">
+        <is>
+          <t>ご発注時に全額を一括でお支払いいただくことを前提とした金額です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
       <c r="B24" s="98" t="inlineStr">
         <is>
-          <t>弊社が保証すること</t>
+          <t>有効期限</t>
         </is>
       </c>
       <c r="C24" s="99" t="inlineStr">
-        <is>
-          <t>教材が安全衛生特別教育規程の定める科目・範囲・時間を満たすこと（監修者名を明示）。受講記録を証明可能な形で保存・出力できること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="B25" s="98" t="inlineStr">
-        <is>
-          <t>弊社が保証しないこと</t>
-        </is>
-      </c>
-      <c r="C25" s="99" t="inlineStr">
-        <is>
-          <t>受講者の所属事業者が負う労働安全衛生法第59条第3項の実施義務が果たされたこと。労働災害が発生しないこと。行政機関が個別の事案において本教材を適法と判断すること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="B26" s="98" t="inlineStr">
-        <is>
-          <t>法令改正への対応</t>
-        </is>
-      </c>
-      <c r="C26" s="99" t="inlineStr">
-        <is>
-          <t>弊社は官報・通達を監視し、該当しうる改正を自動でメール通知します。その改正が教材のどこに影響するかの判断は、聖建様の監修者が行うものとします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="96" t="inlineStr">
-        <is>
-          <t>■ 5. 金額の前提</t>
-        </is>
-      </c>
-      <c r="C28" s="97" t="inlineStr"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="98" t="inlineStr">
-        <is>
-          <t>人日単価</t>
-        </is>
-      </c>
-      <c r="C29" s="99" t="inlineStr">
-        <is>
-          <t>50,000円／人日（シート03のC4で変更可能）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="98" t="inlineStr">
-        <is>
-          <t>教材制作単価</t>
-        </is>
-      </c>
-      <c r="C30" s="99" t="inlineStr">
-        <is>
-          <t>300,000円／科目。聖建様ご指定の単価です。改訂・追加時も同額を適用します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="98" t="inlineStr">
-        <is>
-          <t>支払条件</t>
-        </is>
-      </c>
-      <c r="C31" s="99" t="inlineStr">
-        <is>
-          <t>ご発注時に全額を一括でお支払いいただくことを前提とした金額です。分割払いの場合は金額が変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="98" t="inlineStr">
-        <is>
-          <t>有効期限</t>
-        </is>
-      </c>
-      <c r="C32" s="99" t="inlineStr">
         <is>
           <t>発行日より30日間。</t>
         </is>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17340" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_見積書" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,29 +16,29 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'01_見積書'!$A$1:$F$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'04_教材科目'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05_月額・別途費用'!$A$1:$D$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$26</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="¥#,##0;▲¥#,##0;-"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;h&quot;"/>
-    <numFmt numFmtId="166" formatCode="0&quot;科目&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0&quot;人日&quot;;&quot;▲&quot;#,##0.0&quot;人日&quot;;-"/>
+    <numFmt numFmtId="164" formatCode="\¥#,##0;\▲\¥#,##0;\-"/>
+    <numFmt numFmtId="165" formatCode="0&quot;科目&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0&quot;人日&quot;;&quot;▲&quot;#,##0.0&quot;人日&quot;;\-"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;h&quot;"/>
     <numFmt numFmtId="168" formatCode="&quot;¥&quot;#,##0&quot;  （税抜）&quot;"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -47,211 +46,292 @@
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="006C7A87"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF6C7A87"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001A2430"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF1A2430"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001A2430"/>
+      <color rgb="FF1A2430"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="000000FF"/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="006C7A87"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF6C7A87"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="006C7A87"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF6C7A87"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001E6B4A"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF1E6B4A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001A2430"/>
+      <color rgb="FF1A2430"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001E6B4A"/>
+      <color rgb="FF1E6B4A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001A2430"/>
+      <color rgb="FF1A2430"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="009E2F27"/>
+      <color rgb="FF9E2F27"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="009E2F27"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF9E2F27"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="11.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001A2430"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF1A2430"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="009E2F27"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF9E2F27"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001A2430"/>
+      <color rgb="FF1A2430"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="009E2F27"/>
+      <color rgb="FF9E2F27"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001E6B4A"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF1E6B4A"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001E6B4A"/>
+      <color rgb="FF1E6B4A"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="009E2F27"/>
+      <color rgb="FF9E2F27"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="006C7A87"/>
+      <color rgb="FF6C7A87"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00B05A1E"/>
+      <color rgb="FFB05A1E"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="22"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="000000FF"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001A2430"/>
+      <color rgb="FF1A2430"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="006C7A87"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF6C7A87"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001A2430"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF1A2430"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001B3A57"/>
+      <color rgb="FF1B3A57"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="006C7A87"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF6C7A87"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001A2430"/>
+      <color rgb="FF1A2430"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001A2430"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color rgb="FF1A2430"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="009E2F27"/>
+      <color rgb="FF9E2F27"/>
       <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -263,22 +343,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6EE"/>
+        <fgColor rgb="FFDCE6EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D9"/>
+        <fgColor rgb="FFFFF6D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A57"/>
+        <fgColor rgb="FF1B3A57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F5F7"/>
+        <fgColor rgb="FFF2F5F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -292,23 +372,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
       </left>
       <right style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
       </right>
       <top style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9D4DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D4DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D4DC"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D4DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D4DC"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -316,83 +421,33 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
       </right>
       <top style="thin">
-        <color rgb="00C9D4DC"/>
+        <color rgb="FFC9D4DC"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9D4DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9D4DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D4DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C9D4DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D4DC"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -416,7 +471,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,9 +511,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -466,7 +518,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -478,177 +530,309 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="35" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1027,393 +1211,391 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" style="86" min="1" max="1"/>
+    <col width="20" customWidth="1" style="86" min="2" max="3"/>
+    <col width="16" customWidth="1" style="86" min="4" max="5"/>
+    <col width="18" customWidth="1" style="86" min="6" max="6"/>
+    <col width="3" customWidth="1" style="86" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="86">
+      <c r="B2" s="95" t="inlineStr">
         <is>
           <t>御　見　積　書</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="86">
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>見積番号</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>SP-2026-0003</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="16" customHeight="1" s="86">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2026年9月13日</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="16" customHeight="1" s="86">
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>発行日より30日間</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
+    <row r="8" ht="25" customHeight="1" s="86">
+      <c r="B8" s="91" t="inlineStr">
         <is>
           <t>株式会社聖建　御中</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="93" t="inlineStr">
         <is>
           <t>株式会社スペリオル</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="86">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>〒475-0805　愛知県半田市浜田町1丁目7番地</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="96" t="inlineStr">
         <is>
           <t>〒464-0075　名古屋市千種区内山3-18-10</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="E10" s="6" t="inlineStr">
+    <row r="10" ht="16" customHeight="1" s="86">
+      <c r="E10" s="96" t="inlineStr">
         <is>
           <t>TEL 052-745-6607</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="E11" s="6" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="86">
+      <c r="E11" s="96" t="inlineStr">
         <is>
           <t>登録番号 T9180001048541</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="E12" s="7" t="inlineStr">
+    <row r="12" ht="16" customHeight="1" s="86">
+      <c r="E12" s="85" t="inlineStr">
         <is>
           <t>担当　藤原</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+    <row r="14" ht="17" customHeight="1" s="86">
+      <c r="B14" s="98" t="inlineStr">
         <is>
           <t>下記のとおりお見積り申し上げます。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="B16" s="9" t="inlineStr">
+    <row r="16" ht="32" customHeight="1" s="86">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="101" t="inlineStr">
         <is>
           <t>建設業 特別教育 eラーニング配信システム 構築 および 教材制作（6科目）一式</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="B17" s="9" t="inlineStr">
+      <c r="D16" s="88" t="n"/>
+      <c r="E16" s="88" t="n"/>
+      <c r="F16" s="89" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="86">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>御見積金額</t>
         </is>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="109">
         <f>'03_見積明細'!F28</f>
         <v/>
       </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="14" t="inlineStr"/>
-      <c r="C18" s="15">
+      <c r="D17" s="88" t="n"/>
+      <c r="E17" s="88" t="n"/>
+      <c r="F17" s="89" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="86">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="94">
         <f>"消費税 ¥"&amp;TEXT('03_見積明細'!F29,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT('03_見積明細'!F30,"#,##0")</f>
         <v/>
       </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="12" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="B20" s="9" t="inlineStr">
+      <c r="D18" s="88" t="n"/>
+      <c r="E18" s="88" t="n"/>
+      <c r="F18" s="89" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="86">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>納期</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="90" t="inlineStr">
         <is>
           <t>システム：ご発注後 約4か月　／　教材：第1次3科目 約4か月、第2次3科目 約7か月</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="9" t="inlineStr">
+      <c r="D20" s="88" t="n"/>
+      <c r="E20" s="88" t="n"/>
+      <c r="F20" s="89" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="86">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>納入場所</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="90" t="inlineStr">
         <is>
           <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="12" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="9" t="inlineStr">
+      <c r="D21" s="88" t="n"/>
+      <c r="E21" s="88" t="n"/>
+      <c r="F21" s="89" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="86">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>検収条件</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="90" t="inlineStr">
         <is>
           <t>納品後14日以内に貴社にて検収。期間内にご連絡なき場合は検収完了とみなします。</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="9" t="inlineStr">
+      <c r="D22" s="88" t="n"/>
+      <c r="E22" s="88" t="n"/>
+      <c r="F22" s="89" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="86">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="90" t="inlineStr">
         <is>
           <t>ご発注時に全額を一括でお支払いください。</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="D23" s="88" t="n"/>
+      <c r="E23" s="88" t="n"/>
+      <c r="F23" s="89" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1" s="86">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>内訳</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="18" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="86">
+      <c r="B26" s="92" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="D26" s="89" t="n"/>
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="19" t="inlineStr">
+    <row r="27" ht="17" customHeight="1" s="86">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="100" t="inlineStr">
         <is>
           <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="D27" s="89" t="n"/>
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="110">
         <f>'03_見積明細'!F21</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+    <row r="28" ht="17" customHeight="1" s="86">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="100" t="inlineStr">
         <is>
           <t>特別教育 学科教材 6科目</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="23">
+      <c r="D28" s="89" t="n"/>
+      <c r="E28" s="111">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="110">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="24" t="inlineStr">
+    <row r="29" ht="17" customHeight="1" s="86">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>（税抜）</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr"/>
-      <c r="E29" s="26" t="inlineStr"/>
-      <c r="F29" s="27">
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="112">
         <f>'03_見積明細'!F26</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="19" t="inlineStr">
+    <row r="30" ht="17" customHeight="1" s="86">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>値引</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>貴社特別値引き</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr"/>
-      <c r="E30" s="29" t="inlineStr"/>
-      <c r="F30" s="30">
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="113">
         <f>'03_見積明細'!F27</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="19" t="inlineStr">
+    <row r="31" ht="17" customHeight="1" s="86">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>差引小計</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>（税抜）</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr"/>
-      <c r="E31" s="29" t="inlineStr"/>
-      <c r="F31" s="32">
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="114">
         <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="19" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="86">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr"/>
-      <c r="D32" s="29" t="inlineStr"/>
-      <c r="E32" s="29" t="inlineStr"/>
-      <c r="F32" s="32">
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="114">
         <f>'03_見積明細'!F29</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
+    <row r="33" ht="22" customHeight="1" s="86">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>（税込）</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr"/>
-      <c r="E33" s="14" t="inlineStr"/>
-      <c r="F33" s="35">
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="115">
         <f>'03_見積明細'!F30</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="36" t="inlineStr">
+    <row r="35" ht="17" customHeight="1" s="86">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="37" t="inlineStr">
+    <row r="36" ht="17" customHeight="1" s="86">
+      <c r="B36" s="99" t="inlineStr">
         <is>
           <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="37" t="inlineStr">
+    <row r="37" ht="17" customHeight="1" s="86">
+      <c r="B37" s="99" t="inlineStr">
         <is>
           <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="37" t="inlineStr">
+    <row r="38" ht="17" customHeight="1" s="86">
+      <c r="B38" s="99" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
         </is>
@@ -1457,443 +1639,443 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" style="86" min="1" max="1"/>
+    <col width="40" customWidth="1" style="86" min="2" max="2"/>
+    <col width="16" customWidth="1" style="86" min="3" max="3"/>
+    <col width="14" customWidth="1" style="86" min="4" max="4"/>
+    <col width="56" customWidth="1" style="86" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="86">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>前回お見積りからの増減内訳</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+    <row r="2" ht="17" customHeight="1" s="86">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>2026年9月8日付 SP-2026-0001（税抜 8,000,000円）から、今回のお見積りに至るまでの内訳です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="18" t="inlineStr"/>
-      <c r="B4" s="18" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="86">
+      <c r="A4" s="92" t="n"/>
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="92" t="inlineStr">
         <is>
           <t>増減</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="92" t="inlineStr">
         <is>
           <t>人日</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="92" t="inlineStr">
         <is>
           <t>理由・内容</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="26" t="inlineStr"/>
-      <c r="B5" s="40" t="inlineStr">
+    <row r="5" ht="17" customHeight="1" s="86">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>前回お見積り（2026年9月8日）</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="112" t="n">
         <v>8000000</v>
       </c>
-      <c r="D5" s="41" t="n">
+      <c r="D5" s="116" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>教材10科目＋システム100人日</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+    <row r="6" ht="34" customHeight="1" s="86">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>教材を10科目から6科目へ</t>
         </is>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="117" t="n">
         <v>-1200000</v>
       </c>
-      <c r="D6" s="45" t="inlineStr"/>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="D6" s="118" t="n"/>
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>低圧電気、第2種酸欠、高所作業車、玉掛けの4科目を第2次発注へ。1科目300,000円×4科目</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+    <row r="7" ht="34" customHeight="1" s="86">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>決済機能（ゼウス連携）の追加</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="113" t="n">
         <v>500000</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="119" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>株式会社ゼウスのAPI型決済を組み込み。申込から入金確認、受講開始までを自動化。今回の新規ご要望</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+    <row r="8" ht="34" customHeight="1" s="86">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>受講中のランダム顔照合を除外</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="117" t="n">
         <v>-350000</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="120" t="n">
         <v>-7</v>
       </c>
-      <c r="E8" s="46" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>受講の途中で予告なく撮影する機能を今回の範囲から外します。登録時の本人確認と受講開始時の照合は維持</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+    <row r="9" ht="34" customHeight="1" s="86">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="117" t="n">
         <v>-350000</v>
       </c>
-      <c r="D9" s="45" t="inlineStr"/>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="D9" s="118" t="n"/>
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>ご発注時に全額をお支払いいただく条件に対する調整。分割回収に比べ資金負担と与信リスクが下がるため</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="50" t="inlineStr">
+    <row r="10" ht="26" customHeight="1" s="86">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>今回のお見積り（税抜）</t>
         </is>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="121">
         <f>C5+SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="122">
         <f>'03_見積明細'!D21</f>
         <v/>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>教材6科目＋システム103人日</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="86">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>（検算）見積明細の小計＋調整額</t>
         </is>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="123">
         <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="54" t="inlineStr">
+    <row r="13" ht="20" customHeight="1" s="86">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>増減の内訳（金額の動き）</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="55" t="inlineStr">
+    <row r="14" ht="17" customHeight="1" s="86">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>減額の要因</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="20" t="inlineStr">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1" s="86">
+      <c r="B15" s="100" t="inlineStr">
         <is>
           <t>教材 4科目の削減</t>
         </is>
       </c>
-      <c r="C15" s="56" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
         <is>
           <t>▲1,200,000</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr"/>
-      <c r="E15" s="29" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="20" t="inlineStr">
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="86">
+      <c r="B16" s="100" t="inlineStr">
         <is>
           <t>受講中ランダム照合の除外</t>
         </is>
       </c>
-      <c r="C16" s="56" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>▲350,000</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr"/>
-      <c r="E16" s="29" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="20" t="inlineStr">
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1" s="86">
+      <c r="B17" s="100" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
         </is>
       </c>
-      <c r="C17" s="56" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
         <is>
           <t>▲350,000</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr"/>
-      <c r="E17" s="29" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="57" t="inlineStr">
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1" s="86">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>▲1,900,000</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr"/>
-      <c r="E18" s="29" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="59" t="inlineStr">
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1" s="86">
+      <c r="B20" s="48" t="inlineStr">
         <is>
           <t>増額の要因</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="20" t="inlineStr">
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="86">
+      <c r="B21" s="100" t="inlineStr">
         <is>
           <t>決済機能（ゼウス連携）の追加</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>＋500,000</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr"/>
-      <c r="E21" s="29" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="57" t="inlineStr">
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1" s="86">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C22" s="61" t="inlineStr">
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>＋500,000</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr"/>
-      <c r="E22" s="29" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="62" t="inlineStr">
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1" s="86">
+      <c r="B24" s="51" t="inlineStr">
         <is>
           <t>差引</t>
         </is>
       </c>
-      <c r="C24" s="63" t="inlineStr">
+      <c r="C24" s="52" t="inlineStr">
         <is>
           <t>▲1,400,000</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>8,000,000 − 1,400,000 ＝ 6,600,000</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="64" t="inlineStr">
+    <row r="26" ht="17" customHeight="1" s="86">
+      <c r="B26" s="53" t="inlineStr">
         <is>
           <t>■ このシートは社内資料です（先方には提出しません）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="65" t="inlineStr">
+    <row r="27" ht="17" customHeight="1" s="86">
+      <c r="B27" s="54" t="inlineStr">
         <is>
           <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="65" t="inlineStr">
+    <row r="28" ht="17" customHeight="1" s="86">
+      <c r="B28" s="54" t="inlineStr">
         <is>
           <t>先方向けには「前回からの変更は受講中のランダム顔照合を外すことだけ」と説明し、</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="65" t="inlineStr">
+    <row r="29" ht="17" customHeight="1" s="86">
+      <c r="B29" s="54" t="inlineStr">
         <is>
           <t>下の④は見積書・注文書の上では「貴社特別値引き（特別値引き）」と表示しています。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="65" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="66" t="inlineStr">
+    <row r="30" ht="17" customHeight="1" s="86">
+      <c r="B30" s="54" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="86">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>■ この表の使い方（社内の根拠整理）</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="65" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="86">
+      <c r="B32" s="54" t="inlineStr">
         <is>
           <t>単純な値引きではなく、次の3つの対価として金額が下がっていることを社内で説明できます。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="65" t="inlineStr">
+    <row r="33" ht="17" customHeight="1" s="86">
+      <c r="B33" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　① 納品する教材が4科目減ること（成果物の減少）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="65" t="inlineStr">
+    <row r="34" ht="17" customHeight="1" s="86">
+      <c r="B34" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　② 受講中のランダム照合を実装しないこと（機能の減少）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="65" t="inlineStr">
+    <row r="35" ht="17" customHeight="1" s="86">
+      <c r="B35" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　③ 全額を前払いいただくこと（支払条件の対価）</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="65" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="65" t="inlineStr">
+    <row r="36" ht="17" customHeight="1" s="86">
+      <c r="B36" s="54" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1" s="86">
+      <c r="B37" s="54" t="inlineStr">
         <is>
           <t>一方で、決済機能（ゼウス連携）は新しいご要望のため増額しています。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="67" t="inlineStr">
+    <row r="38" ht="17" customHeight="1" s="86">
+      <c r="B38" s="56" t="inlineStr">
         <is>
           <t>減る理由と増える理由の両方を示すことで、価格の根拠が明確になります。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="65" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="66" t="inlineStr">
+    <row r="39" ht="17" customHeight="1" s="86">
+      <c r="B39" s="54" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1" s="86">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>■ 月額費用の変更</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="65" t="inlineStr">
+    <row r="41" ht="17" customHeight="1" s="86">
+      <c r="B41" s="54" t="inlineStr">
         <is>
           <t>保守・運用サービス　80,000円 → 60,000円（▲20,000円）</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="65" t="inlineStr">
+    <row r="42" ht="17" customHeight="1" s="86">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　受講中のランダム照合を実装しないため、照合結果の目視確認という運用作業がなくなります。</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="67" t="inlineStr">
+    <row r="43" ht="17" customHeight="1" s="86">
+      <c r="B43" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">　運用工数が実際に減るため、その分を月額に反映しています。</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="65" t="inlineStr">
+    <row r="44" ht="17" customHeight="1" s="86">
+      <c r="B44" s="54" t="inlineStr">
         <is>
           <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="65" t="inlineStr">
+    <row r="45" ht="17" customHeight="1" s="86">
+      <c r="B45" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　　　　　　合計 80,000円／月（サーバー費を除く・税抜）</t>
         </is>
@@ -1913,671 +2095,671 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="86" min="1" max="1"/>
+    <col width="28" customWidth="1" style="86" min="2" max="2"/>
+    <col width="54" customWidth="1" style="86" min="3" max="3"/>
+    <col width="9" customWidth="1" style="86" min="4" max="4"/>
+    <col width="12" customWidth="1" style="86" min="5" max="5"/>
+    <col width="14" customWidth="1" style="86" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="86">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>見積明細</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+    <row r="2" ht="17" customHeight="1" s="86">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>黄色のセルが編集箇所です。人日単価と各項目の人日を変えると、見積書・増減内訳・注文書まで自動で再計算されます。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+    <row r="4" ht="17" customHeight="1" s="86">
+      <c r="A4" s="102" t="inlineStr">
         <is>
           <t>人日単価</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="69" t="n">
+      <c r="B4" s="89" t="n"/>
+      <c r="C4" s="124" t="n">
         <v>50000</v>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>円／人日</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6" ht="22" customHeight="1" s="86">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="92" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="92" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="92" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="70" t="inlineStr">
+    <row r="7" ht="17" customHeight="1" s="86">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>1. システム開発</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="12" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="B7" s="88" t="n"/>
+      <c r="C7" s="88" t="n"/>
+      <c r="D7" s="88" t="n"/>
+      <c r="E7" s="88" t="n"/>
+      <c r="F7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="86">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>要件定義・基本設計</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>業務フローの確定、データモデル設計、API設計、画面設計、利用規約・特定商取引法表記・個人情報の取扱い方針の整備支援</t>
         </is>
       </c>
-      <c r="D8" s="72" t="n">
+      <c r="D8" s="125" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="110">
         <f>D8*E8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="71" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="86">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>AWS本番環境の構築</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>VPC、EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch の構築とCI/CD</t>
         </is>
       </c>
-      <c r="D9" s="72" t="n">
+      <c r="D9" s="125" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="110">
         <f>D9*E9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="71" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="86">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>動画配信基盤</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>HLS変換（FFmpeg）、短寿命の署名付きマニフェスト配信、章単位の受講制御、MP4直リンクの排除</t>
         </is>
       </c>
-      <c r="D10" s="72" t="n">
+      <c r="D10" s="125" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="110">
         <f>D10*E10</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="71" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="86">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>視聴整合性・実視聴時間の集計</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>heartbeatの受信と検証、未視聴位置へのシーク制限、倍速検知、可視状態の判定、サーバー側での検証済み秒数の集計、異常検知</t>
         </is>
       </c>
-      <c r="D11" s="72" t="n">
+      <c r="D11" s="125" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="110">
         <f>D11*E11</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="71" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="86">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>本人確認（登録時）</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>その場撮影UI（getUserMedia）、ライブネス判定、本人確認書類との突合、顔の1:1照合、運営の審査画面</t>
         </is>
       </c>
-      <c r="D12" s="72" t="n">
+      <c r="D12" s="125" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="110">
         <f>D12*E12</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="71" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="86">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>PC↔スマートフォン引き継ぎ</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>QRコードとワンタイムURLによる撮影工程の引き継ぎ</t>
         </is>
       </c>
-      <c r="D13" s="72" t="n">
+      <c r="D13" s="125" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="110">
         <f>D13*E13</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="71" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="86">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>顔照合（受講開始時のみ）</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>各章の再生開始時に1:1照合を実施。受講中のランダム照合は今回の範囲外とします</t>
         </is>
       </c>
-      <c r="D14" s="72" t="n">
+      <c r="D14" s="125" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="110">
         <f>D14*E14</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="71" t="inlineStr">
+    <row r="15" ht="30" customHeight="1" s="86">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>確認問題・自動採点</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>章末問題、修了確認テスト、出題のランダム化、不合格後の再受講制御</t>
         </is>
       </c>
-      <c r="D15" s="72" t="n">
+      <c r="D15" s="125" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="110">
         <f>D15*E15</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="71" t="inlineStr">
+    <row r="16" ht="30" customHeight="1" s="86">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>修了判定・修了証の発行</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>サーバー側での修了条件の再検証、修了記録の作成、修了証PDFの発行・再発行・ダウンロード</t>
         </is>
       </c>
-      <c r="D16" s="72" t="n">
+      <c r="D16" s="125" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="110">
         <f>D16*E16</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="71" t="inlineStr">
+    <row r="17" ht="30" customHeight="1" s="86">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>決済機能（ゼウス連携）</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>株式会社ゼウスのデータ転送（API）型による決済組み込み。申込から入金確認、受講開始までの自動化。領収書の発行</t>
         </is>
       </c>
-      <c r="D17" s="72" t="n">
+      <c r="D17" s="125" t="n">
         <v>10</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="110">
         <f>D17*E17</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="71" t="inlineStr">
+    <row r="18" ht="30" customHeight="1" s="86">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>受講者ポータル</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応</t>
         </is>
       </c>
-      <c r="D18" s="72" t="n">
+      <c r="D18" s="125" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="110">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="71" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="86">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>運営管理画面（基本機能）</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理</t>
         </is>
       </c>
-      <c r="D19" s="72" t="n">
+      <c r="D19" s="125" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="110">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="71" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="86">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>結合テスト・E2E・受入支援</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成</t>
         </is>
       </c>
-      <c r="D20" s="72" t="n">
+      <c r="D20" s="125" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="110">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="110">
         <f>D20*E20</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr"/>
-      <c r="B21" s="40" t="inlineStr">
+    <row r="21" ht="17" customHeight="1" s="86">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>システム開発 小計</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr"/>
-      <c r="D21" s="73">
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="126">
         <f>SUM(D8:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="26" t="inlineStr"/>
-      <c r="F21" s="27">
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="112">
         <f>SUM(F8:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="70" t="inlineStr">
+    <row r="23" ht="17" customHeight="1" s="86">
+      <c r="A23" s="103" t="inlineStr">
         <is>
           <t>2. eラーニング教材の制作</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="71" t="inlineStr">
+      <c r="B23" s="88" t="n"/>
+      <c r="C23" s="88" t="n"/>
+      <c r="D23" s="88" t="n"/>
+      <c r="E23" s="88" t="n"/>
+      <c r="F23" s="89" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="86">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>教材</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>特別教育 学科教材の制作</t>
         </is>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="35">
         <f>"6科目・学科"&amp;TEXT('04_教材科目'!$D$17,"0.0")&amp;"時間分。構成台本の書き起こし、スライド、図解、ナレーション、バーチャル講師映像、章末問題・修了確認テストの作成"</f>
         <v/>
       </c>
-      <c r="D24" s="74">
+      <c r="D24" s="127">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="E24" s="75">
+      <c r="E24" s="128">
         <f>'04_教材科目'!$D$4</f>
         <v/>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="110">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr"/>
-      <c r="B26" s="62" t="inlineStr">
+    <row r="26" ht="19" customHeight="1" s="86">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="51" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="52">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="122">
         <f>D21</f>
         <v/>
       </c>
-      <c r="E26" s="14" t="inlineStr"/>
-      <c r="F26" s="35">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="115">
         <f>F21+F24</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="76" t="inlineStr">
+    <row r="27" ht="17" customHeight="1" s="86">
+      <c r="B27" s="64" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>ご発注時に全額をお支払いいただく条件に対する調整額です</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr"/>
-      <c r="E27" s="29" t="inlineStr"/>
-      <c r="F27" s="69" t="n">
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="124" t="n">
         <v>-350000</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="77" t="inlineStr">
+    <row r="28" ht="17" customHeight="1" s="86">
+      <c r="B28" s="65" t="inlineStr">
         <is>
           <t>差引 小計（税抜）</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr"/>
-      <c r="D28" s="29" t="inlineStr"/>
-      <c r="E28" s="29" t="inlineStr"/>
-      <c r="F28" s="32">
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="114">
         <f>F26+F27</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="77" t="inlineStr">
+    <row r="29" ht="17" customHeight="1" s="86">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="D29" s="78" t="n">
+      <c r="D29" s="66" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="29" t="inlineStr"/>
-      <c r="F29" s="32">
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="114">
         <f>ROUND(F28*D29,0)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="14" t="inlineStr"/>
-      <c r="B30" s="50" t="inlineStr">
+    <row r="30" ht="24" customHeight="1" s="86">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>合計（税込）</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr"/>
-      <c r="E30" s="14" t="inlineStr"/>
-      <c r="F30" s="51">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="121">
         <f>F28+F29</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="66" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="86">
+      <c r="A32" s="55" t="inlineStr">
         <is>
           <t>■ 今回の範囲から外したもの（第2次発注のご相談）</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="65" t="inlineStr">
+    <row r="33" ht="17" customHeight="1" s="86">
+      <c r="A33" s="54" t="inlineStr">
         <is>
           <t>・受講中のランダム顔照合（受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="65" t="inlineStr">
+    <row r="34" ht="17" customHeight="1" s="86">
+      <c r="A34" s="54" t="inlineStr">
         <is>
           <t>・企業管理ポータル（従業員の一括申込、進捗確認、修了者一覧のCSV出力）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="65" t="inlineStr">
+    <row r="35" ht="17" customHeight="1" s="86">
+      <c r="A35" s="54" t="inlineStr">
         <is>
           <t>・運営管理画面の拡張（監査レポート出力、組織管理、売上・入金管理）</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="65" t="inlineStr">
+    <row r="36" ht="17" customHeight="1" s="86">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>・受講画面からの質疑応答機能（当面はメールで対応）</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="65" t="inlineStr">
+    <row r="37" ht="17" customHeight="1" s="86">
+      <c r="A37" s="54" t="inlineStr">
         <is>
           <t>・修了証の真正性検証ページ（QRコード）</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="65" t="inlineStr">
+    <row r="38" ht="17" customHeight="1" s="86">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>・教材 4科目（低圧電気、第2種酸欠、高所作業車、玉掛け）</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="65" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="66" t="inlineStr">
+    <row r="39" ht="17" customHeight="1" s="86">
+      <c r="A39" s="54" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1" s="86">
+      <c r="A40" s="55" t="inlineStr">
         <is>
           <t>■ 本見積に含まれないもの（別途）</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="65" t="inlineStr">
+    <row r="41" ht="17" customHeight="1" s="86">
+      <c r="A41" s="54" t="inlineStr">
         <is>
           <t>・月額の保守・運用サービスおよび法令改正監視・通知サービス（シート05）</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="65" t="inlineStr">
+    <row r="42" ht="17" customHeight="1" s="86">
+      <c r="A42" s="54" t="inlineStr">
         <is>
           <t>・AWSの利用料（聖建様のご負担）、株式会社ゼウスとのご契約（初期費用無料・月額3,000円・決済手数料）</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="65" t="inlineStr">
+    <row r="43" ht="17" customHeight="1" s="86">
+      <c r="A43" s="54" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂（1科目300,000円・都度発注）</t>
         </is>
@@ -2602,384 +2784,384 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" style="86" min="1" max="1"/>
+    <col width="7" customWidth="1" style="86" min="2" max="2"/>
+    <col width="32" customWidth="1" style="86" min="3" max="3"/>
+    <col width="8" customWidth="1" style="86" min="4" max="4"/>
+    <col width="38" customWidth="1" style="86" min="5" max="5"/>
+    <col width="14" customWidth="1" style="86" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="86">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>eラーニング教材 制作科目一覧（6科目）</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+    <row r="2" ht="17" customHeight="1" s="86">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>A列に 1 を入れた科目が制作対象になります。10科目から6科目へ絞り込んだ状態です。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
-      <c r="B4" s="68" t="inlineStr">
+    <row r="4" ht="17" customHeight="1" s="86">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="102" t="inlineStr">
         <is>
           <t>制作単価（1科目あたり）</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr"/>
-      <c r="D4" s="69" t="n">
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="124" t="n">
         <v>300000</v>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>円／科目</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1" s="86">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>制作
 (1で選択)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>優先
 順位</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>特別教育の名称</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="92" t="inlineStr">
         <is>
           <t>学科
 (時間)</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="92" t="inlineStr">
         <is>
           <t>選定・除外の理由</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="92" t="inlineStr">
         <is>
           <t>制作費</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="79" t="n">
+    <row r="7" ht="26" customHeight="1" s="86">
+      <c r="A7" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="80" t="n">
+      <c r="B7" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>フルハーネス型墜落制止用器具</t>
         </is>
       </c>
-      <c r="D7" s="81" t="n">
+      <c r="D7" s="129" t="n">
         <v>4.5</v>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>対象職種が最も広く、初期商品群の中核</t>
         </is>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="110">
         <f>IF(A7=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="79" t="n">
+    <row r="8" ht="26" customHeight="1" s="86">
+      <c r="A8" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="80" t="n">
+      <c r="B8" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>足場の組立て・解体・変更</t>
         </is>
       </c>
-      <c r="D8" s="81" t="n">
+      <c r="D8" s="129" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="46" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>実技の定めがなく、学科のみで修了まで完結する</t>
         </is>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="110">
         <f>IF(A8=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="79" t="n">
+    <row r="9" ht="26" customHeight="1" s="86">
+      <c r="A9" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="80" t="n">
+      <c r="B9" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>自由研削用といし</t>
         </is>
       </c>
-      <c r="D9" s="81" t="n">
+      <c r="D9" s="129" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>幅広い工種で利用され、学科時間もコンパクト</t>
         </is>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="110">
         <f>IF(A9=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="79" t="n">
+    <row r="10" ht="26" customHeight="1" s="86">
+      <c r="A10" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="80" t="n">
+      <c r="B10" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="82" t="inlineStr">
+      <c r="C10" s="70" t="inlineStr">
         <is>
           <t>低圧電気取扱業務</t>
         </is>
       </c>
-      <c r="D10" s="83" t="n">
+      <c r="D10" s="130" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>学科7時間と最長級。制作負担が大きく第2次へ</t>
         </is>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="110">
         <f>IF(A10=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="79" t="n">
+    <row r="11" ht="26" customHeight="1" s="86">
+      <c r="A11" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="80" t="n">
+      <c r="B11" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>アーク溶接等</t>
         </is>
       </c>
-      <c r="D11" s="81" t="n">
+      <c r="D11" s="129" t="n">
         <v>11</v>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>既存の制作資産を活用できるため優先</t>
         </is>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="110">
         <f>IF(A11=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="79" t="n">
+    <row r="12" ht="26" customHeight="1" s="86">
+      <c r="A12" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="80" t="n">
+      <c r="B12" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>石綿使用建築物等の解体・破砕等</t>
         </is>
       </c>
-      <c r="D12" s="81" t="n">
+      <c r="D12" s="129" t="n">
         <v>4.5</v>
       </c>
-      <c r="E12" s="46" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>実技なし。解体・改修の需要が継続的にある</t>
         </is>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="110">
         <f>IF(A12=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="79" t="n">
+    <row r="13" ht="26" customHeight="1" s="86">
+      <c r="A13" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="80" t="n">
+      <c r="B13" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>特定粉じん作業</t>
         </is>
       </c>
-      <c r="D13" s="81" t="n">
+      <c r="D13" s="129" t="n">
         <v>4.5</v>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>実技なし。建設現場の有害業務として汎用性が高い</t>
         </is>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="110">
         <f>IF(A13=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="79" t="n">
+    <row r="14" ht="26" customHeight="1" s="86">
+      <c r="A14" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="B14" s="80" t="n">
+      <c r="B14" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C14" s="70" t="inlineStr">
         <is>
           <t>第2種酸素欠乏危険作業</t>
         </is>
       </c>
-      <c r="D14" s="83" t="n">
+      <c r="D14" s="130" t="n">
         <v>5.5</v>
       </c>
-      <c r="E14" s="46" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>対象職種が設備・土木に限られるため第2次へ</t>
         </is>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="110">
         <f>IF(A14=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="79" t="n">
+    <row r="15" ht="26" customHeight="1" s="86">
+      <c r="A15" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="B15" s="80" t="n">
+      <c r="B15" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="82" t="inlineStr">
+      <c r="C15" s="70" t="inlineStr">
         <is>
           <t>高所作業車（10m未満）</t>
         </is>
       </c>
-      <c r="D15" s="83" t="n">
+      <c r="D15" s="130" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="46" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>実技3時間を伴い、対象が限定的なため第2次へ</t>
         </is>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="110">
         <f>IF(A15=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="79" t="n">
+    <row r="16" ht="26" customHeight="1" s="86">
+      <c r="A16" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="B16" s="80" t="n">
+      <c r="B16" s="68" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="82" t="inlineStr">
+      <c r="C16" s="70" t="inlineStr">
         <is>
           <t>玉掛け（1t未満）</t>
         </is>
       </c>
-      <c r="D16" s="83" t="n">
+      <c r="D16" s="130" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="46" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>実技4時間を伴い、対象が限定的なため第2次へ</t>
         </is>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="110">
         <f>IF(A16=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="84">
+    <row r="17" ht="17" customHeight="1" s="86">
+      <c r="A17" s="131">
         <f>SUM(A7:A16)</f>
         <v/>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="68" t="inlineStr">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="102" t="inlineStr">
         <is>
           <t>制作対象 合計</t>
         </is>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="132">
         <f>SUMPRODUCT($A7:$A16,$D7:$D16)</f>
         <v/>
       </c>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="86">
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="133">
         <f>SUM(F7:F16)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="66" t="inlineStr">
+    <row r="19" ht="17" customHeight="1" s="86">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>■ 選定の考え方</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+    <row r="20" ht="17" customHeight="1" s="86">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>・実技の定めがない科目（足場・石綿・特定粉じん）を優先し、最短で販売を開始できるようにしています。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="65" t="inlineStr">
+    <row r="21" ht="17" customHeight="1" s="86">
+      <c r="A21" s="54" t="inlineStr">
         <is>
           <t>・アーク溶接等は既存の制作資産があるため、優先して商品化します。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="65" t="inlineStr">
+    <row r="22" ht="17" customHeight="1" s="86">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>・除外した4科目は、学科時間が長いか対象職種が限定的なものです。第2次発注でのご検討をお願いします。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="65" t="inlineStr">
+    <row r="23" ht="17" customHeight="1" s="86">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>・A列の 1 と 0 を入れ替えれば、対象科目を自由に変更できます（見積金額も自動で追随します）。</t>
         </is>
@@ -3000,289 +3182,289 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" style="86" min="1" max="1"/>
+    <col width="32" customWidth="1" style="86" min="2" max="2"/>
+    <col width="16" customWidth="1" style="86" min="3" max="3"/>
+    <col width="66" customWidth="1" style="86" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="86">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>月額費用と別途費用</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+    <row r="2" ht="17" customHeight="1" s="86">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>初期費用（シート01）とは別に、下記が発生します。金額はすべて税抜です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="86">
+      <c r="A4" s="92" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="92" t="inlineStr">
         <is>
           <t>月額／単価</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="92" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="87" t="inlineStr">
+    <row r="5" ht="46" customHeight="1" s="86">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>弊社へ
 お支払い</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>保守・運用サービス</t>
         </is>
       </c>
-      <c r="C5" s="69" t="n">
+      <c r="C5" s="124" t="n">
         <v>60000</v>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="90" t="inlineStr">
         <is>
           <t>システムの死活監視とエラー監視、障害対応、軽微な改修、受講者からの問い合わせ一次対応、月次レポート。受講中のランダム照合を実装しないため、照合結果の目視確認が不要となり、前回の80,000円から減額しています</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="26" t="inlineStr"/>
-      <c r="B6" s="77" t="inlineStr">
+    <row r="6" ht="40" customHeight="1" s="86">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>法令改正監視・通知サービス</t>
         </is>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="124" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="90" t="inlineStr">
         <is>
           <t>月2回（月初・月中）、官報・厚生労働省の通達・パブリックコメントを確認。対象6科目に影響しうる改正を検知したら、聖建様と弊社の双方へ自動でメール通知。月次で「該当なし」も含めて報告</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr"/>
-      <c r="B7" s="62" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="86">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="51" t="inlineStr">
         <is>
           <t>月額 小計（サーバー費を除く）</t>
         </is>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="121">
         <f>SUM(C5:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>聖建様のご指定額です</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="87" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="86">
+      <c r="A9" s="75" t="inlineStr">
         <is>
           <t>お客様
 ご負担</t>
         </is>
       </c>
-      <c r="B9" s="77" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>AWS 利用料（構成B・推奨）</t>
         </is>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="124" t="n">
         <v>22800</v>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="90" t="inlineStr">
         <is>
           <t>EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch。聖建様名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="26" t="inlineStr"/>
-      <c r="B10" s="77" t="inlineStr">
+    <row r="10" ht="28" customHeight="1" s="86">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>従量課金（顔照合・配信ほか）</t>
         </is>
       </c>
-      <c r="C10" s="88" t="inlineStr">
+      <c r="C10" s="76" t="inlineStr">
         <is>
           <t>実費</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="90" t="inlineStr">
         <is>
           <t>顔照合API、ライブネス判定、CDN転送、メール送信。受講者100名／月で約600円（AWS利用料に含まれます）</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="26" t="inlineStr"/>
-      <c r="B11" s="77" t="inlineStr">
+    <row r="11" ht="32" customHeight="1" s="86">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>株式会社ゼウス（決済代行）</t>
         </is>
       </c>
-      <c r="C11" s="69" t="n">
+      <c r="C11" s="124" t="n">
         <v>3000</v>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="90" t="inlineStr">
         <is>
           <t>初期費用は無料。月額3,000円。クレジットカード決済手数料は最大3.5%（売上に応じて発生）。聖建様が直接ご契約いただきます</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="87" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="86">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>都度
 発注</t>
         </is>
       </c>
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>教材の改訂（法令改正対応）</t>
         </is>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="113">
         <f>'04_教材科目'!D4</f>
         <v/>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="90" t="inlineStr">
         <is>
           <t>1科目あたり。新規制作と同額です。台本の修正、該当部分の動画の再生成と差し替え、教材の版の更新を含みます</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="26" t="inlineStr"/>
-      <c r="B14" s="77" t="inlineStr">
+    <row r="14" ht="28" customHeight="1" s="86">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>教材の追加制作（第2次）</t>
         </is>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="113">
         <f>'04_教材科目'!D4</f>
         <v/>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="90" t="inlineStr">
         <is>
           <t>低圧電気、第2種酸欠、高所作業車、玉掛けの4科目。1科目あたり300,000円</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="16" ht="19" customHeight="1" s="86">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>参考：月額の合計（聖建様のご負担総額）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="77" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="86">
+      <c r="B17" s="65" t="inlineStr">
         <is>
           <t>弊社サービス ＋ AWS ＋ ゼウス月額</t>
         </is>
       </c>
-      <c r="C17" s="89">
+      <c r="C17" s="134">
         <f>'05_月額・別途費用'!C7+C9+C11</f>
         <v/>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>税抜。決済手数料は売上に応じて別途発生します</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="66" t="inlineStr">
+    <row r="19" ht="17" customHeight="1" s="86">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>■ 月額80,000円の根拠</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+    <row r="20" ht="17" customHeight="1" s="86">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>聖建様のご指定額（サーバー費を除く月額80,000円）にあわせ、内訳を次のとおり組みました。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="65" t="inlineStr">
+    <row r="21" ht="17" customHeight="1" s="86">
+      <c r="A21" s="54" t="inlineStr">
         <is>
           <t>・保守・運用サービス　60,000円　… 受講中のランダム照合を実装しないため、照合結果の</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="67" t="inlineStr">
+    <row r="22" ht="17" customHeight="1" s="86">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">　　目視確認という運用作業がなくなります。その分を減額しています。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="65" t="inlineStr">
+    <row r="23" ht="17" customHeight="1" s="86">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>・法令改正監視・通知サービス　20,000円　… 前回から変更ありません。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="65" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="66" t="inlineStr">
+    <row r="24" ht="17" customHeight="1" s="86">
+      <c r="A24" s="54" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1" s="86">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>■ ゼウスについて</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="65" t="inlineStr">
+    <row r="26" ht="17" customHeight="1" s="86">
+      <c r="A26" s="54" t="inlineStr">
         <is>
           <t>・株式会社ゼウス（1994年設立・国内の決済代行事業者）との契約は聖建様が直接行っていただきます。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="65" t="inlineStr">
+    <row r="27" ht="17" customHeight="1" s="86">
+      <c r="A27" s="54" t="inlineStr">
         <is>
           <t>・初期費用は無料、月額3,000円、クレジットカード決済手数料は最大3.5%です（2026年9月時点）。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="65" t="inlineStr">
+    <row r="28" ht="17" customHeight="1" s="86">
+      <c r="A28" s="54" t="inlineStr">
         <is>
           <t>・接続方式はデータ転送（API）型を想定しています。申込から入金確認、受講開始までを自動化します。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="64" t="inlineStr">
+    <row r="29" ht="17" customHeight="1" s="86">
+      <c r="A29" s="53" t="inlineStr">
         <is>
           <t>・最新の料金と条件は、ご契約前にゼウス社へ直接ご確認ください。</t>
         </is>
@@ -3301,332 +3483,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:F34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" style="86" min="1" max="1"/>
+    <col width="20" customWidth="1" style="86" min="2" max="2"/>
+    <col width="24" customWidth="1" style="86" min="3" max="3"/>
+    <col width="14" customWidth="1" style="86" min="4" max="4"/>
+    <col width="16" customWidth="1" style="86" min="5" max="5"/>
+    <col width="18" customWidth="1" style="86" min="6" max="6"/>
+    <col width="3" customWidth="1" style="86" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="86">
+      <c r="B2" s="95" t="inlineStr">
         <is>
           <t>注　文　書</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="86">
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>注文番号</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>（ご記入ください）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SP-2026-0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="86">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　　　　　月　　　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" s="86">
+      <c r="B7" s="91" t="inlineStr">
         <is>
           <t>株式会社スペリオル　御中</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="96" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="22" customHeight="1" s="86">
+      <c r="B8" s="97" t="inlineStr">
         <is>
           <t>〒464-0075　名古屋市千種区内山3-18-10</t>
         </is>
       </c>
-      <c r="E8" s="90" t="inlineStr">
+      <c r="E8" s="105" t="inlineStr">
         <is>
           <t>株式会社聖建</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="86">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>TEL 052-745-6607　／　登録番号 T9180001048541</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="96" t="inlineStr">
         <is>
           <t>〒475-0805　愛知県半田市浜田町1丁目7番地</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="65" t="inlineStr">
-        <is>
-          <t>担当　藤原 様</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+    <row r="10" ht="17" customHeight="1" s="86">
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　</t>
+        </is>
+      </c>
+      <c r="E10" s="96" t="inlineStr">
         <is>
           <t>TEL 0569-84-9669</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="E11" s="91" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="86">
+      <c r="E11" s="104" t="inlineStr">
         <is>
           <t>ご担当　　　　　　　　　　　　　　印</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+    <row r="13" ht="17" customHeight="1" s="86">
+      <c r="B13" s="98" t="inlineStr">
         <is>
           <t>下記のとおり注文いたします。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="9" t="inlineStr">
+    <row r="15" ht="30" customHeight="1" s="86">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="101" t="inlineStr">
         <is>
           <t>建設業 特別教育 eラーニング配信システム 構築 および 教材制作（6科目）一式</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="D15" s="88" t="n"/>
+      <c r="E15" s="88" t="n"/>
+      <c r="F15" s="89" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="86">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>根拠見積</t>
         </is>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="90">
         <f>'01_見積書'!C4&amp;"（"&amp;'01_見積書'!C5&amp;" 発行）"</f>
         <v/>
       </c>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="D16" s="88" t="n"/>
+      <c r="E16" s="88" t="n"/>
+      <c r="F16" s="89" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="86">
+      <c r="B18" s="92" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr"/>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="E18" s="92" t="n"/>
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="19" t="inlineStr">
+    <row r="19" ht="28" customHeight="1" s="86">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="78" t="inlineStr">
         <is>
           <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr"/>
-      <c r="F19" s="22">
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="110">
         <f>'03_見積明細'!F21</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="19" t="inlineStr">
+    <row r="20" ht="28" customHeight="1" s="86">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
       </c>
-      <c r="C20" s="92" t="inlineStr">
+      <c r="C20" s="78" t="inlineStr">
         <is>
           <t>特別教育 学科教材 6科目</t>
         </is>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="111">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="E20" s="29" t="inlineStr"/>
-      <c r="F20" s="22">
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="110">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="40" t="inlineStr">
+    <row r="21" ht="17" customHeight="1" s="86">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr"/>
-      <c r="D21" s="26" t="inlineStr"/>
-      <c r="E21" s="26" t="inlineStr"/>
-      <c r="F21" s="27">
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="112">
         <f>SUM(F19:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="76" t="inlineStr">
+    <row r="22" ht="17" customHeight="1" s="86">
+      <c r="B22" s="64" t="inlineStr">
         <is>
           <t>特別値引き</t>
         </is>
       </c>
-      <c r="C22" s="93" t="inlineStr"/>
-      <c r="D22" s="29" t="inlineStr"/>
-      <c r="E22" s="29" t="inlineStr"/>
-      <c r="F22" s="30">
+      <c r="C22" s="79" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="113">
         <f>'03_見積明細'!F27</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="77" t="inlineStr">
+    <row r="23" ht="17" customHeight="1" s="86">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
       </c>
-      <c r="C23" s="93" t="inlineStr"/>
-      <c r="D23" s="94">
+      <c r="C23" s="79" t="n"/>
+      <c r="D23" s="80">
         <f>'03_見積明細'!D29</f>
         <v/>
       </c>
-      <c r="E23" s="29" t="inlineStr"/>
-      <c r="F23" s="32">
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="114">
         <f>ROUND((F21+F22)*D23,0)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="50" t="inlineStr">
+    <row r="24" ht="26" customHeight="1" s="86">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>ご注文金額（税込）</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="14" t="inlineStr"/>
-      <c r="F24" s="95">
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="135">
         <f>F21+F22+F23</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="26" ht="42" customHeight="1" s="86">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>納期</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="90" t="inlineStr">
         <is>
           <t>システム：ご発注後 約4か月　／　教材：第1次3科目 約4か月、第2次3科目 約7か月</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="12" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="D26" s="88" t="n"/>
+      <c r="E26" s="88" t="n"/>
+      <c r="F26" s="89" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="86">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>納入場所</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="90" t="inlineStr">
         <is>
           <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="12" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="D27" s="88" t="n"/>
+      <c r="E27" s="88" t="n"/>
+      <c r="F27" s="89" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="86">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>検収条件</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="90" t="inlineStr">
         <is>
           <t>納品後14日以内に検収。期間内にご連絡なき場合は検収完了とみなします。</t>
         </is>
       </c>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="B29" s="9" t="inlineStr">
+      <c r="D28" s="88" t="n"/>
+      <c r="E28" s="88" t="n"/>
+      <c r="F28" s="89" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="86">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="90" t="inlineStr">
         <is>
           <t>本注文書の発行時に、上記ご注文金額の全額を一括でお支払いいたします。</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="12" t="n"/>
+      <c r="D29" s="88" t="n"/>
+      <c r="E29" s="88" t="n"/>
+      <c r="F29" s="89" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="86">
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="86">
+      <c r="B32" s="99" t="inlineStr">
+        <is>
+          <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="86">
+      <c r="B33" s="99" t="inlineStr">
+        <is>
+          <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1" s="86">
+      <c r="B34" s="99" t="inlineStr">
+        <is>
+          <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="C16:F16"/>
@@ -3651,227 +3864,245 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:C24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" style="86" min="1" max="1"/>
+    <col width="30" customWidth="1" style="86" min="2" max="2"/>
+    <col width="88" customWidth="1" style="86" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="B1" s="38" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="86">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>見積の前提条件</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="96" t="inlineStr">
+      <c r="C1" s="107" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="107" t="n"/>
+      <c r="C2" s="107" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="86">
+      <c r="B3" s="82" t="inlineStr">
         <is>
           <t>■ 1. 本見積に含まれるもの</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr"/>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="B4" s="98" t="inlineStr">
+      <c r="C3" s="83" t="n"/>
+    </row>
+    <row r="4" ht="31" customHeight="1" s="86">
+      <c r="B4" s="108" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
       </c>
-      <c r="C4" s="99" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、確認問題、修了判定、修了証の発行、決済機能、受講者ポータル、運営管理画面の基本機能。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="98" t="inlineStr">
+    <row r="5" ht="34" customHeight="1" s="86">
+      <c r="B5" s="108" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
       </c>
-      <c r="C5" s="99" t="inlineStr">
-        <is>
-          <t>特別教育 学科教材 6科目。構成台本、スライド、図解、ナレーション、バーチャル講師映像、章末問題・修了確認テストの作成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="B6" s="98" t="inlineStr">
+      <c r="C5" s="90" t="inlineStr">
+        <is>
+          <t>特別教育 学科教材 6科目。構成台本、スライド、図解、ナレーション、章末問題・修了確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" s="86">
+      <c r="B6" s="108" t="inlineStr">
         <is>
           <t>修了証</t>
         </is>
       </c>
-      <c r="C6" s="99" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>修了証PDFの自動発行、再発行、受講者によるダウンロード。記載項目は受講者氏名、科目、法定学科時間、有効視聴時間、テスト得点、講師名、発行者、証明書番号。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="98" t="inlineStr">
+    <row r="7" ht="22" customHeight="1" s="86">
+      <c r="B7" s="108" t="inlineStr">
         <is>
           <t>サーバー環境の構築</t>
         </is>
       </c>
-      <c r="C7" s="99" t="inlineStr">
+      <c r="C7" s="90" t="inlineStr">
         <is>
           <t>本番運用に耐える構成で構築します。データベースは冗長化し、日次のバックアップを取得します。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="100" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="107" t="n"/>
+      <c r="C8" s="107" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="86">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>■ 2. 本見積に含まれないもの（別途）</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="B10" s="98" t="inlineStr">
+      <c r="C9" s="83" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1" s="86">
+      <c r="B10" s="108" t="inlineStr">
         <is>
           <t>受講中のランダム顔照合</t>
         </is>
       </c>
-      <c r="C10" s="99" t="inlineStr">
-        <is>
-          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。登録時の本人確認と受講開始時の顔照合は実装します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="B11" s="98" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。
+登録時の本人確認と受講開始時の顔照合は実装します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1" s="86">
+      <c r="B11" s="108" t="inlineStr">
         <is>
           <t>月額サービス</t>
         </is>
       </c>
-      <c r="C11" s="99" t="inlineStr">
-        <is>
-          <t>保守・運用サービス 60,000円／月、法令改正監視・通知サービス 20,000円／月。合計80,000円／月（税抜）。別途契約とします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="98" t="inlineStr">
+      <c r="C11" s="90" t="inlineStr">
+        <is>
+          <t>保守・運用サービス 60,000円／月、法令改正監視・通知サービス 20,000円／月。合計80,000円／月（税抜）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="86">
+      <c r="B12" s="108" t="inlineStr">
         <is>
           <t>サーバー利用料</t>
         </is>
       </c>
-      <c r="C12" s="99" t="inlineStr">
-        <is>
-          <t>貴社のご負担とします。月額20,000円程度（税抜）。貴社名義でのご契約を推奨します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="98" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>貴社のご負担とします。月額20,000円程度（税抜）。貴社名義でのご契約をお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="86">
+      <c r="B13" s="108" t="inlineStr">
         <is>
           <t>教材の改訂・追加</t>
         </is>
       </c>
-      <c r="C13" s="99" t="inlineStr">
+      <c r="C13" s="90" t="inlineStr">
         <is>
           <t>1科目300,000円（都度発注）。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="98" t="inlineStr">
+    <row r="14" ht="22" customHeight="1" s="86">
+      <c r="B14" s="108" t="inlineStr">
         <is>
           <t>教材の監修</t>
         </is>
       </c>
-      <c r="C14" s="99" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>内容の監修は貴社の社内有資格者が担われる前提です。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="96" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="107" t="n"/>
+      <c r="C15" s="107" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="86">
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>■ 3. 責任の分担</t>
         </is>
       </c>
-      <c r="C16" s="97" t="inlineStr"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="B17" s="98" t="inlineStr">
+      <c r="C16" s="83" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1" s="86">
+      <c r="B17" s="108" t="inlineStr">
         <is>
           <t>弊社が保証すること</t>
         </is>
       </c>
-      <c r="C17" s="99" t="inlineStr">
+      <c r="C17" s="90" t="inlineStr">
         <is>
           <t>教材が安全衛生特別教育規程の定める科目・範囲・時間を満たすこと（監修者名を明示）。受講記録を証明可能な形で保存・出力できること。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="B18" s="98" t="inlineStr">
+    <row r="18" ht="34" customHeight="1" s="86">
+      <c r="B18" s="108" t="inlineStr">
         <is>
           <t>弊社が保証しないこと</t>
         </is>
       </c>
-      <c r="C18" s="99" t="inlineStr">
+      <c r="C18" s="90" t="inlineStr">
         <is>
           <t>受講者の所属事業者が負う労働安全衛生法第59条第3項の実施義務が果たされたこと。労働災害が発生しないこと。行政機関が個別の事案において本教材を適法と判断すること。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="B19" s="98" t="inlineStr">
+    <row r="19" ht="34" customHeight="1" s="86">
+      <c r="B19" s="108" t="inlineStr">
         <is>
           <t>法令改正への対応</t>
         </is>
       </c>
-      <c r="C19" s="99" t="inlineStr">
+      <c r="C19" s="90" t="inlineStr">
         <is>
           <t>弊社は官報・通達を監視し、該当しうる改正を自動でメール通知します。その改正が教材のどこに影響するかの判断は、貴社の監修者が行うものとします。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="96" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="107" t="n"/>
+      <c r="C20" s="107" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="86">
+      <c r="B21" s="82" t="inlineStr">
         <is>
           <t>■ 4. 金額の前提</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="98" t="inlineStr">
+      <c r="C21" s="83" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="86">
+      <c r="B22" s="108" t="inlineStr">
         <is>
           <t>教材制作単価</t>
         </is>
       </c>
-      <c r="C22" s="99" t="inlineStr">
+      <c r="C22" s="90" t="inlineStr">
         <is>
           <t>300,000円／科目。貴社ご指定の単価です。改訂・追加時も同額を適用します。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="98" t="inlineStr">
+    <row r="23" ht="22" customHeight="1" s="86">
+      <c r="B23" s="108" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
-      <c r="C23" s="99" t="inlineStr">
+      <c r="C23" s="90" t="inlineStr">
         <is>
           <t>ご発注時に全額を一括でお支払いいただくことを前提とした金額です。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="98" t="inlineStr">
+    <row r="24" ht="22" customHeight="1" s="86">
+      <c r="B24" s="108" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
       </c>
-      <c r="C24" s="99" t="inlineStr">
+      <c r="C24" s="90" t="inlineStr">
         <is>
           <t>発行日より30日間。</t>
         </is>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17340" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17340" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_見積書" sheetId="1" state="visible" r:id="rId1"/>
@@ -334,7 +334,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -359,6 +359,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F5F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -433,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -683,19 +689,55 @@
     <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -707,46 +749,16 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -835,74 +847,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -919,6 +864,31 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <absoluteAnchor>
+    <pos x="7391880" y="1793879"/>
+    <ext cx="878040" cy="878040"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1213,22 +1183,22 @@
   <dimension ref="B2:F38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" style="86" min="1" max="1"/>
-    <col width="20" customWidth="1" style="86" min="2" max="3"/>
-    <col width="16" customWidth="1" style="86" min="4" max="5"/>
-    <col width="18" customWidth="1" style="86" min="6" max="6"/>
-    <col width="3" customWidth="1" style="86" min="7" max="7"/>
+    <col width="3" customWidth="1" style="89" min="1" max="1"/>
+    <col width="20" customWidth="1" style="89" min="2" max="3"/>
+    <col width="16" customWidth="1" style="89" min="4" max="5"/>
+    <col width="18" customWidth="1" style="89" min="6" max="6"/>
+    <col width="3" customWidth="1" style="89" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" s="86">
-      <c r="B2" s="95" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="89">
+      <c r="B2" s="97" t="inlineStr">
         <is>
           <t>御　見　積　書</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="86">
-      <c r="B4" s="97" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="89">
+      <c r="B4" s="93" t="inlineStr">
         <is>
           <t>見積番号</t>
         </is>
@@ -1239,8 +1209,8 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="86">
-      <c r="B5" s="97" t="inlineStr">
+    <row r="5" ht="16" customHeight="1" s="89">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
@@ -1251,8 +1221,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="86">
-      <c r="B6" s="97" t="inlineStr">
+    <row r="6" ht="16" customHeight="1" s="89">
+      <c r="B6" s="93" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
@@ -1263,98 +1233,98 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="25" customHeight="1" s="86">
-      <c r="B8" s="91" t="inlineStr">
+    <row r="8" ht="25" customHeight="1" s="89">
+      <c r="B8" s="99" t="inlineStr">
         <is>
           <t>株式会社聖建　御中</t>
         </is>
       </c>
-      <c r="E8" s="93" t="inlineStr">
+      <c r="E8" s="105" t="inlineStr">
         <is>
           <t>株式会社スペリオル</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="86">
-      <c r="B9" s="97" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="89">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>〒475-0805　愛知県半田市浜田町1丁目7番地</t>
         </is>
       </c>
-      <c r="E9" s="96" t="inlineStr">
+      <c r="E9" s="95" t="inlineStr">
         <is>
           <t>〒464-0075　名古屋市千種区内山3-18-10</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="86">
-      <c r="E10" s="96" t="inlineStr">
+    <row r="10" ht="16" customHeight="1" s="89">
+      <c r="E10" s="95" t="inlineStr">
         <is>
           <t>TEL 052-745-6607</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="86">
-      <c r="E11" s="96" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="89">
+      <c r="E11" s="95" t="inlineStr">
         <is>
           <t>登録番号 T9180001048541</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" s="86">
-      <c r="E12" s="85" t="inlineStr">
+    <row r="12" ht="16" customHeight="1" s="89">
+      <c r="E12" s="102" t="inlineStr">
         <is>
           <t>担当　藤原</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1" s="86">
-      <c r="B14" s="98" t="inlineStr">
+    <row r="14" ht="17" customHeight="1" s="89">
+      <c r="B14" s="96" t="inlineStr">
         <is>
           <t>下記のとおりお見積り申し上げます。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1" s="86">
+    <row r="16" ht="32" customHeight="1" s="89">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="C16" s="101" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t>建設業 特別教育 eラーニング配信システム 構築 および 教材制作（6科目）一式</t>
         </is>
       </c>
-      <c r="D16" s="88" t="n"/>
-      <c r="E16" s="88" t="n"/>
-      <c r="F16" s="89" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" s="86">
+      <c r="D16" s="91" t="n"/>
+      <c r="E16" s="91" t="n"/>
+      <c r="F16" s="92" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="89">
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>御見積金額</t>
         </is>
       </c>
-      <c r="C17" s="109">
+      <c r="C17" s="111">
         <f>'03_見積明細'!F28</f>
         <v/>
       </c>
-      <c r="D17" s="88" t="n"/>
-      <c r="E17" s="88" t="n"/>
-      <c r="F17" s="89" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" s="86">
+      <c r="D17" s="91" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="92" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="89">
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="94">
+      <c r="C18" s="106">
         <f>"消費税 ¥"&amp;TEXT('03_見積明細'!F29,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT('03_見積明細'!F30,"#,##0")</f>
         <v/>
       </c>
-      <c r="D18" s="88" t="n"/>
-      <c r="E18" s="88" t="n"/>
-      <c r="F18" s="89" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1" s="86">
+      <c r="D18" s="91" t="n"/>
+      <c r="E18" s="91" t="n"/>
+      <c r="F18" s="92" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="89">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>納期</t>
@@ -1365,11 +1335,11 @@
           <t>システム：ご発注後 約4か月　／　教材：第1次3科目 約4か月、第2次3科目 約7か月</t>
         </is>
       </c>
-      <c r="D20" s="88" t="n"/>
-      <c r="E20" s="88" t="n"/>
-      <c r="F20" s="89" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="86">
+      <c r="D20" s="91" t="n"/>
+      <c r="E20" s="91" t="n"/>
+      <c r="F20" s="92" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="89">
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>納入場所</t>
@@ -1380,11 +1350,11 @@
           <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
-      <c r="D21" s="88" t="n"/>
-      <c r="E21" s="88" t="n"/>
-      <c r="F21" s="89" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" s="86">
+      <c r="D21" s="91" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="92" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="89">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>検収条件</t>
@@ -1395,11 +1365,11 @@
           <t>納品後14日以内に貴社にて検収。期間内にご連絡なき場合は検収完了とみなします。</t>
         </is>
       </c>
-      <c r="D22" s="88" t="n"/>
-      <c r="E22" s="88" t="n"/>
-      <c r="F22" s="89" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" s="86">
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="92" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="89">
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>支払条件</t>
@@ -1410,84 +1380,84 @@
           <t>ご発注時に全額を一括でお支払いください。</t>
         </is>
       </c>
-      <c r="D23" s="88" t="n"/>
-      <c r="E23" s="88" t="n"/>
-      <c r="F23" s="89" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1" s="86">
+      <c r="D23" s="91" t="n"/>
+      <c r="E23" s="91" t="n"/>
+      <c r="F23" s="92" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1" s="89">
       <c r="B25" s="7" t="inlineStr">
         <is>
           <t>内訳</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1" s="86">
-      <c r="B26" s="92" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="89">
+      <c r="B26" s="104" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="C26" s="104" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D26" s="89" t="n"/>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="D26" s="92" t="n"/>
+      <c r="E26" s="104" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="F26" s="104" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="86">
+    <row r="27" ht="17" customHeight="1" s="89">
       <c r="B27" s="9" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
       </c>
-      <c r="C27" s="100" t="inlineStr">
+      <c r="C27" s="101" t="inlineStr">
         <is>
           <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
         </is>
       </c>
-      <c r="D27" s="89" t="n"/>
+      <c r="D27" s="92" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
       </c>
-      <c r="F27" s="110">
+      <c r="F27" s="112">
         <f>'03_見積明細'!F21</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="86">
+    <row r="28" ht="17" customHeight="1" s="89">
       <c r="B28" s="9" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
       </c>
-      <c r="C28" s="100" t="inlineStr">
+      <c r="C28" s="101" t="inlineStr">
         <is>
           <t>特別教育 学科教材 6科目</t>
         </is>
       </c>
-      <c r="D28" s="89" t="n"/>
-      <c r="E28" s="111">
+      <c r="D28" s="92" t="n"/>
+      <c r="E28" s="113">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="F28" s="110">
+      <c r="F28" s="112">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1" s="86">
+    <row r="29" ht="17" customHeight="1" s="89">
       <c r="B29" s="14" t="inlineStr">
         <is>
           <t>小計</t>
@@ -1500,12 +1470,12 @@
       </c>
       <c r="D29" s="16" t="n"/>
       <c r="E29" s="16" t="n"/>
-      <c r="F29" s="112">
+      <c r="F29" s="114">
         <f>'03_見積明細'!F26</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1" s="86">
+    <row r="30" ht="17" customHeight="1" s="89">
       <c r="B30" s="9" t="inlineStr">
         <is>
           <t>値引</t>
@@ -1518,12 +1488,12 @@
       </c>
       <c r="D30" s="19" t="n"/>
       <c r="E30" s="19" t="n"/>
-      <c r="F30" s="113">
+      <c r="F30" s="115">
         <f>'03_見積明細'!F27</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="17" customHeight="1" s="86">
+    <row r="31" ht="17" customHeight="1" s="89">
       <c r="B31" s="9" t="inlineStr">
         <is>
           <t>差引小計</t>
@@ -1536,12 +1506,12 @@
       </c>
       <c r="D31" s="19" t="n"/>
       <c r="E31" s="19" t="n"/>
-      <c r="F31" s="114">
+      <c r="F31" s="116">
         <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1" s="86">
+    <row r="32" ht="17" customHeight="1" s="89">
       <c r="B32" s="9" t="inlineStr">
         <is>
           <t>消費税</t>
@@ -1550,12 +1520,12 @@
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="n"/>
-      <c r="F32" s="114">
+      <c r="F32" s="116">
         <f>'03_見積明細'!F29</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1" s="86">
+    <row r="33" ht="22" customHeight="1" s="89">
       <c r="B33" s="23" t="inlineStr">
         <is>
           <t>合計</t>
@@ -1568,34 +1538,34 @@
       </c>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
-      <c r="F33" s="115">
+      <c r="F33" s="117">
         <f>'03_見積明細'!F30</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1" s="86">
+    <row r="35" ht="17" customHeight="1" s="89">
       <c r="B35" s="26" t="inlineStr">
         <is>
           <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1" s="86">
-      <c r="B36" s="99" t="inlineStr">
+    <row r="36" ht="17" customHeight="1" s="89">
+      <c r="B36" s="88" t="inlineStr">
         <is>
           <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1" s="86">
-      <c r="B37" s="99" t="inlineStr">
+    <row r="37" ht="17" customHeight="1" s="89">
+      <c r="B37" s="88" t="inlineStr">
         <is>
           <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1" s="86">
-      <c r="B38" s="99" t="inlineStr">
+    <row r="38" ht="17" customHeight="1" s="89">
+      <c r="B38" s="88" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
         </is>
@@ -1628,7 +1598,8 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1641,61 +1612,61 @@
   <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="6" customWidth="1" style="86" min="1" max="1"/>
-    <col width="40" customWidth="1" style="86" min="2" max="2"/>
-    <col width="16" customWidth="1" style="86" min="3" max="3"/>
-    <col width="14" customWidth="1" style="86" min="4" max="4"/>
-    <col width="56" customWidth="1" style="86" min="5" max="5"/>
+    <col width="6" customWidth="1" style="89" min="1" max="1"/>
+    <col width="40" customWidth="1" style="89" min="2" max="2"/>
+    <col width="16" customWidth="1" style="89" min="3" max="3"/>
+    <col width="14" customWidth="1" style="89" min="4" max="4"/>
+    <col width="56" customWidth="1" style="89" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="86">
+    <row r="1" ht="24" customHeight="1" s="89">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>前回お見積りからの増減内訳</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="86">
+    <row r="2" ht="17" customHeight="1" s="89">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>2026年9月8日付 SP-2026-0001（税抜 8,000,000円）から、今回のお見積りに至るまでの内訳です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="86">
-      <c r="A4" s="92" t="n"/>
-      <c r="B4" s="92" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="89">
+      <c r="A4" s="104" t="n"/>
+      <c r="B4" s="104" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
+      <c r="C4" s="104" t="inlineStr">
         <is>
           <t>増減</t>
         </is>
       </c>
-      <c r="D4" s="92" t="inlineStr">
+      <c r="D4" s="104" t="inlineStr">
         <is>
           <t>人日</t>
         </is>
       </c>
-      <c r="E4" s="92" t="inlineStr">
+      <c r="E4" s="104" t="inlineStr">
         <is>
           <t>理由・内容</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" s="86">
+    <row r="5" ht="17" customHeight="1" s="89">
       <c r="A5" s="16" t="n"/>
       <c r="B5" s="29" t="inlineStr">
         <is>
           <t>前回お見積り（2026年9月8日）</t>
         </is>
       </c>
-      <c r="C5" s="112" t="n">
+      <c r="C5" s="114" t="n">
         <v>8000000</v>
       </c>
-      <c r="D5" s="116" t="n">
+      <c r="D5" s="118" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1704,7 +1675,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" s="86">
+    <row r="6" ht="34" customHeight="1" s="89">
       <c r="A6" s="31" t="inlineStr">
         <is>
           <t>①</t>
@@ -1715,17 +1686,17 @@
           <t>教材を10科目から6科目へ</t>
         </is>
       </c>
-      <c r="C6" s="117" t="n">
+      <c r="C6" s="119" t="n">
         <v>-1200000</v>
       </c>
-      <c r="D6" s="118" t="n"/>
+      <c r="D6" s="120" t="n"/>
       <c r="E6" s="35" t="inlineStr">
         <is>
           <t>低圧電気、第2種酸欠、高所作業車、玉掛けの4科目を第2次発注へ。1科目300,000円×4科目</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" s="86">
+    <row r="7" ht="34" customHeight="1" s="89">
       <c r="A7" s="36" t="inlineStr">
         <is>
           <t>②</t>
@@ -1736,10 +1707,10 @@
           <t>決済機能（ゼウス連携）の追加</t>
         </is>
       </c>
-      <c r="C7" s="113" t="n">
+      <c r="C7" s="115" t="n">
         <v>500000</v>
       </c>
-      <c r="D7" s="119" t="n">
+      <c r="D7" s="121" t="n">
         <v>10</v>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -1748,7 +1719,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" s="86">
+    <row r="8" ht="34" customHeight="1" s="89">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>③</t>
@@ -1759,10 +1730,10 @@
           <t>受講中のランダム顔照合を除外</t>
         </is>
       </c>
-      <c r="C8" s="117" t="n">
+      <c r="C8" s="119" t="n">
         <v>-350000</v>
       </c>
-      <c r="D8" s="120" t="n">
+      <c r="D8" s="122" t="n">
         <v>-7</v>
       </c>
       <c r="E8" s="35" t="inlineStr">
@@ -1771,7 +1742,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" s="86">
+    <row r="9" ht="34" customHeight="1" s="89">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>④</t>
@@ -1782,28 +1753,28 @@
           <t>全額一括前払いによる調整</t>
         </is>
       </c>
-      <c r="C9" s="117" t="n">
+      <c r="C9" s="119" t="n">
         <v>-350000</v>
       </c>
-      <c r="D9" s="118" t="n"/>
+      <c r="D9" s="120" t="n"/>
       <c r="E9" s="35" t="inlineStr">
         <is>
           <t>ご発注時に全額をお支払いいただく条件に対する調整。分割回収に比べ資金負担と与信リスクが下がるため</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1" s="86">
+    <row r="10" ht="26" customHeight="1" s="89">
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="39" t="inlineStr">
         <is>
           <t>今回のお見積り（税抜）</t>
         </is>
       </c>
-      <c r="C10" s="121">
+      <c r="C10" s="123">
         <f>C5+SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="124">
         <f>'03_見積明細'!D21</f>
         <v/>
       </c>
@@ -1813,25 +1784,25 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="86">
-      <c r="B11" s="97" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="89">
+      <c r="B11" s="93" t="inlineStr">
         <is>
           <t>（検算）見積明細の小計＋調整額</t>
         </is>
       </c>
-      <c r="C11" s="123">
+      <c r="C11" s="125">
         <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="86">
+    <row r="13" ht="20" customHeight="1" s="89">
       <c r="B13" s="43" t="inlineStr">
         <is>
           <t>増減の内訳（金額の動き）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1" s="86">
+    <row r="14" ht="17" customHeight="1" s="89">
       <c r="B14" s="44" t="inlineStr">
         <is>
           <t>減額の要因</t>
@@ -1841,8 +1812,8 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="86">
-      <c r="B15" s="100" t="inlineStr">
+    <row r="15" ht="17" customHeight="1" s="89">
+      <c r="B15" s="101" t="inlineStr">
         <is>
           <t>教材 4科目の削減</t>
         </is>
@@ -1855,8 +1826,8 @@
       <c r="D15" s="19" t="n"/>
       <c r="E15" s="19" t="n"/>
     </row>
-    <row r="16" ht="17" customHeight="1" s="86">
-      <c r="B16" s="100" t="inlineStr">
+    <row r="16" ht="17" customHeight="1" s="89">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>受講中ランダム照合の除外</t>
         </is>
@@ -1869,8 +1840,8 @@
       <c r="D16" s="19" t="n"/>
       <c r="E16" s="19" t="n"/>
     </row>
-    <row r="17" ht="17" customHeight="1" s="86">
-      <c r="B17" s="100" t="inlineStr">
+    <row r="17" ht="17" customHeight="1" s="89">
+      <c r="B17" s="101" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
         </is>
@@ -1883,7 +1854,7 @@
       <c r="D17" s="19" t="n"/>
       <c r="E17" s="19" t="n"/>
     </row>
-    <row r="18" ht="17" customHeight="1" s="86">
+    <row r="18" ht="17" customHeight="1" s="89">
       <c r="B18" s="46" t="inlineStr">
         <is>
           <t>小計</t>
@@ -1897,7 +1868,7 @@
       <c r="D18" s="19" t="n"/>
       <c r="E18" s="19" t="n"/>
     </row>
-    <row r="20" ht="17" customHeight="1" s="86">
+    <row r="20" ht="17" customHeight="1" s="89">
       <c r="B20" s="48" t="inlineStr">
         <is>
           <t>増額の要因</t>
@@ -1907,8 +1878,8 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
     </row>
-    <row r="21" ht="17" customHeight="1" s="86">
-      <c r="B21" s="100" t="inlineStr">
+    <row r="21" ht="17" customHeight="1" s="89">
+      <c r="B21" s="101" t="inlineStr">
         <is>
           <t>決済機能（ゼウス連携）の追加</t>
         </is>
@@ -1921,7 +1892,7 @@
       <c r="D21" s="19" t="n"/>
       <c r="E21" s="19" t="n"/>
     </row>
-    <row r="22" ht="17" customHeight="1" s="86">
+    <row r="22" ht="17" customHeight="1" s="89">
       <c r="B22" s="46" t="inlineStr">
         <is>
           <t>小計</t>
@@ -1935,7 +1906,7 @@
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="19" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="86">
+    <row r="24" ht="19" customHeight="1" s="89">
       <c r="B24" s="51" t="inlineStr">
         <is>
           <t>差引</t>
@@ -1953,128 +1924,128 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="17" customHeight="1" s="86">
+    <row r="26" ht="17" customHeight="1" s="89">
       <c r="B26" s="53" t="inlineStr">
         <is>
           <t>■ このシートは社内資料です（先方には提出しません）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="86">
+    <row r="27" ht="17" customHeight="1" s="89">
       <c r="B27" s="54" t="inlineStr">
         <is>
           <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="86">
+    <row r="28" ht="17" customHeight="1" s="89">
       <c r="B28" s="54" t="inlineStr">
         <is>
           <t>先方向けには「前回からの変更は受講中のランダム顔照合を外すことだけ」と説明し、</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1" s="86">
+    <row r="29" ht="17" customHeight="1" s="89">
       <c r="B29" s="54" t="inlineStr">
         <is>
           <t>下の④は見積書・注文書の上では「貴社特別値引き（特別値引き）」と表示しています。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1" s="86">
+    <row r="30" ht="17" customHeight="1" s="89">
       <c r="B30" s="54" t="n"/>
     </row>
-    <row r="31" ht="17" customHeight="1" s="86">
+    <row r="31" ht="17" customHeight="1" s="89">
       <c r="B31" s="55" t="inlineStr">
         <is>
           <t>■ この表の使い方（社内の根拠整理）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1" s="86">
+    <row r="32" ht="17" customHeight="1" s="89">
       <c r="B32" s="54" t="inlineStr">
         <is>
           <t>単純な値引きではなく、次の3つの対価として金額が下がっていることを社内で説明できます。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1" s="86">
+    <row r="33" ht="17" customHeight="1" s="89">
       <c r="B33" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　① 納品する教材が4科目減ること（成果物の減少）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1" s="86">
+    <row r="34" ht="17" customHeight="1" s="89">
       <c r="B34" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　② 受講中のランダム照合を実装しないこと（機能の減少）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1" s="86">
+    <row r="35" ht="17" customHeight="1" s="89">
       <c r="B35" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　③ 全額を前払いいただくこと（支払条件の対価）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1" s="86">
+    <row r="36" ht="17" customHeight="1" s="89">
       <c r="B36" s="54" t="n"/>
     </row>
-    <row r="37" ht="17" customHeight="1" s="86">
+    <row r="37" ht="17" customHeight="1" s="89">
       <c r="B37" s="54" t="inlineStr">
         <is>
           <t>一方で、決済機能（ゼウス連携）は新しいご要望のため増額しています。</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1" s="86">
+    <row r="38" ht="17" customHeight="1" s="89">
       <c r="B38" s="56" t="inlineStr">
         <is>
           <t>減る理由と増える理由の両方を示すことで、価格の根拠が明確になります。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="17" customHeight="1" s="86">
+    <row r="39" ht="17" customHeight="1" s="89">
       <c r="B39" s="54" t="n"/>
     </row>
-    <row r="40" ht="17" customHeight="1" s="86">
+    <row r="40" ht="17" customHeight="1" s="89">
       <c r="B40" s="55" t="inlineStr">
         <is>
           <t>■ 月額費用の変更</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1" s="86">
+    <row r="41" ht="17" customHeight="1" s="89">
       <c r="B41" s="54" t="inlineStr">
         <is>
           <t>保守・運用サービス　80,000円 → 60,000円（▲20,000円）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1" s="86">
+    <row r="42" ht="17" customHeight="1" s="89">
       <c r="B42" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　受講中のランダム照合を実装しないため、照合結果の目視確認という運用作業がなくなります。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1" s="86">
+    <row r="43" ht="17" customHeight="1" s="89">
       <c r="B43" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">　運用工数が実際に減るため、その分を月額に反映しています。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="17" customHeight="1" s="86">
+    <row r="44" ht="17" customHeight="1" s="89">
       <c r="B44" s="54" t="inlineStr">
         <is>
           <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1" s="86">
+    <row r="45" ht="17" customHeight="1" s="89">
       <c r="B45" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　　　　　　合計 80,000円／月（サーバー費を除く・税抜）</t>
@@ -2097,36 +2068,36 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" style="86" min="1" max="1"/>
-    <col width="28" customWidth="1" style="86" min="2" max="2"/>
-    <col width="54" customWidth="1" style="86" min="3" max="3"/>
-    <col width="9" customWidth="1" style="86" min="4" max="4"/>
-    <col width="12" customWidth="1" style="86" min="5" max="5"/>
-    <col width="14" customWidth="1" style="86" min="6" max="6"/>
+    <col width="12" customWidth="1" style="89" min="1" max="1"/>
+    <col width="28" customWidth="1" style="89" min="2" max="2"/>
+    <col width="54" customWidth="1" style="89" min="3" max="3"/>
+    <col width="9" customWidth="1" style="89" min="4" max="4"/>
+    <col width="12" customWidth="1" style="89" min="5" max="5"/>
+    <col width="14" customWidth="1" style="89" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="86">
+    <row r="1" ht="24" customHeight="1" s="89">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>見積明細</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="86">
+    <row r="2" ht="17" customHeight="1" s="89">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>黄色のセルが編集箇所です。人日単価と各項目の人日を変えると、見積書・増減内訳・注文書まで自動で再計算されます。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" s="86">
-      <c r="A4" s="102" t="inlineStr">
+    <row r="4" ht="17" customHeight="1" s="89">
+      <c r="A4" s="107" t="inlineStr">
         <is>
           <t>人日単価</t>
         </is>
       </c>
-      <c r="B4" s="89" t="n"/>
-      <c r="C4" s="124" t="n">
+      <c r="B4" s="92" t="n"/>
+      <c r="C4" s="126" t="n">
         <v>50000</v>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -2135,51 +2106,51 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" s="86">
-      <c r="A6" s="92" t="inlineStr">
+    <row r="6" ht="22" customHeight="1" s="89">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B6" s="92" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="104" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D6" s="92" t="inlineStr">
+      <c r="D6" s="104" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E6" s="92" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="F6" s="92" t="inlineStr">
+      <c r="F6" s="104" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1" s="86">
-      <c r="A7" s="103" t="inlineStr">
+    <row r="7" ht="17" customHeight="1" s="89">
+      <c r="A7" s="108" t="inlineStr">
         <is>
           <t>1. システム開発</t>
         </is>
       </c>
-      <c r="B7" s="88" t="n"/>
-      <c r="C7" s="88" t="n"/>
-      <c r="D7" s="88" t="n"/>
-      <c r="E7" s="88" t="n"/>
-      <c r="F7" s="89" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="86">
+      <c r="B7" s="91" t="n"/>
+      <c r="C7" s="91" t="n"/>
+      <c r="D7" s="91" t="n"/>
+      <c r="E7" s="91" t="n"/>
+      <c r="F7" s="92" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="89">
       <c r="A8" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2195,19 +2166,19 @@
           <t>業務フローの確定、データモデル設計、API設計、画面設計、利用規約・特定商取引法表記・個人情報の取扱い方針の整備支援</t>
         </is>
       </c>
-      <c r="D8" s="125" t="n">
+      <c r="D8" s="127" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="110">
+      <c r="E8" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="110">
+      <c r="F8" s="112">
         <f>D8*E8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="86">
+    <row r="9" ht="30" customHeight="1" s="89">
       <c r="A9" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2223,19 +2194,19 @@
           <t>VPC、EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch の構築とCI/CD</t>
         </is>
       </c>
-      <c r="D9" s="125" t="n">
+      <c r="D9" s="127" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="110">
+      <c r="E9" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F9" s="110">
+      <c r="F9" s="112">
         <f>D9*E9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="86">
+    <row r="10" ht="30" customHeight="1" s="89">
       <c r="A10" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2251,19 +2222,19 @@
           <t>HLS変換（FFmpeg）、短寿命の署名付きマニフェスト配信、章単位の受講制御、MP4直リンクの排除</t>
         </is>
       </c>
-      <c r="D10" s="125" t="n">
+      <c r="D10" s="127" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="110">
+      <c r="E10" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="110">
+      <c r="F10" s="112">
         <f>D10*E10</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="86">
+    <row r="11" ht="30" customHeight="1" s="89">
       <c r="A11" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2279,19 +2250,19 @@
           <t>heartbeatの受信と検証、未視聴位置へのシーク制限、倍速検知、可視状態の判定、サーバー側での検証済み秒数の集計、異常検知</t>
         </is>
       </c>
-      <c r="D11" s="125" t="n">
+      <c r="D11" s="127" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="110">
+      <c r="E11" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="110">
+      <c r="F11" s="112">
         <f>D11*E11</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="86">
+    <row r="12" ht="30" customHeight="1" s="89">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2307,19 +2278,19 @@
           <t>その場撮影UI（getUserMedia）、ライブネス判定、本人確認書類との突合、顔の1:1照合、運営の審査画面</t>
         </is>
       </c>
-      <c r="D12" s="125" t="n">
+      <c r="D12" s="127" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="110">
+      <c r="E12" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="110">
+      <c r="F12" s="112">
         <f>D12*E12</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="86">
+    <row r="13" ht="30" customHeight="1" s="89">
       <c r="A13" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2335,19 +2306,19 @@
           <t>QRコードとワンタイムURLによる撮影工程の引き継ぎ</t>
         </is>
       </c>
-      <c r="D13" s="125" t="n">
+      <c r="D13" s="127" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="110">
+      <c r="E13" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="110">
+      <c r="F13" s="112">
         <f>D13*E13</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="86">
+    <row r="14" ht="30" customHeight="1" s="89">
       <c r="A14" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2363,19 +2334,19 @@
           <t>各章の再生開始時に1:1照合を実施。受講中のランダム照合は今回の範囲外とします</t>
         </is>
       </c>
-      <c r="D14" s="125" t="n">
+      <c r="D14" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="110">
+      <c r="E14" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="110">
+      <c r="F14" s="112">
         <f>D14*E14</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="86">
+    <row r="15" ht="30" customHeight="1" s="89">
       <c r="A15" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2391,19 +2362,19 @@
           <t>章末問題、修了確認テスト、出題のランダム化、不合格後の再受講制御</t>
         </is>
       </c>
-      <c r="D15" s="125" t="n">
+      <c r="D15" s="127" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="110">
+      <c r="E15" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="110">
+      <c r="F15" s="112">
         <f>D15*E15</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="86">
+    <row r="16" ht="30" customHeight="1" s="89">
       <c r="A16" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2419,19 +2390,19 @@
           <t>サーバー側での修了条件の再検証、修了記録の作成、修了証PDFの発行・再発行・ダウンロード</t>
         </is>
       </c>
-      <c r="D16" s="125" t="n">
+      <c r="D16" s="127" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="110">
+      <c r="E16" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="110">
+      <c r="F16" s="112">
         <f>D16*E16</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="86">
+    <row r="17" ht="30" customHeight="1" s="89">
       <c r="A17" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2447,19 +2418,19 @@
           <t>株式会社ゼウスのデータ転送（API）型による決済組み込み。申込から入金確認、受講開始までの自動化。領収書の発行</t>
         </is>
       </c>
-      <c r="D17" s="125" t="n">
+      <c r="D17" s="127" t="n">
         <v>10</v>
       </c>
-      <c r="E17" s="110">
+      <c r="E17" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F17" s="110">
+      <c r="F17" s="112">
         <f>D17*E17</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="86">
+    <row r="18" ht="30" customHeight="1" s="89">
       <c r="A18" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2475,19 +2446,19 @@
           <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応</t>
         </is>
       </c>
-      <c r="D18" s="125" t="n">
+      <c r="D18" s="127" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="110">
+      <c r="E18" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="110">
+      <c r="F18" s="112">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="86">
+    <row r="19" ht="30" customHeight="1" s="89">
       <c r="A19" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2503,19 +2474,19 @@
           <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理</t>
         </is>
       </c>
-      <c r="D19" s="125" t="n">
+      <c r="D19" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="110">
+      <c r="E19" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="110">
+      <c r="F19" s="112">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="86">
+    <row r="20" ht="30" customHeight="1" s="89">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2531,19 +2502,19 @@
           <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成</t>
         </is>
       </c>
-      <c r="D20" s="125" t="n">
+      <c r="D20" s="127" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="110">
+      <c r="E20" s="112">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="110">
+      <c r="F20" s="112">
         <f>D20*E20</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="86">
+    <row r="21" ht="17" customHeight="1" s="89">
       <c r="A21" s="16" t="n"/>
       <c r="B21" s="29" t="inlineStr">
         <is>
@@ -2551,29 +2522,29 @@
         </is>
       </c>
       <c r="C21" s="16" t="n"/>
-      <c r="D21" s="126">
+      <c r="D21" s="128">
         <f>SUM(D8:D20)</f>
         <v/>
       </c>
       <c r="E21" s="16" t="n"/>
-      <c r="F21" s="112">
+      <c r="F21" s="114">
         <f>SUM(F8:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1" s="86">
-      <c r="A23" s="103" t="inlineStr">
+    <row r="23" ht="17" customHeight="1" s="89">
+      <c r="A23" s="108" t="inlineStr">
         <is>
           <t>2. eラーニング教材の制作</t>
         </is>
       </c>
-      <c r="B23" s="88" t="n"/>
-      <c r="C23" s="88" t="n"/>
-      <c r="D23" s="88" t="n"/>
-      <c r="E23" s="88" t="n"/>
-      <c r="F23" s="89" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1" s="86">
+      <c r="B23" s="91" t="n"/>
+      <c r="C23" s="91" t="n"/>
+      <c r="D23" s="91" t="n"/>
+      <c r="E23" s="91" t="n"/>
+      <c r="F23" s="92" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="89">
       <c r="A24" s="59" t="inlineStr">
         <is>
           <t>教材</t>
@@ -2588,20 +2559,20 @@
         <f>"6科目・学科"&amp;TEXT('04_教材科目'!$D$17,"0.0")&amp;"時間分。構成台本の書き起こし、スライド、図解、ナレーション、バーチャル講師映像、章末問題・修了確認テストの作成"</f>
         <v/>
       </c>
-      <c r="D24" s="127">
+      <c r="D24" s="129">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="E24" s="128">
+      <c r="E24" s="130">
         <f>'04_教材科目'!$D$4</f>
         <v/>
       </c>
-      <c r="F24" s="110">
+      <c r="F24" s="112">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1" s="86">
+    <row r="26" ht="19" customHeight="1" s="89">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="51" t="inlineStr">
         <is>
@@ -2609,17 +2580,17 @@
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="122">
+      <c r="D26" s="124">
         <f>D21</f>
         <v/>
       </c>
       <c r="E26" s="5" t="n"/>
-      <c r="F26" s="115">
+      <c r="F26" s="117">
         <f>F21+F24</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="86">
+    <row r="27" ht="17" customHeight="1" s="89">
       <c r="B27" s="64" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
@@ -2632,11 +2603,11 @@
       </c>
       <c r="D27" s="19" t="n"/>
       <c r="E27" s="19" t="n"/>
-      <c r="F27" s="124" t="n">
+      <c r="F27" s="126" t="n">
         <v>-350000</v>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="86">
+    <row r="28" ht="17" customHeight="1" s="89">
       <c r="B28" s="65" t="inlineStr">
         <is>
           <t>差引 小計（税抜）</t>
@@ -2645,12 +2616,12 @@
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="19" t="n"/>
-      <c r="F28" s="114">
+      <c r="F28" s="116">
         <f>F26+F27</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1" s="86">
+    <row r="29" ht="17" customHeight="1" s="89">
       <c r="B29" s="65" t="inlineStr">
         <is>
           <t>消費税</t>
@@ -2665,12 +2636,12 @@
         <v>0.1</v>
       </c>
       <c r="E29" s="19" t="n"/>
-      <c r="F29" s="114">
+      <c r="F29" s="116">
         <f>ROUND(F28*D29,0)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1" s="86">
+    <row r="30" ht="24" customHeight="1" s="89">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="39" t="inlineStr">
         <is>
@@ -2680,85 +2651,85 @@
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
-      <c r="F30" s="121">
+      <c r="F30" s="123">
         <f>F28+F29</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1" s="86">
+    <row r="32" ht="17" customHeight="1" s="89">
       <c r="A32" s="55" t="inlineStr">
         <is>
           <t>■ 今回の範囲から外したもの（第2次発注のご相談）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1" s="86">
+    <row r="33" ht="17" customHeight="1" s="89">
       <c r="A33" s="54" t="inlineStr">
         <is>
           <t>・受講中のランダム顔照合（受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1" s="86">
+    <row r="34" ht="17" customHeight="1" s="89">
       <c r="A34" s="54" t="inlineStr">
         <is>
           <t>・企業管理ポータル（従業員の一括申込、進捗確認、修了者一覧のCSV出力）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1" s="86">
+    <row r="35" ht="17" customHeight="1" s="89">
       <c r="A35" s="54" t="inlineStr">
         <is>
           <t>・運営管理画面の拡張（監査レポート出力、組織管理、売上・入金管理）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1" s="86">
+    <row r="36" ht="17" customHeight="1" s="89">
       <c r="A36" s="54" t="inlineStr">
         <is>
           <t>・受講画面からの質疑応答機能（当面はメールで対応）</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1" s="86">
+    <row r="37" ht="17" customHeight="1" s="89">
       <c r="A37" s="54" t="inlineStr">
         <is>
           <t>・修了証の真正性検証ページ（QRコード）</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1" s="86">
+    <row r="38" ht="17" customHeight="1" s="89">
       <c r="A38" s="54" t="inlineStr">
         <is>
           <t>・教材 4科目（低圧電気、第2種酸欠、高所作業車、玉掛け）</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="17" customHeight="1" s="86">
+    <row r="39" ht="17" customHeight="1" s="89">
       <c r="A39" s="54" t="n"/>
     </row>
-    <row r="40" ht="17" customHeight="1" s="86">
+    <row r="40" ht="17" customHeight="1" s="89">
       <c r="A40" s="55" t="inlineStr">
         <is>
           <t>■ 本見積に含まれないもの（別途）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1" s="86">
+    <row r="41" ht="17" customHeight="1" s="89">
       <c r="A41" s="54" t="inlineStr">
         <is>
           <t>・月額の保守・運用サービスおよび法令改正監視・通知サービス（シート05）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1" s="86">
+    <row r="42" ht="17" customHeight="1" s="89">
       <c r="A42" s="54" t="inlineStr">
         <is>
           <t>・AWSの利用料（聖建様のご負担）、株式会社ゼウスとのご契約（初期費用無料・月額3,000円・決済手数料）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1" s="86">
+    <row r="43" ht="17" customHeight="1" s="89">
       <c r="A43" s="54" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂（1科目300,000円・都度発注）</t>
@@ -2786,37 +2757,37 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="9" customWidth="1" style="86" min="1" max="1"/>
-    <col width="7" customWidth="1" style="86" min="2" max="2"/>
-    <col width="32" customWidth="1" style="86" min="3" max="3"/>
-    <col width="8" customWidth="1" style="86" min="4" max="4"/>
-    <col width="38" customWidth="1" style="86" min="5" max="5"/>
-    <col width="14" customWidth="1" style="86" min="6" max="6"/>
+    <col width="9" customWidth="1" style="89" min="1" max="1"/>
+    <col width="7" customWidth="1" style="89" min="2" max="2"/>
+    <col width="32" customWidth="1" style="89" min="3" max="3"/>
+    <col width="8" customWidth="1" style="89" min="4" max="4"/>
+    <col width="38" customWidth="1" style="89" min="5" max="5"/>
+    <col width="14" customWidth="1" style="89" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="86">
+    <row r="1" ht="24" customHeight="1" s="89">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>eラーニング教材 制作科目一覧（6科目）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="86">
+    <row r="2" ht="17" customHeight="1" s="89">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>A列に 1 を入れた科目が制作対象になります。10科目から6科目へ絞り込んだ状態です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" s="86">
+    <row r="4" ht="17" customHeight="1" s="89">
       <c r="A4" s="5" t="n"/>
-      <c r="B4" s="102" t="inlineStr">
+      <c r="B4" s="107" t="inlineStr">
         <is>
           <t>制作単価（1科目あたり）</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="124" t="n">
+      <c r="D4" s="126" t="n">
         <v>300000</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
@@ -2826,42 +2797,42 @@
       </c>
       <c r="F4" s="5" t="n"/>
     </row>
-    <row r="6" ht="32" customHeight="1" s="86">
-      <c r="A6" s="92" t="inlineStr">
+    <row r="6" ht="32" customHeight="1" s="89">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>制作
 (1で選択)</t>
         </is>
       </c>
-      <c r="B6" s="92" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>優先
 順位</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="104" t="inlineStr">
         <is>
           <t>特別教育の名称</t>
         </is>
       </c>
-      <c r="D6" s="92" t="inlineStr">
+      <c r="D6" s="104" t="inlineStr">
         <is>
           <t>学科
 (時間)</t>
         </is>
       </c>
-      <c r="E6" s="92" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr">
         <is>
           <t>選定・除外の理由</t>
         </is>
       </c>
-      <c r="F6" s="92" t="inlineStr">
+      <c r="F6" s="104" t="inlineStr">
         <is>
           <t>制作費</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1" s="86">
+    <row r="7" ht="26" customHeight="1" s="89">
       <c r="A7" s="67" t="n">
         <v>1</v>
       </c>
@@ -2873,7 +2844,7 @@
           <t>フルハーネス型墜落制止用器具</t>
         </is>
       </c>
-      <c r="D7" s="129" t="n">
+      <c r="D7" s="131" t="n">
         <v>4.5</v>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -2881,12 +2852,12 @@
           <t>対象職種が最も広く、初期商品群の中核</t>
         </is>
       </c>
-      <c r="F7" s="110">
+      <c r="F7" s="112">
         <f>IF(A7=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1" s="86">
+    <row r="8" ht="26" customHeight="1" s="89">
       <c r="A8" s="67" t="n">
         <v>1</v>
       </c>
@@ -2898,7 +2869,7 @@
           <t>足場の組立て・解体・変更</t>
         </is>
       </c>
-      <c r="D8" s="129" t="n">
+      <c r="D8" s="131" t="n">
         <v>6</v>
       </c>
       <c r="E8" s="35" t="inlineStr">
@@ -2906,12 +2877,12 @@
           <t>実技の定めがなく、学科のみで修了まで完結する</t>
         </is>
       </c>
-      <c r="F8" s="110">
+      <c r="F8" s="112">
         <f>IF(A8=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1" s="86">
+    <row r="9" ht="26" customHeight="1" s="89">
       <c r="A9" s="67" t="n">
         <v>1</v>
       </c>
@@ -2923,7 +2894,7 @@
           <t>自由研削用といし</t>
         </is>
       </c>
-      <c r="D9" s="129" t="n">
+      <c r="D9" s="131" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="35" t="inlineStr">
@@ -2931,12 +2902,12 @@
           <t>幅広い工種で利用され、学科時間もコンパクト</t>
         </is>
       </c>
-      <c r="F9" s="110">
+      <c r="F9" s="112">
         <f>IF(A9=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1" s="86">
+    <row r="10" ht="26" customHeight="1" s="89">
       <c r="A10" s="67" t="n">
         <v>0</v>
       </c>
@@ -2948,7 +2919,7 @@
           <t>低圧電気取扱業務</t>
         </is>
       </c>
-      <c r="D10" s="130" t="n">
+      <c r="D10" s="132" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="35" t="inlineStr">
@@ -2956,12 +2927,12 @@
           <t>学科7時間と最長級。制作負担が大きく第2次へ</t>
         </is>
       </c>
-      <c r="F10" s="110">
+      <c r="F10" s="112">
         <f>IF(A10=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1" s="86">
+    <row r="11" ht="26" customHeight="1" s="89">
       <c r="A11" s="67" t="n">
         <v>1</v>
       </c>
@@ -2973,7 +2944,7 @@
           <t>アーク溶接等</t>
         </is>
       </c>
-      <c r="D11" s="129" t="n">
+      <c r="D11" s="131" t="n">
         <v>11</v>
       </c>
       <c r="E11" s="35" t="inlineStr">
@@ -2981,12 +2952,12 @@
           <t>既存の制作資産を活用できるため優先</t>
         </is>
       </c>
-      <c r="F11" s="110">
+      <c r="F11" s="112">
         <f>IF(A11=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1" s="86">
+    <row r="12" ht="26" customHeight="1" s="89">
       <c r="A12" s="67" t="n">
         <v>1</v>
       </c>
@@ -2998,7 +2969,7 @@
           <t>石綿使用建築物等の解体・破砕等</t>
         </is>
       </c>
-      <c r="D12" s="129" t="n">
+      <c r="D12" s="131" t="n">
         <v>4.5</v>
       </c>
       <c r="E12" s="35" t="inlineStr">
@@ -3006,12 +2977,12 @@
           <t>実技なし。解体・改修の需要が継続的にある</t>
         </is>
       </c>
-      <c r="F12" s="110">
+      <c r="F12" s="112">
         <f>IF(A12=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1" s="86">
+    <row r="13" ht="26" customHeight="1" s="89">
       <c r="A13" s="67" t="n">
         <v>1</v>
       </c>
@@ -3023,7 +2994,7 @@
           <t>特定粉じん作業</t>
         </is>
       </c>
-      <c r="D13" s="129" t="n">
+      <c r="D13" s="131" t="n">
         <v>4.5</v>
       </c>
       <c r="E13" s="35" t="inlineStr">
@@ -3031,12 +3002,12 @@
           <t>実技なし。建設現場の有害業務として汎用性が高い</t>
         </is>
       </c>
-      <c r="F13" s="110">
+      <c r="F13" s="112">
         <f>IF(A13=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1" s="86">
+    <row r="14" ht="26" customHeight="1" s="89">
       <c r="A14" s="67" t="n">
         <v>0</v>
       </c>
@@ -3048,7 +3019,7 @@
           <t>第2種酸素欠乏危険作業</t>
         </is>
       </c>
-      <c r="D14" s="130" t="n">
+      <c r="D14" s="132" t="n">
         <v>5.5</v>
       </c>
       <c r="E14" s="35" t="inlineStr">
@@ -3056,12 +3027,12 @@
           <t>対象職種が設備・土木に限られるため第2次へ</t>
         </is>
       </c>
-      <c r="F14" s="110">
+      <c r="F14" s="112">
         <f>IF(A14=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1" s="86">
+    <row r="15" ht="26" customHeight="1" s="89">
       <c r="A15" s="67" t="n">
         <v>0</v>
       </c>
@@ -3073,7 +3044,7 @@
           <t>高所作業車（10m未満）</t>
         </is>
       </c>
-      <c r="D15" s="130" t="n">
+      <c r="D15" s="132" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="35" t="inlineStr">
@@ -3081,12 +3052,12 @@
           <t>実技3時間を伴い、対象が限定的なため第2次へ</t>
         </is>
       </c>
-      <c r="F15" s="110">
+      <c r="F15" s="112">
         <f>IF(A15=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1" s="86">
+    <row r="16" ht="26" customHeight="1" s="89">
       <c r="A16" s="67" t="n">
         <v>0</v>
       </c>
@@ -3098,7 +3069,7 @@
           <t>玉掛け（1t未満）</t>
         </is>
       </c>
-      <c r="D16" s="130" t="n">
+      <c r="D16" s="132" t="n">
         <v>5</v>
       </c>
       <c r="E16" s="35" t="inlineStr">
@@ -3106,61 +3077,61 @@
           <t>実技4時間を伴い、対象が限定的なため第2次へ</t>
         </is>
       </c>
-      <c r="F16" s="110">
+      <c r="F16" s="112">
         <f>IF(A16=1,$D$4,0)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="17" customHeight="1" s="86">
-      <c r="A17" s="131">
+    <row r="17" ht="17" customHeight="1" s="89">
+      <c r="A17" s="133">
         <f>SUM(A7:A16)</f>
         <v/>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="102" t="inlineStr">
+      <c r="C17" s="107" t="inlineStr">
         <is>
           <t>制作対象 合計</t>
         </is>
       </c>
-      <c r="D17" s="132">
+      <c r="D17" s="134">
         <f>SUMPRODUCT($A7:$A16,$D7:$D16)</f>
         <v/>
       </c>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="133">
+      <c r="F17" s="135">
         <f>SUM(F7:F16)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1" s="86">
+    <row r="19" ht="17" customHeight="1" s="89">
       <c r="A19" s="55" t="inlineStr">
         <is>
           <t>■ 選定の考え方</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1" s="86">
+    <row r="20" ht="17" customHeight="1" s="89">
       <c r="A20" s="54" t="inlineStr">
         <is>
           <t>・実技の定めがない科目（足場・石綿・特定粉じん）を優先し、最短で販売を開始できるようにしています。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="86">
+    <row r="21" ht="17" customHeight="1" s="89">
       <c r="A21" s="54" t="inlineStr">
         <is>
           <t>・アーク溶接等は既存の制作資産があるため、優先して商品化します。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1" s="86">
+    <row r="22" ht="17" customHeight="1" s="89">
       <c r="A22" s="54" t="inlineStr">
         <is>
           <t>・除外した4科目は、学科時間が長いか対象職種が限定的なものです。第2次発注でのご検討をお願いします。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1" s="86">
+    <row r="23" ht="17" customHeight="1" s="89">
       <c r="A23" s="54" t="inlineStr">
         <is>
           <t>・A列の 1 と 0 を入れ替えれば、対象科目を自由に変更できます（見積金額も自動で追随します）。</t>
@@ -3184,49 +3155,49 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="16" customWidth="1" style="86" min="1" max="1"/>
-    <col width="32" customWidth="1" style="86" min="2" max="2"/>
-    <col width="16" customWidth="1" style="86" min="3" max="3"/>
-    <col width="66" customWidth="1" style="86" min="4" max="4"/>
+    <col width="16" customWidth="1" style="89" min="1" max="1"/>
+    <col width="32" customWidth="1" style="89" min="2" max="2"/>
+    <col width="16" customWidth="1" style="89" min="3" max="3"/>
+    <col width="66" customWidth="1" style="89" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="86">
+    <row r="1" ht="24" customHeight="1" s="89">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>月額費用と別途費用</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="86">
+    <row r="2" ht="17" customHeight="1" s="89">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>初期費用（シート01）とは別に、下記が発生します。金額はすべて税抜です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="86">
-      <c r="A4" s="92" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="89">
+      <c r="A4" s="104" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B4" s="92" t="inlineStr">
+      <c r="B4" s="104" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
+      <c r="C4" s="104" t="inlineStr">
         <is>
           <t>月額／単価</t>
         </is>
       </c>
-      <c r="D4" s="92" t="inlineStr">
+      <c r="D4" s="104" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1" s="86">
+    <row r="5" ht="46" customHeight="1" s="89">
       <c r="A5" s="75" t="inlineStr">
         <is>
           <t>弊社へ
@@ -3238,7 +3209,7 @@
           <t>保守・運用サービス</t>
         </is>
       </c>
-      <c r="C5" s="124" t="n">
+      <c r="C5" s="126" t="n">
         <v>60000</v>
       </c>
       <c r="D5" s="90" t="inlineStr">
@@ -3247,14 +3218,14 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1" s="86">
+    <row r="6" ht="40" customHeight="1" s="89">
       <c r="A6" s="16" t="n"/>
       <c r="B6" s="65" t="inlineStr">
         <is>
           <t>法令改正監視・通知サービス</t>
         </is>
       </c>
-      <c r="C6" s="124" t="n">
+      <c r="C6" s="126" t="n">
         <v>20000</v>
       </c>
       <c r="D6" s="90" t="inlineStr">
@@ -3263,14 +3234,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="86">
+    <row r="7" ht="20" customHeight="1" s="89">
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="51" t="inlineStr">
         <is>
           <t>月額 小計（サーバー費を除く）</t>
         </is>
       </c>
-      <c r="C7" s="121">
+      <c r="C7" s="123">
         <f>SUM(C5:C6)</f>
         <v/>
       </c>
@@ -3280,7 +3251,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" s="86">
+    <row r="9" ht="36" customHeight="1" s="89">
       <c r="A9" s="75" t="inlineStr">
         <is>
           <t>お客様
@@ -3292,7 +3263,7 @@
           <t>AWS 利用料（構成B・推奨）</t>
         </is>
       </c>
-      <c r="C9" s="124" t="n">
+      <c r="C9" s="126" t="n">
         <v>22800</v>
       </c>
       <c r="D9" s="90" t="inlineStr">
@@ -3301,7 +3272,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" s="86">
+    <row r="10" ht="28" customHeight="1" s="89">
       <c r="A10" s="16" t="n"/>
       <c r="B10" s="65" t="inlineStr">
         <is>
@@ -3319,14 +3290,14 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1" s="86">
+    <row r="11" ht="32" customHeight="1" s="89">
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="65" t="inlineStr">
         <is>
           <t>株式会社ゼウス（決済代行）</t>
         </is>
       </c>
-      <c r="C11" s="124" t="n">
+      <c r="C11" s="126" t="n">
         <v>3000</v>
       </c>
       <c r="D11" s="90" t="inlineStr">
@@ -3335,7 +3306,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="86">
+    <row r="13" ht="30" customHeight="1" s="89">
       <c r="A13" s="75" t="inlineStr">
         <is>
           <t>都度
@@ -3347,7 +3318,7 @@
           <t>教材の改訂（法令改正対応）</t>
         </is>
       </c>
-      <c r="C13" s="113">
+      <c r="C13" s="115">
         <f>'04_教材科目'!D4</f>
         <v/>
       </c>
@@ -3357,14 +3328,14 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1" s="86">
+    <row r="14" ht="28" customHeight="1" s="89">
       <c r="A14" s="16" t="n"/>
       <c r="B14" s="65" t="inlineStr">
         <is>
           <t>教材の追加制作（第2次）</t>
         </is>
       </c>
-      <c r="C14" s="113">
+      <c r="C14" s="115">
         <f>'04_教材科目'!D4</f>
         <v/>
       </c>
@@ -3374,20 +3345,20 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1" s="86">
+    <row r="16" ht="19" customHeight="1" s="89">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>参考：月額の合計（聖建様のご負担総額）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" s="86">
+    <row r="17" ht="20" customHeight="1" s="89">
       <c r="B17" s="65" t="inlineStr">
         <is>
           <t>弊社サービス ＋ AWS ＋ ゼウス月額</t>
         </is>
       </c>
-      <c r="C17" s="134">
+      <c r="C17" s="136">
         <f>'05_月額・別途費用'!C7+C9+C11</f>
         <v/>
       </c>
@@ -3397,73 +3368,73 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1" s="86">
+    <row r="19" ht="17" customHeight="1" s="89">
       <c r="A19" s="55" t="inlineStr">
         <is>
           <t>■ 月額80,000円の根拠</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1" s="86">
+    <row r="20" ht="17" customHeight="1" s="89">
       <c r="A20" s="54" t="inlineStr">
         <is>
           <t>聖建様のご指定額（サーバー費を除く月額80,000円）にあわせ、内訳を次のとおり組みました。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="86">
+    <row r="21" ht="17" customHeight="1" s="89">
       <c r="A21" s="54" t="inlineStr">
         <is>
           <t>・保守・運用サービス　60,000円　… 受講中のランダム照合を実装しないため、照合結果の</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1" s="86">
+    <row r="22" ht="17" customHeight="1" s="89">
       <c r="A22" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">　　目視確認という運用作業がなくなります。その分を減額しています。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1" s="86">
+    <row r="23" ht="17" customHeight="1" s="89">
       <c r="A23" s="54" t="inlineStr">
         <is>
           <t>・法令改正監視・通知サービス　20,000円　… 前回から変更ありません。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="17" customHeight="1" s="86">
+    <row r="24" ht="17" customHeight="1" s="89">
       <c r="A24" s="54" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1" s="86">
+    <row r="25" ht="17" customHeight="1" s="89">
       <c r="A25" s="55" t="inlineStr">
         <is>
           <t>■ ゼウスについて</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="17" customHeight="1" s="86">
+    <row r="26" ht="17" customHeight="1" s="89">
       <c r="A26" s="54" t="inlineStr">
         <is>
           <t>・株式会社ゼウス（1994年設立・国内の決済代行事業者）との契約は聖建様が直接行っていただきます。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="86">
+    <row r="27" ht="17" customHeight="1" s="89">
       <c r="A27" s="54" t="inlineStr">
         <is>
           <t>・初期費用は無料、月額3,000円、クレジットカード決済手数料は最大3.5%です（2026年9月時点）。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="86">
+    <row r="28" ht="17" customHeight="1" s="89">
       <c r="A28" s="54" t="inlineStr">
         <is>
           <t>・接続方式はデータ転送（API）型を想定しています。申込から入金確認、受講開始までを自動化します。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1" s="86">
+    <row r="29" ht="17" customHeight="1" s="89">
       <c r="A29" s="53" t="inlineStr">
         <is>
           <t>・最新の料金と条件は、ご契約前にゼウス社へ直接ご確認ください。</t>
@@ -3486,24 +3457,24 @@
   <dimension ref="B2:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" style="86" min="1" max="1"/>
-    <col width="20" customWidth="1" style="86" min="2" max="2"/>
-    <col width="24" customWidth="1" style="86" min="3" max="3"/>
-    <col width="14" customWidth="1" style="86" min="4" max="4"/>
-    <col width="16" customWidth="1" style="86" min="5" max="5"/>
-    <col width="18" customWidth="1" style="86" min="6" max="6"/>
-    <col width="3" customWidth="1" style="86" min="7" max="7"/>
+    <col width="3" customWidth="1" style="89" min="1" max="1"/>
+    <col width="20" customWidth="1" style="89" min="2" max="2"/>
+    <col width="24" customWidth="1" style="89" min="3" max="3"/>
+    <col width="14" customWidth="1" style="89" min="4" max="4"/>
+    <col width="16" customWidth="1" style="89" min="5" max="5"/>
+    <col width="18" customWidth="1" style="89" min="6" max="6"/>
+    <col width="3" customWidth="1" style="89" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" s="86">
-      <c r="B2" s="95" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="89">
+      <c r="B2" s="97" t="inlineStr">
         <is>
           <t>注　文　書</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="86">
-      <c r="B4" s="97" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="89">
+      <c r="B4" s="93" t="inlineStr">
         <is>
           <t>注文番号</t>
         </is>
@@ -3514,8 +3485,8 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="86">
-      <c r="B5" s="97" t="inlineStr">
+    <row r="5" ht="16" customHeight="1" s="89">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
@@ -3526,84 +3497,84 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1" s="86">
-      <c r="B7" s="91" t="inlineStr">
+    <row r="7" ht="25" customHeight="1" s="89">
+      <c r="B7" s="99" t="inlineStr">
         <is>
           <t>株式会社スペリオル　御中</t>
         </is>
       </c>
-      <c r="E7" s="96" t="inlineStr">
+      <c r="E7" s="95" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" s="86">
-      <c r="B8" s="97" t="inlineStr">
+    <row r="8" ht="22" customHeight="1" s="89">
+      <c r="B8" s="93" t="inlineStr">
         <is>
           <t>〒464-0075　名古屋市千種区内山3-18-10</t>
         </is>
       </c>
-      <c r="E8" s="105" t="inlineStr">
+      <c r="E8" s="100" t="inlineStr">
         <is>
           <t>株式会社聖建</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="86">
-      <c r="B9" s="97" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="89">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>TEL 052-745-6607　／　登録番号 T9180001048541</t>
         </is>
       </c>
-      <c r="E9" s="96" t="inlineStr">
+      <c r="E9" s="95" t="inlineStr">
         <is>
           <t>〒475-0805　愛知県半田市浜田町1丁目7番地</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17" customHeight="1" s="86">
+    <row r="10" ht="17" customHeight="1" s="89">
       <c r="B10" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
       </c>
-      <c r="E10" s="96" t="inlineStr">
+      <c r="E10" s="95" t="inlineStr">
         <is>
           <t>TEL 0569-84-9669</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="86">
-      <c r="E11" s="104" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="89">
+      <c r="E11" s="98" t="inlineStr">
         <is>
           <t>ご担当　　　　　　　　　　　　　　印</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="17" customHeight="1" s="86">
-      <c r="B13" s="98" t="inlineStr">
+    <row r="13" ht="17" customHeight="1" s="89">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>下記のとおり注文いたします。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="86">
+    <row r="15" ht="30" customHeight="1" s="89">
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="C15" s="101" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t>建設業 特別教育 eラーニング配信システム 構築 および 教材制作（6科目）一式</t>
         </is>
       </c>
-      <c r="D15" s="88" t="n"/>
-      <c r="E15" s="88" t="n"/>
-      <c r="F15" s="89" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1" s="86">
+      <c r="D15" s="91" t="n"/>
+      <c r="E15" s="91" t="n"/>
+      <c r="F15" s="92" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="89">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>根拠見積</t>
@@ -3613,34 +3584,34 @@
         <f>'01_見積書'!C4&amp;"（"&amp;'01_見積書'!C5&amp;" 発行）"</f>
         <v/>
       </c>
-      <c r="D16" s="88" t="n"/>
-      <c r="E16" s="88" t="n"/>
-      <c r="F16" s="89" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" s="86">
-      <c r="B18" s="92" t="inlineStr">
+      <c r="D16" s="91" t="n"/>
+      <c r="E16" s="91" t="n"/>
+      <c r="F16" s="92" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="89">
+      <c r="B18" s="104" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="104" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="D18" s="104" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E18" s="92" t="n"/>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="E18" s="104" t="n"/>
+      <c r="F18" s="104" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" s="86">
+    <row r="19" ht="28" customHeight="1" s="89">
       <c r="B19" s="9" t="inlineStr">
         <is>
           <t>システム開発</t>
@@ -3657,12 +3628,12 @@
         </is>
       </c>
       <c r="E19" s="19" t="n"/>
-      <c r="F19" s="110">
+      <c r="F19" s="112">
         <f>'03_見積明細'!F21</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" s="86">
+    <row r="20" ht="28" customHeight="1" s="89">
       <c r="B20" s="9" t="inlineStr">
         <is>
           <t>教材制作</t>
@@ -3673,17 +3644,17 @@
           <t>特別教育 学科教材 6科目</t>
         </is>
       </c>
-      <c r="D20" s="111">
+      <c r="D20" s="113">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
       <c r="E20" s="19" t="n"/>
-      <c r="F20" s="110">
+      <c r="F20" s="112">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="86">
+    <row r="21" ht="17" customHeight="1" s="89">
       <c r="B21" s="29" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
@@ -3692,12 +3663,12 @@
       <c r="C21" s="16" t="n"/>
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
-      <c r="F21" s="112">
+      <c r="F21" s="114">
         <f>SUM(F19:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1" s="86">
+    <row r="22" ht="17" customHeight="1" s="89">
       <c r="B22" s="64" t="inlineStr">
         <is>
           <t>特別値引き</t>
@@ -3706,12 +3677,12 @@
       <c r="C22" s="79" t="n"/>
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="19" t="n"/>
-      <c r="F22" s="113">
+      <c r="F22" s="115">
         <f>'03_見積明細'!F27</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1" s="86">
+    <row r="23" ht="17" customHeight="1" s="89">
       <c r="B23" s="65" t="inlineStr">
         <is>
           <t>消費税</t>
@@ -3723,12 +3694,12 @@
         <v/>
       </c>
       <c r="E23" s="19" t="n"/>
-      <c r="F23" s="114">
+      <c r="F23" s="116">
         <f>ROUND((F21+F22)*D23,0)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1" s="86">
+    <row r="24" ht="26" customHeight="1" s="89">
       <c r="B24" s="39" t="inlineStr">
         <is>
           <t>ご注文金額（税込）</t>
@@ -3737,12 +3708,12 @@
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
-      <c r="F24" s="135">
+      <c r="F24" s="137">
         <f>F21+F22+F23</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1" s="86">
+    <row r="26" ht="42" customHeight="1" s="89">
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>納期</t>
@@ -3753,11 +3724,11 @@
           <t>システム：ご発注後 約4か月　／　教材：第1次3科目 約4か月、第2次3科目 約7か月</t>
         </is>
       </c>
-      <c r="D26" s="88" t="n"/>
-      <c r="E26" s="88" t="n"/>
-      <c r="F26" s="89" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" s="86">
+      <c r="D26" s="91" t="n"/>
+      <c r="E26" s="91" t="n"/>
+      <c r="F26" s="92" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="89">
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>納入場所</t>
@@ -3768,11 +3739,11 @@
           <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
-      <c r="D27" s="88" t="n"/>
-      <c r="E27" s="88" t="n"/>
-      <c r="F27" s="89" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" s="86">
+      <c r="D27" s="91" t="n"/>
+      <c r="E27" s="91" t="n"/>
+      <c r="F27" s="92" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="89">
       <c r="B28" s="4" t="inlineStr">
         <is>
           <t>検収条件</t>
@@ -3783,11 +3754,11 @@
           <t>納品後14日以内に検収。期間内にご連絡なき場合は検収完了とみなします。</t>
         </is>
       </c>
-      <c r="D28" s="88" t="n"/>
-      <c r="E28" s="88" t="n"/>
-      <c r="F28" s="89" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1" s="86">
+      <c r="D28" s="91" t="n"/>
+      <c r="E28" s="91" t="n"/>
+      <c r="F28" s="92" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="89">
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>支払条件</t>
@@ -3798,33 +3769,33 @@
           <t>本注文書の発行時に、上記ご注文金額の全額を一括でお支払いいたします。</t>
         </is>
       </c>
-      <c r="D29" s="88" t="n"/>
-      <c r="E29" s="88" t="n"/>
-      <c r="F29" s="89" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="86">
+      <c r="D29" s="91" t="n"/>
+      <c r="E29" s="91" t="n"/>
+      <c r="F29" s="92" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="89">
       <c r="B31" s="26" t="inlineStr">
         <is>
           <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1" s="86">
-      <c r="B32" s="99" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="89">
+      <c r="B32" s="88" t="inlineStr">
         <is>
           <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1" s="86">
-      <c r="B33" s="99" t="inlineStr">
+    <row r="33" ht="17" customHeight="1" s="89">
+      <c r="B33" s="88" t="inlineStr">
         <is>
           <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1" s="86">
-      <c r="B34" s="99" t="inlineStr">
+    <row r="34" ht="17" customHeight="1" s="89">
+      <c r="B34" s="88" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
         </is>
@@ -3833,8 +3804,8 @@
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="C26:F26"/>
@@ -3853,7 +3824,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="94" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3866,24 +3837,24 @@
   <dimension ref="B1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" style="86" min="1" max="1"/>
-    <col width="30" customWidth="1" style="86" min="2" max="2"/>
-    <col width="88" customWidth="1" style="86" min="3" max="3"/>
+    <col width="3" customWidth="1" style="89" min="1" max="1"/>
+    <col width="30" customWidth="1" style="89" min="2" max="2"/>
+    <col width="88" customWidth="1" style="89" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="86">
-      <c r="B1" s="106" t="inlineStr">
-        <is>
-          <t>見積の前提条件</t>
-        </is>
-      </c>
-      <c r="C1" s="107" t="n"/>
+    <row r="1" ht="24" customHeight="1" s="89">
+      <c r="B1" s="85" t="inlineStr">
+        <is>
+          <t>聖建様　見積前提条件</t>
+        </is>
+      </c>
+      <c r="C1" s="86" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="107" t="n"/>
-      <c r="C2" s="107" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1" s="86">
+      <c r="B2" s="86" t="n"/>
+      <c r="C2" s="86" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="89">
       <c r="B3" s="82" t="inlineStr">
         <is>
           <t>■ 1. 本見積に含まれるもの</t>
@@ -3891,8 +3862,8 @@
       </c>
       <c r="C3" s="83" t="n"/>
     </row>
-    <row r="4" ht="31" customHeight="1" s="86">
-      <c r="B4" s="108" t="inlineStr">
+    <row r="4" ht="31" customHeight="1" s="89">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
@@ -3903,8 +3874,8 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" s="86">
-      <c r="B5" s="108" t="inlineStr">
+    <row r="5" ht="34" customHeight="1" s="89">
+      <c r="B5" s="87" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
@@ -3915,8 +3886,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" s="86">
-      <c r="B6" s="108" t="inlineStr">
+    <row r="6" ht="34" customHeight="1" s="89">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>修了証</t>
         </is>
@@ -3927,8 +3898,8 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" s="86">
-      <c r="B7" s="108" t="inlineStr">
+    <row r="7" ht="22" customHeight="1" s="89">
+      <c r="B7" s="87" t="inlineStr">
         <is>
           <t>サーバー環境の構築</t>
         </is>
@@ -3940,10 +3911,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="107" t="n"/>
-      <c r="C8" s="107" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="86">
+      <c r="B8" s="86" t="n"/>
+      <c r="C8" s="86" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="89">
       <c r="B9" s="84" t="inlineStr">
         <is>
           <t>■ 2. 本見積に含まれないもの（別途）</t>
@@ -3951,21 +3922,20 @@
       </c>
       <c r="C9" s="83" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1" s="86">
-      <c r="B10" s="108" t="inlineStr">
+    <row r="10" ht="34" customHeight="1" s="89">
+      <c r="B10" s="109" t="inlineStr">
         <is>
           <t>受講中のランダム顔照合</t>
         </is>
       </c>
-      <c r="C10" s="90" t="inlineStr">
-        <is>
-          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。
-登録時の本人確認と受講開始時の顔照合は実装します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="23" customHeight="1" s="86">
-      <c r="B11" s="108" t="inlineStr">
+      <c r="C10" s="110" t="inlineStr">
+        <is>
+          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。　　　　　　　　　　　登録時の本人確認と受講開始時の顔照合は実装します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1" s="89">
+      <c r="B11" s="87" t="inlineStr">
         <is>
           <t>月額サービス</t>
         </is>
@@ -3976,8 +3946,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1" s="86">
-      <c r="B12" s="108" t="inlineStr">
+    <row r="12" ht="22" customHeight="1" s="89">
+      <c r="B12" s="87" t="inlineStr">
         <is>
           <t>サーバー利用料</t>
         </is>
@@ -3988,8 +3958,8 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" s="86">
-      <c r="B13" s="108" t="inlineStr">
+    <row r="13" ht="22" customHeight="1" s="89">
+      <c r="B13" s="87" t="inlineStr">
         <is>
           <t>教材の改訂・追加</t>
         </is>
@@ -4000,8 +3970,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" s="86">
-      <c r="B14" s="108" t="inlineStr">
+    <row r="14" ht="22" customHeight="1" s="89">
+      <c r="B14" s="87" t="inlineStr">
         <is>
           <t>教材の監修</t>
         </is>
@@ -4013,10 +3983,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="107" t="n"/>
-      <c r="C15" s="107" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" s="86">
+      <c r="B15" s="86" t="n"/>
+      <c r="C15" s="86" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="89">
       <c r="B16" s="82" t="inlineStr">
         <is>
           <t>■ 3. 責任の分担</t>
@@ -4024,8 +3994,8 @@
       </c>
       <c r="C16" s="83" t="n"/>
     </row>
-    <row r="17" ht="34" customHeight="1" s="86">
-      <c r="B17" s="108" t="inlineStr">
+    <row r="17" ht="34" customHeight="1" s="89">
+      <c r="B17" s="87" t="inlineStr">
         <is>
           <t>弊社が保証すること</t>
         </is>
@@ -4036,8 +4006,8 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1" s="86">
-      <c r="B18" s="108" t="inlineStr">
+    <row r="18" ht="34" customHeight="1" s="89">
+      <c r="B18" s="87" t="inlineStr">
         <is>
           <t>弊社が保証しないこと</t>
         </is>
@@ -4048,8 +4018,8 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1" s="86">
-      <c r="B19" s="108" t="inlineStr">
+    <row r="19" ht="34" customHeight="1" s="89">
+      <c r="B19" s="87" t="inlineStr">
         <is>
           <t>法令改正への対応</t>
         </is>
@@ -4061,10 +4031,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="107" t="n"/>
-      <c r="C20" s="107" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" s="86">
+      <c r="B20" s="86" t="n"/>
+      <c r="C20" s="86" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="89">
       <c r="B21" s="82" t="inlineStr">
         <is>
           <t>■ 4. 金額の前提</t>
@@ -4072,8 +4042,8 @@
       </c>
       <c r="C21" s="83" t="n"/>
     </row>
-    <row r="22" ht="22" customHeight="1" s="86">
-      <c r="B22" s="108" t="inlineStr">
+    <row r="22" ht="22" customHeight="1" s="89">
+      <c r="B22" s="87" t="inlineStr">
         <is>
           <t>教材制作単価</t>
         </is>
@@ -4084,20 +4054,20 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1" s="86">
-      <c r="B23" s="108" t="inlineStr">
+    <row r="23" ht="22" customHeight="1" s="89">
+      <c r="B23" s="87" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
       <c r="C23" s="90" t="inlineStr">
         <is>
-          <t>ご発注時に全額を一括でお支払いいただくことを前提とした金額です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" s="86">
-      <c r="B24" s="108" t="inlineStr">
+          <t>2026年9月29日までに全額を一括でお支払いいただくことを前提とした金額です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="89">
+      <c r="B24" s="87" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
@@ -4111,6 +4081,6 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="74" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -869,7 +869,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7391880" y="1793879"/>
+    <pos x="6549120" y="1464479"/>
     <ext cx="878040" cy="878040"/>
     <pic>
       <nvPicPr>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C23" s="90" t="inlineStr">
         <is>
-          <t>ご発注時に全額を一括でお支払いください。</t>
+          <t>2026年9月29日までに全額を一括でお支払いください。</t>
         </is>
       </c>
       <c r="D23" s="91" t="n"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C29" s="90" t="inlineStr">
         <is>
-          <t>本注文書の発行時に、上記ご注文金額の全額を一括でお支払いいたします。</t>
+          <t>2026年9月29日までに、上記ご注文金額の全額を一括でお支払いいたします。</t>
         </is>
       </c>
       <c r="D29" s="91" t="n"/>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -3930,7 +3930,8 @@
       </c>
       <c r="C10" s="110" t="inlineStr">
         <is>
-          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。　　　　　　　　　　　登録時の本人確認と受講開始時の顔照合は実装します。</t>
+          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。
+登録時の本人確認と受講開始時の顔照合は実装します。</t>
         </is>
       </c>
     </row>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17340" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17340" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_見積書" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,12 +16,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'01_見積書'!$A$1:$F$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'04_教材科目'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05_月額・別途費用'!$A$1:$D$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$27</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -698,68 +698,68 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -847,7 +847,74 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1183,46 +1250,46 @@
   <dimension ref="B2:F38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" style="89" min="1" max="1"/>
-    <col width="20" customWidth="1" style="89" min="2" max="3"/>
-    <col width="16" customWidth="1" style="89" min="4" max="5"/>
-    <col width="18" customWidth="1" style="89" min="6" max="6"/>
-    <col width="3" customWidth="1" style="89" min="7" max="7"/>
+    <col width="3" customWidth="1" style="91" min="1" max="1"/>
+    <col width="20" customWidth="1" style="91" min="2" max="3"/>
+    <col width="16" customWidth="1" style="91" min="4" max="5"/>
+    <col width="18" customWidth="1" style="91" min="6" max="6"/>
+    <col width="3" customWidth="1" style="91" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" s="89">
-      <c r="B2" s="97" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="91">
+      <c r="B2" s="100" t="inlineStr">
         <is>
           <t>御　見　積　書</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="89">
-      <c r="B4" s="93" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="91">
+      <c r="B4" s="102" t="inlineStr">
         <is>
           <t>見積番号</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SP-2026-0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="89">
-      <c r="B5" s="93" t="inlineStr">
+          <t>SP-2026-0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="91">
+      <c r="B5" s="102" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026年9月13日</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="89">
-      <c r="B6" s="93" t="inlineStr">
+          <t>2026年9月14日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="91">
+      <c r="B6" s="102" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
@@ -1233,221 +1300,221 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="25" customHeight="1" s="89">
-      <c r="B8" s="99" t="inlineStr">
+    <row r="8" ht="25" customHeight="1" s="91">
+      <c r="B8" s="96" t="inlineStr">
         <is>
           <t>株式会社聖建　御中</t>
         </is>
       </c>
-      <c r="E8" s="105" t="inlineStr">
+      <c r="E8" s="98" t="inlineStr">
         <is>
           <t>株式会社スペリオル</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="89">
-      <c r="B9" s="93" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="91">
+      <c r="B9" s="102" t="inlineStr">
         <is>
           <t>〒475-0805　愛知県半田市浜田町1丁目7番地</t>
         </is>
       </c>
-      <c r="E9" s="95" t="inlineStr">
+      <c r="E9" s="101" t="inlineStr">
         <is>
           <t>〒464-0075　名古屋市千種区内山3-18-10</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="89">
-      <c r="E10" s="95" t="inlineStr">
+    <row r="10" ht="16" customHeight="1" s="91">
+      <c r="E10" s="101" t="inlineStr">
         <is>
           <t>TEL 052-745-6607</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="89">
-      <c r="E11" s="95" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="91">
+      <c r="E11" s="101" t="inlineStr">
         <is>
           <t>登録番号 T9180001048541</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" s="89">
-      <c r="E12" s="102" t="inlineStr">
+    <row r="12" ht="16" customHeight="1" s="91">
+      <c r="E12" s="90" t="inlineStr">
         <is>
           <t>担当　藤原</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1" s="89">
-      <c r="B14" s="96" t="inlineStr">
+    <row r="14" ht="17" customHeight="1" s="91">
+      <c r="B14" s="103" t="inlineStr">
         <is>
           <t>下記のとおりお見積り申し上げます。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1" s="89">
+    <row r="16" ht="32" customHeight="1" s="91">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="106" t="inlineStr">
         <is>
           <t>建設業 特別教育 eラーニング配信システム 構築 および 教材制作（6科目）一式</t>
         </is>
       </c>
-      <c r="D16" s="91" t="n"/>
-      <c r="E16" s="91" t="n"/>
-      <c r="F16" s="92" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" s="89">
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="94" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="91">
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>御見積金額</t>
         </is>
       </c>
       <c r="C17" s="111">
-        <f>'03_見積明細'!F28</f>
-        <v/>
-      </c>
-      <c r="D17" s="91" t="n"/>
-      <c r="E17" s="91" t="n"/>
-      <c r="F17" s="92" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" s="89">
+        <f>'03_見積明細'!F30</f>
+        <v/>
+      </c>
+      <c r="D17" s="93" t="n"/>
+      <c r="E17" s="93" t="n"/>
+      <c r="F17" s="94" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="91">
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="106">
-        <f>"消費税 ¥"&amp;TEXT('03_見積明細'!F29,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT('03_見積明細'!F30,"#,##0")</f>
-        <v/>
-      </c>
-      <c r="D18" s="91" t="n"/>
-      <c r="E18" s="91" t="n"/>
-      <c r="F18" s="92" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1" s="89">
+      <c r="C18" s="99">
+        <f>"消費税 ¥"&amp;TEXT('03_見積明細'!F31,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT('03_見積明細'!F32,"#,##0")</f>
+        <v/>
+      </c>
+      <c r="D18" s="93" t="n"/>
+      <c r="E18" s="93" t="n"/>
+      <c r="F18" s="94" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="91">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>納期</t>
         </is>
       </c>
-      <c r="C20" s="90" t="inlineStr">
+      <c r="C20" s="95" t="inlineStr">
         <is>
           <t>システム：ご発注後 約4か月　／　教材：第1次3科目 約4か月、第2次3科目 約7か月</t>
         </is>
       </c>
-      <c r="D20" s="91" t="n"/>
-      <c r="E20" s="91" t="n"/>
-      <c r="F20" s="92" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="89">
+      <c r="D20" s="93" t="n"/>
+      <c r="E20" s="93" t="n"/>
+      <c r="F20" s="94" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="91">
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>納入場所</t>
         </is>
       </c>
-      <c r="C21" s="90" t="inlineStr">
+      <c r="C21" s="95" t="inlineStr">
         <is>
           <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
-      <c r="D21" s="91" t="n"/>
-      <c r="E21" s="91" t="n"/>
-      <c r="F21" s="92" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" s="89">
+      <c r="D21" s="93" t="n"/>
+      <c r="E21" s="93" t="n"/>
+      <c r="F21" s="94" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="91">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>検収条件</t>
         </is>
       </c>
-      <c r="C22" s="90" t="inlineStr">
+      <c r="C22" s="95" t="inlineStr">
         <is>
           <t>納品後14日以内に貴社にて検収。期間内にご連絡なき場合は検収完了とみなします。</t>
         </is>
       </c>
-      <c r="D22" s="91" t="n"/>
-      <c r="E22" s="91" t="n"/>
-      <c r="F22" s="92" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" s="89">
+      <c r="D22" s="93" t="n"/>
+      <c r="E22" s="93" t="n"/>
+      <c r="F22" s="94" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="91">
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
-      <c r="C23" s="90" t="inlineStr">
+      <c r="C23" s="95" t="inlineStr">
         <is>
           <t>2026年9月29日までに全額を一括でお支払いください。</t>
         </is>
       </c>
-      <c r="D23" s="91" t="n"/>
-      <c r="E23" s="91" t="n"/>
-      <c r="F23" s="92" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1" s="89">
+      <c r="D23" s="93" t="n"/>
+      <c r="E23" s="93" t="n"/>
+      <c r="F23" s="94" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1" s="91">
       <c r="B25" s="7" t="inlineStr">
         <is>
           <t>内訳</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1" s="89">
-      <c r="B26" s="104" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="91">
+      <c r="B26" s="97" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C26" s="104" t="inlineStr">
+      <c r="C26" s="97" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D26" s="92" t="n"/>
-      <c r="E26" s="104" t="inlineStr">
+      <c r="D26" s="94" t="n"/>
+      <c r="E26" s="97" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="F26" s="104" t="inlineStr">
+      <c r="F26" s="97" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="89">
+    <row r="27" ht="17" customHeight="1" s="91">
       <c r="B27" s="9" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
       </c>
-      <c r="C27" s="101" t="inlineStr">
-        <is>
-          <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
-        </is>
-      </c>
-      <c r="D27" s="92" t="n"/>
+      <c r="C27" s="105" t="inlineStr">
+        <is>
+          <t>配信基盤・視聴整合性・本人確認・在席確認・修了証発行</t>
+        </is>
+      </c>
+      <c r="D27" s="94" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
       </c>
       <c r="F27" s="112">
-        <f>'03_見積明細'!F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1" s="89">
+        <f>'03_見積明細'!F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1" s="91">
       <c r="B28" s="9" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
       </c>
-      <c r="C28" s="101" t="inlineStr">
+      <c r="C28" s="105" t="inlineStr">
         <is>
           <t>特別教育 学科教材 6科目</t>
         </is>
       </c>
-      <c r="D28" s="92" t="n"/>
+      <c r="D28" s="94" t="n"/>
       <c r="E28" s="113">
         <f>'04_教材科目'!$A$17</f>
         <v/>
@@ -1457,7 +1524,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1" s="89">
+    <row r="29" ht="17" customHeight="1" s="91">
       <c r="B29" s="14" t="inlineStr">
         <is>
           <t>小計</t>
@@ -1471,11 +1538,11 @@
       <c r="D29" s="16" t="n"/>
       <c r="E29" s="16" t="n"/>
       <c r="F29" s="114">
-        <f>'03_見積明細'!F26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1" s="89">
+        <f>'03_見積明細'!F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1" s="91">
       <c r="B30" s="9" t="inlineStr">
         <is>
           <t>値引</t>
@@ -1489,11 +1556,11 @@
       <c r="D30" s="19" t="n"/>
       <c r="E30" s="19" t="n"/>
       <c r="F30" s="115">
-        <f>'03_見積明細'!F27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="89">
+        <f>'03_見積明細'!F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="91">
       <c r="B31" s="9" t="inlineStr">
         <is>
           <t>差引小計</t>
@@ -1507,11 +1574,11 @@
       <c r="D31" s="19" t="n"/>
       <c r="E31" s="19" t="n"/>
       <c r="F31" s="116">
-        <f>'03_見積明細'!F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1" s="89">
+        <f>'03_見積明細'!F30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="91">
       <c r="B32" s="9" t="inlineStr">
         <is>
           <t>消費税</t>
@@ -1521,11 +1588,11 @@
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="n"/>
       <c r="F32" s="116">
-        <f>'03_見積明細'!F29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1" s="89">
+        <f>'03_見積明細'!F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" s="91">
       <c r="B33" s="23" t="inlineStr">
         <is>
           <t>合計</t>
@@ -1539,33 +1606,33 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="117">
-        <f>'03_見積明細'!F30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="17" customHeight="1" s="89">
+        <f>'03_見積明細'!F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1" s="91">
       <c r="B35" s="26" t="inlineStr">
         <is>
           <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1" s="89">
-      <c r="B36" s="88" t="inlineStr">
-        <is>
-          <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1" s="89">
-      <c r="B37" s="88" t="inlineStr">
+    <row r="36" ht="17" customHeight="1" s="91">
+      <c r="B36" s="104" t="inlineStr">
+        <is>
+          <t>・月額 保守・運用サービス 65,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 85,000円／月</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1" s="91">
+      <c r="B37" s="104" t="inlineStr">
         <is>
           <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1" s="89">
-      <c r="B38" s="88" t="inlineStr">
+    <row r="38" ht="17" customHeight="1" s="91">
+      <c r="B38" s="104" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
         </is>
@@ -1609,54 +1676,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="6" customWidth="1" style="89" min="1" max="1"/>
-    <col width="40" customWidth="1" style="89" min="2" max="2"/>
-    <col width="16" customWidth="1" style="89" min="3" max="3"/>
-    <col width="14" customWidth="1" style="89" min="4" max="4"/>
-    <col width="56" customWidth="1" style="89" min="5" max="5"/>
+    <col width="6" customWidth="1" style="91" min="1" max="1"/>
+    <col width="40" customWidth="1" style="91" min="2" max="2"/>
+    <col width="16" customWidth="1" style="91" min="3" max="3"/>
+    <col width="14" customWidth="1" style="91" min="4" max="4"/>
+    <col width="56" customWidth="1" style="91" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="89">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>前回お見積りからの増減内訳</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="89">
+    <row r="2" ht="17" customHeight="1" s="91">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>2026年9月8日付 SP-2026-0001（税抜 8,000,000円）から、今回のお見積りに至るまでの内訳です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="89">
-      <c r="A4" s="104" t="n"/>
-      <c r="B4" s="104" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="91">
+      <c r="A4" s="97" t="n"/>
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="97" t="inlineStr">
         <is>
           <t>増減</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="97" t="inlineStr">
         <is>
           <t>人日</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="97" t="inlineStr">
         <is>
           <t>理由・内容</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" s="89">
+    <row r="5" ht="17" customHeight="1" s="91">
       <c r="A5" s="16" t="n"/>
       <c r="B5" s="29" t="inlineStr">
         <is>
@@ -1675,7 +1742,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" s="89">
+    <row r="6" ht="34" customHeight="1" s="91">
       <c r="A6" s="31" t="inlineStr">
         <is>
           <t>①</t>
@@ -1696,7 +1763,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" s="89">
+    <row r="7" ht="34" customHeight="1" s="91">
       <c r="A7" s="36" t="inlineStr">
         <is>
           <t>②</t>
@@ -1719,7 +1786,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" s="89">
+    <row r="8" ht="34" customHeight="1" s="91">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>③</t>
@@ -1742,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" s="89">
+    <row r="9" ht="34" customHeight="1" s="91">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>④</t>
@@ -1763,292 +1830,364 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1" s="89">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="39" t="inlineStr">
+    <row r="10" ht="34" customHeight="1" s="91">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>在席確認（カメラ前からの離席検知）の追加</t>
+        </is>
+      </c>
+      <c r="C10" s="119" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D10" s="122" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>受講中はカメラ映像を端末内で判定し、離席したら再生を自動停止。離席時間は有効視聴時間から除外。今回の新規ご要望</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" s="91">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>受講中のランダム顔照合を再度組み入れ</t>
+        </is>
+      </c>
+      <c r="C11" s="119" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D11" s="122" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>③でいったん外したが、⑤のカメラ基盤を共用できるため7人日→4人日で実装可能。単独実装より350,000円→200,000円と安く戻せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>今回のお見積り（税抜）</t>
         </is>
       </c>
-      <c r="C10" s="123">
-        <f>C5+SUM(C6:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="124">
-        <f>'03_見積明細'!D21</f>
-        <v/>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>教材6科目＋システム103人日</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="89">
-      <c r="B11" s="93" t="inlineStr">
+      <c r="C12" s="123">
+        <f>C5+SUM(C6:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="124">
+        <f>'03_見積明細'!D23</f>
+        <v/>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>教材6科目＋システム125人日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="91">
+      <c r="B13" s="102" t="inlineStr">
         <is>
           <t>（検算）見積明細の小計＋調整額</t>
         </is>
       </c>
-      <c r="C11" s="125">
-        <f>'03_見積明細'!F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="89">
-      <c r="B13" s="43" t="inlineStr">
+      <c r="C13" s="125">
+        <f>'03_見積明細'!F30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1" s="91"/>
+    <row r="15" ht="17" customHeight="1" s="91">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>増減の内訳（金額の動き）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1" s="89">
-      <c r="B14" s="44" t="inlineStr">
+    <row r="16" ht="17" customHeight="1" s="91">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>減額の要因</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1" s="89">
-      <c r="B15" s="101" t="inlineStr">
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1" s="91">
+      <c r="B17" s="105" t="inlineStr">
         <is>
           <t>教材 4科目の削減</t>
         </is>
       </c>
-      <c r="C15" s="45" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
         <is>
           <t>▲1,200,000</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1" s="89">
-      <c r="B16" s="101" t="inlineStr">
-        <is>
-          <t>受講中ランダム照合の除外</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>▲350,000</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1" s="89">
-      <c r="B17" s="101" t="inlineStr">
-        <is>
-          <t>全額一括前払いによる調整</t>
-        </is>
-      </c>
-      <c r="C17" s="45" t="inlineStr">
-        <is>
-          <t>▲350,000</t>
         </is>
       </c>
       <c r="D17" s="19" t="n"/>
       <c r="E17" s="19" t="n"/>
     </row>
-    <row r="18" ht="17" customHeight="1" s="89">
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>▲1,900,000</t>
+    <row r="18" ht="17" customHeight="1" s="91">
+      <c r="B18" s="105" t="inlineStr">
+        <is>
+          <t>受講中ランダム照合の除外（③）</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>▲350,000</t>
         </is>
       </c>
       <c r="D18" s="19" t="n"/>
       <c r="E18" s="19" t="n"/>
     </row>
-    <row r="20" ht="17" customHeight="1" s="89">
-      <c r="B20" s="48" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="105" t="inlineStr">
+        <is>
+          <t>全額一括前払いによる調整</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>▲350,000</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1" s="91">
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>▲1,900,000</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="91"/>
+    <row r="22" ht="17" customHeight="1" s="91">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>増額の要因</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1" s="89">
-      <c r="B21" s="101" t="inlineStr">
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>決済機能（ゼウス連携）の追加</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C23" s="45" t="inlineStr">
         <is>
           <t>＋500,000</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1" s="89">
-      <c r="B22" s="46" t="inlineStr">
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1" s="91">
+      <c r="B24" s="105" t="inlineStr">
+        <is>
+          <t>在席確認の追加</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>＋900,000</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="105" t="inlineStr">
+        <is>
+          <t>受講中ランダム照合の再組入れ（⑥）</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>＋200,000</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1" s="91">
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C22" s="50" t="inlineStr">
-        <is>
-          <t>＋500,000</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1" s="89">
-      <c r="B24" s="51" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>＋1,600,000</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1" s="91"/>
+    <row r="28" ht="17" customHeight="1" s="91">
+      <c r="B28" s="53" t="inlineStr">
         <is>
           <t>差引</t>
         </is>
       </c>
-      <c r="C24" s="52" t="inlineStr">
-        <is>
-          <t>▲1,400,000</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>8,000,000 − 1,400,000 ＝ 6,600,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1" s="89">
-      <c r="B26" s="53" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>▲300,000</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>8,000,000 − 300,000 ＝ 7,700,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1" s="91">
+      <c r="B29" s="54" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1" s="91">
+      <c r="B30" s="54" t="inlineStr">
         <is>
           <t>■ このシートは社内資料です（先方には提出しません）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="89">
-      <c r="B27" s="54" t="inlineStr">
+    <row r="31" ht="17" customHeight="1" s="91">
+      <c r="B31" s="54" t="inlineStr">
         <is>
           <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="89">
-      <c r="B28" s="54" t="inlineStr">
-        <is>
-          <t>先方向けには「前回からの変更は受講中のランダム顔照合を外すことだけ」と説明し、</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1" s="89">
-      <c r="B29" s="54" t="inlineStr">
-        <is>
-          <t>下の④は見積書・注文書の上では「貴社特別値引き（特別値引き）」と表示しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1" s="89">
-      <c r="B30" s="54" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="89">
-      <c r="B31" s="55" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="91">
+      <c r="B32" s="54" t="inlineStr">
+        <is>
+          <t>③で外したランダム顔照合が⑥で戻っています。単純な出し戻しに見せないため、</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="91">
+      <c r="B33" s="54" t="inlineStr">
+        <is>
+          <t>「在席確認を入れるので、そのカメラを使ってランダム照合も安く足せる」という順序で説明してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1" s="91">
+      <c r="B34" s="54" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1" s="91">
+      <c r="B35" s="54" t="inlineStr">
         <is>
           <t>■ この表の使い方（社内の根拠整理）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1" s="89">
-      <c r="B32" s="54" t="inlineStr">
-        <is>
-          <t>単純な値引きではなく、次の3つの対価として金額が下がっていることを社内で説明できます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1" s="89">
-      <c r="B33" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　① 納品する教材が4科目減ること（成果物の減少）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17" customHeight="1" s="89">
-      <c r="B34" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　② 受講中のランダム照合を実装しないこと（機能の減少）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="17" customHeight="1" s="89">
-      <c r="B35" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　③ 全額を前払いいただくこと（支払条件の対価）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1" s="89">
-      <c r="B36" s="54" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1" s="89">
+    <row r="36" ht="17" customHeight="1" s="91">
+      <c r="B36" s="54" t="inlineStr">
+        <is>
+          <t>値上げの根拠は次の2点です。どちらも先方の新しいご要望に対応するものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1" s="91">
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>一方で、決済機能（ゼウス連携）は新しいご要望のため増額しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1" s="89">
-      <c r="B38" s="56" t="inlineStr">
-        <is>
-          <t>減る理由と増える理由の両方を示すことで、価格の根拠が明確になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1" s="89">
+          <t xml:space="preserve">　⑤ カメラ前からの離席を検知して再生を止める機能（18人日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1" s="91">
+      <c r="B38" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑥ 受講中のランダム顔照合（4人日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1" s="91">
       <c r="B39" s="54" t="n"/>
     </row>
-    <row r="40" ht="17" customHeight="1" s="89">
-      <c r="B40" s="55" t="inlineStr">
+    <row r="40" ht="17" customHeight="1" s="91">
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t>⑥は単独なら7人日・350,000円ですが、⑤のカメラ基盤を共用するため4人日・200,000円で済みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1" s="91">
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>「離席検知をやるなら、顔照合は半額強で付けられます」が一番の売り文句です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1" s="91">
+      <c r="B42" s="55" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1" s="91">
+      <c r="B43" s="54" t="inlineStr">
         <is>
           <t>■ 月額費用の変更</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1" s="89">
-      <c r="B41" s="54" t="inlineStr">
-        <is>
-          <t>保守・運用サービス　80,000円 → 60,000円（▲20,000円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1" s="89">
-      <c r="B42" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　受講中のランダム照合を実装しないため、照合結果の目視確認という運用作業がなくなります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="17" customHeight="1" s="89">
-      <c r="B43" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　運用工数が実際に減るため、その分を月額に反映しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="17" customHeight="1" s="89">
+    <row r="44" ht="17" customHeight="1" s="91">
       <c r="B44" s="54" t="inlineStr">
         <is>
+          <t>保守・運用サービス　60,000円 → 65,000円（＋5,000円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1" s="91">
+      <c r="B45" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　在席確認の離席ログ確認と、カメラが認識しない等の問い合わせ対応が増えるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ランダム照合の目視確認は在席確認の画面で一括して行えるため、＋20,000円ではなく＋5,000円で収まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="54" t="inlineStr">
+        <is>
           <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1" s="89">
-      <c r="B45" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　　　　　合計 80,000円／月（サーバー費を除く・税抜）</t>
+    <row r="48">
+      <c r="B48" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　合計 85,000円／月（サーバー費を除く・税抜）</t>
         </is>
       </c>
     </row>
@@ -2065,38 +2204,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" style="89" min="1" max="1"/>
-    <col width="28" customWidth="1" style="89" min="2" max="2"/>
-    <col width="54" customWidth="1" style="89" min="3" max="3"/>
-    <col width="9" customWidth="1" style="89" min="4" max="4"/>
-    <col width="12" customWidth="1" style="89" min="5" max="5"/>
-    <col width="14" customWidth="1" style="89" min="6" max="6"/>
+    <col width="12" customWidth="1" style="91" min="1" max="1"/>
+    <col width="28" customWidth="1" style="91" min="2" max="2"/>
+    <col width="54" customWidth="1" style="91" min="3" max="3"/>
+    <col width="9" customWidth="1" style="91" min="4" max="4"/>
+    <col width="12" customWidth="1" style="91" min="5" max="5"/>
+    <col width="14" customWidth="1" style="91" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="89">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>見積明細</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="89">
+    <row r="2" ht="17" customHeight="1" s="91">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>黄色のセルが編集箇所です。人日単価と各項目の人日を変えると、見積書・増減内訳・注文書まで自動で再計算されます。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" s="89">
+    <row r="4" ht="17" customHeight="1" s="91">
       <c r="A4" s="107" t="inlineStr">
         <is>
           <t>人日単価</t>
         </is>
       </c>
-      <c r="B4" s="92" t="n"/>
+      <c r="B4" s="94" t="n"/>
       <c r="C4" s="126" t="n">
         <v>50000</v>
       </c>
@@ -2106,51 +2245,51 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" s="89">
-      <c r="A6" s="104" t="inlineStr">
+    <row r="6" ht="22" customHeight="1" s="91">
+      <c r="A6" s="97" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="97" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D6" s="104" t="inlineStr">
+      <c r="D6" s="97" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E6" s="104" t="inlineStr">
+      <c r="E6" s="97" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
+      <c r="F6" s="97" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1" s="89">
+    <row r="7" ht="17" customHeight="1" s="91">
       <c r="A7" s="108" t="inlineStr">
         <is>
           <t>1. システム開発</t>
         </is>
       </c>
-      <c r="B7" s="91" t="n"/>
-      <c r="C7" s="91" t="n"/>
-      <c r="D7" s="91" t="n"/>
-      <c r="E7" s="91" t="n"/>
-      <c r="F7" s="92" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="89">
+      <c r="B7" s="93" t="n"/>
+      <c r="C7" s="93" t="n"/>
+      <c r="D7" s="93" t="n"/>
+      <c r="E7" s="93" t="n"/>
+      <c r="F7" s="94" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="91">
       <c r="A8" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2178,7 +2317,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="89">
+    <row r="9" ht="30" customHeight="1" s="91">
       <c r="A9" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2206,7 +2345,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="89">
+    <row r="10" ht="30" customHeight="1" s="91">
       <c r="A10" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2234,7 +2373,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="89">
+    <row r="11" ht="30" customHeight="1" s="91">
       <c r="A11" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2262,7 +2401,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="89">
+    <row r="12" ht="30" customHeight="1" s="91">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2290,7 +2429,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="89">
+    <row r="13" ht="30" customHeight="1" s="91">
       <c r="A13" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2318,7 +2457,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="89">
+    <row r="14" ht="30" customHeight="1" s="91">
       <c r="A14" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2346,7 +2485,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="89">
+    <row r="15" ht="30" customHeight="1" s="91">
       <c r="A15" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2374,7 +2513,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="89">
+    <row r="16" ht="30" customHeight="1" s="91">
       <c r="A16" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2402,7 +2541,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="89">
+    <row r="17" ht="30" customHeight="1" s="91">
       <c r="A17" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2430,7 +2569,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="89">
+    <row r="18" ht="30" customHeight="1" s="91">
       <c r="A18" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2458,7 +2597,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="89">
+    <row r="19" ht="30" customHeight="1" s="91">
       <c r="A19" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2486,7 +2625,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="89">
+    <row r="20" ht="30" customHeight="1" s="91">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>システム</t>
@@ -2514,223 +2653,282 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="89">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="29" t="inlineStr">
+    <row r="21" ht="30" customHeight="1" s="91">
+      <c r="A21" s="59" t="inlineStr">
+        <is>
+          <t>システム</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>在席確認（カメラ前からの離席検知）</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>受講中はカメラ映像を端末内で判定し、受講者が画面前から離れたら再生を自動停止。離席の開始と終了を記録し、有効視聴時間から除外。画像はサーバーへ送信しません</t>
+        </is>
+      </c>
+      <c r="D21" s="127" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" s="112">
+        <f>$C$4</f>
+        <v/>
+      </c>
+      <c r="F21" s="112">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="91">
+      <c r="A22" s="59" t="inlineStr">
+        <is>
+          <t>システム</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>受講中のランダム顔照合</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>受講中に予告なく静止画を取得し、登録時の顔と1:1照合。在席確認のカメラ基盤を共用するため、単独で実装する場合（7人日）より少ない工数で実現できます</t>
+        </is>
+      </c>
+      <c r="D22" s="127" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="112">
+        <f>$C$4</f>
+        <v/>
+      </c>
+      <c r="F22" s="112">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1" s="91">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="51" t="inlineStr">
         <is>
           <t>システム開発 小計</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="128">
-        <f>SUM(D8:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="114">
-        <f>SUM(F8:F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1" s="89">
-      <c r="A23" s="108" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="124">
+        <f>SUM(D8:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="117">
+        <f>SUM(F8:F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="91"/>
+    <row r="25">
+      <c r="A25" s="108" t="inlineStr">
         <is>
           <t>2. eラーニング教材の制作</t>
         </is>
       </c>
-      <c r="B23" s="91" t="n"/>
-      <c r="C23" s="91" t="n"/>
-      <c r="D23" s="91" t="n"/>
-      <c r="E23" s="91" t="n"/>
-      <c r="F23" s="92" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1" s="89">
-      <c r="A24" s="59" t="inlineStr">
+      <c r="B25" s="93" t="n"/>
+      <c r="C25" s="93" t="n"/>
+      <c r="D25" s="93" t="n"/>
+      <c r="E25" s="93" t="n"/>
+      <c r="F25" s="94" t="n"/>
+    </row>
+    <row r="26" ht="19" customHeight="1" s="91">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>教材</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>特別教育 学科教材の制作</t>
         </is>
       </c>
-      <c r="C24" s="35">
+      <c r="C26" s="35">
         <f>"6科目・学科"&amp;TEXT('04_教材科目'!$D$17,"0.0")&amp;"時間分。構成台本の書き起こし、スライド、図解、ナレーション、バーチャル講師映像、章末問題・修了確認テストの作成"</f>
         <v/>
       </c>
-      <c r="D24" s="129">
+      <c r="D26" s="129">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="E24" s="130">
+      <c r="E26" s="130">
         <f>'04_教材科目'!$D$4</f>
         <v/>
       </c>
-      <c r="F24" s="112">
+      <c r="F26" s="112">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1" s="89">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="51" t="inlineStr">
+    <row r="27" ht="17" customHeight="1" s="91"/>
+    <row r="28" ht="17" customHeight="1" s="91">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="51" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="124">
-        <f>D21</f>
-        <v/>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="117">
-        <f>F21+F24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1" s="89">
-      <c r="B27" s="64" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="124">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="117">
+        <f>F23+F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1" s="91">
+      <c r="B29" s="64" t="inlineStr">
         <is>
           <t>全額一括前払いによる調整</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>ご発注時に全額をお支払いいただく条件に対する調整額です</t>
         </is>
       </c>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="126" t="n">
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="126" t="n">
         <v>-350000</v>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="89">
-      <c r="B28" s="65" t="inlineStr">
+    <row r="30" ht="24" customHeight="1" s="91">
+      <c r="B30" s="65" t="inlineStr">
         <is>
           <t>差引 小計（税抜）</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="116">
-        <f>F26+F27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1" s="89">
-      <c r="B29" s="65" t="inlineStr">
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="116">
+        <f>F28+F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="65" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="D29" s="66" t="n">
+      <c r="D31" s="66" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="116">
-        <f>ROUND(F28*D29,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" s="89">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="116">
+        <f>ROUND(F30*D31,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="91">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>合計（税込）</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="123">
-        <f>F28+F29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1" s="89">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="123">
+        <f>F30+F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="91"/>
+    <row r="34" ht="17" customHeight="1" s="91">
+      <c r="A34" s="55" t="inlineStr">
         <is>
           <t>■ 今回の範囲から外したもの（第2次発注のご相談）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1" s="89">
-      <c r="A33" s="54" t="inlineStr">
-        <is>
-          <t>・受講中のランダム顔照合（受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17" customHeight="1" s="89">
-      <c r="A34" s="54" t="inlineStr">
+    <row r="35" ht="17" customHeight="1" s="91">
+      <c r="A35" s="54" t="inlineStr">
+        <is>
+          <t>・受講者どうしの掲示板・質疑応答機能（当面はメールで対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1" s="91">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>・企業管理ポータル（従業員の一括申込、進捗確認、修了者一覧のCSV出力）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1" s="89">
-      <c r="A35" s="54" t="inlineStr">
+    <row r="37" ht="17" customHeight="1" s="91">
+      <c r="A37" s="54" t="inlineStr">
         <is>
           <t>・運営管理画面の拡張（監査レポート出力、組織管理、売上・入金管理）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1" s="89">
-      <c r="A36" s="54" t="inlineStr">
+    <row r="38" ht="17" customHeight="1" s="91">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>・受講画面からの質疑応答機能（当面はメールで対応）</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1" s="89">
-      <c r="A37" s="54" t="inlineStr">
+    <row r="39" ht="17" customHeight="1" s="91">
+      <c r="A39" s="54" t="inlineStr">
         <is>
           <t>・修了証の真正性検証ページ（QRコード）</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1" s="89">
-      <c r="A38" s="54" t="inlineStr">
+    <row r="40" ht="17" customHeight="1" s="91">
+      <c r="A40" s="54" t="inlineStr">
         <is>
           <t>・教材 4科目（低圧電気、第2種酸欠、高所作業車、玉掛け）</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="17" customHeight="1" s="89">
-      <c r="A39" s="54" t="n"/>
-    </row>
-    <row r="40" ht="17" customHeight="1" s="89">
-      <c r="A40" s="55" t="inlineStr">
+    <row r="41" ht="17" customHeight="1" s="91">
+      <c r="A41" s="54" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1" s="91">
+      <c r="A42" s="55" t="inlineStr">
         <is>
           <t>■ 本見積に含まれないもの（別途）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1" s="89">
-      <c r="A41" s="54" t="inlineStr">
+    <row r="43" ht="17" customHeight="1" s="91">
+      <c r="A43" s="54" t="inlineStr">
         <is>
           <t>・月額の保守・運用サービスおよび法令改正監視・通知サービス（シート05）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1" s="89">
-      <c r="A42" s="54" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>・AWSの利用料（聖建様のご負担）、株式会社ゼウスとのご契約（初期費用無料・月額3,000円・決済手数料）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1" s="89">
-      <c r="A43" s="54" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="54" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂（1科目300,000円・都度発注）</t>
         </is>
@@ -2740,7 +2938,7 @@
   <mergeCells count="3">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -2757,29 +2955,29 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="9" customWidth="1" style="89" min="1" max="1"/>
-    <col width="7" customWidth="1" style="89" min="2" max="2"/>
-    <col width="32" customWidth="1" style="89" min="3" max="3"/>
-    <col width="8" customWidth="1" style="89" min="4" max="4"/>
-    <col width="38" customWidth="1" style="89" min="5" max="5"/>
-    <col width="14" customWidth="1" style="89" min="6" max="6"/>
+    <col width="9" customWidth="1" style="91" min="1" max="1"/>
+    <col width="7" customWidth="1" style="91" min="2" max="2"/>
+    <col width="32" customWidth="1" style="91" min="3" max="3"/>
+    <col width="8" customWidth="1" style="91" min="4" max="4"/>
+    <col width="38" customWidth="1" style="91" min="5" max="5"/>
+    <col width="14" customWidth="1" style="91" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="89">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>eラーニング教材 制作科目一覧（6科目）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="89">
+    <row r="2" ht="17" customHeight="1" s="91">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>A列に 1 を入れた科目が制作対象になります。10科目から6科目へ絞り込んだ状態です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" s="89">
+    <row r="4" ht="17" customHeight="1" s="91">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="107" t="inlineStr">
         <is>
@@ -2797,42 +2995,42 @@
       </c>
       <c r="F4" s="5" t="n"/>
     </row>
-    <row r="6" ht="32" customHeight="1" s="89">
-      <c r="A6" s="104" t="inlineStr">
+    <row r="6" ht="32" customHeight="1" s="91">
+      <c r="A6" s="97" t="inlineStr">
         <is>
           <t>制作
 (1で選択)</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>優先
 順位</t>
         </is>
       </c>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="97" t="inlineStr">
         <is>
           <t>特別教育の名称</t>
         </is>
       </c>
-      <c r="D6" s="104" t="inlineStr">
+      <c r="D6" s="97" t="inlineStr">
         <is>
           <t>学科
 (時間)</t>
         </is>
       </c>
-      <c r="E6" s="104" t="inlineStr">
+      <c r="E6" s="97" t="inlineStr">
         <is>
           <t>選定・除外の理由</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
+      <c r="F6" s="97" t="inlineStr">
         <is>
           <t>制作費</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1" s="89">
+    <row r="7" ht="26" customHeight="1" s="91">
       <c r="A7" s="67" t="n">
         <v>1</v>
       </c>
@@ -2857,7 +3055,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1" s="89">
+    <row r="8" ht="26" customHeight="1" s="91">
       <c r="A8" s="67" t="n">
         <v>1</v>
       </c>
@@ -2882,7 +3080,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1" s="89">
+    <row r="9" ht="26" customHeight="1" s="91">
       <c r="A9" s="67" t="n">
         <v>1</v>
       </c>
@@ -2907,7 +3105,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1" s="89">
+    <row r="10" ht="26" customHeight="1" s="91">
       <c r="A10" s="67" t="n">
         <v>0</v>
       </c>
@@ -2932,7 +3130,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1" s="89">
+    <row r="11" ht="26" customHeight="1" s="91">
       <c r="A11" s="67" t="n">
         <v>1</v>
       </c>
@@ -2957,7 +3155,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1" s="89">
+    <row r="12" ht="26" customHeight="1" s="91">
       <c r="A12" s="67" t="n">
         <v>1</v>
       </c>
@@ -2982,7 +3180,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1" s="89">
+    <row r="13" ht="26" customHeight="1" s="91">
       <c r="A13" s="67" t="n">
         <v>1</v>
       </c>
@@ -3007,7 +3205,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1" s="89">
+    <row r="14" ht="26" customHeight="1" s="91">
       <c r="A14" s="67" t="n">
         <v>0</v>
       </c>
@@ -3032,7 +3230,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1" s="89">
+    <row r="15" ht="26" customHeight="1" s="91">
       <c r="A15" s="67" t="n">
         <v>0</v>
       </c>
@@ -3057,7 +3255,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1" s="89">
+    <row r="16" ht="26" customHeight="1" s="91">
       <c r="A16" s="67" t="n">
         <v>0</v>
       </c>
@@ -3082,7 +3280,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="17" customHeight="1" s="89">
+    <row r="17" ht="17" customHeight="1" s="91">
       <c r="A17" s="133">
         <f>SUM(A7:A16)</f>
         <v/>
@@ -3103,35 +3301,35 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1" s="89">
+    <row r="19" ht="17" customHeight="1" s="91">
       <c r="A19" s="55" t="inlineStr">
         <is>
           <t>■ 選定の考え方</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1" s="89">
+    <row r="20" ht="17" customHeight="1" s="91">
       <c r="A20" s="54" t="inlineStr">
         <is>
           <t>・実技の定めがない科目（足場・石綿・特定粉じん）を優先し、最短で販売を開始できるようにしています。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="89">
+    <row r="21" ht="17" customHeight="1" s="91">
       <c r="A21" s="54" t="inlineStr">
         <is>
           <t>・アーク溶接等は既存の制作資産があるため、優先して商品化します。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1" s="89">
+    <row r="22" ht="17" customHeight="1" s="91">
       <c r="A22" s="54" t="inlineStr">
         <is>
           <t>・除外した4科目は、学科時間が長いか対象職種が限定的なものです。第2次発注でのご検討をお願いします。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1" s="89">
+    <row r="23" ht="17" customHeight="1" s="91">
       <c r="A23" s="54" t="inlineStr">
         <is>
           <t>・A列の 1 と 0 を入れ替えれば、対象科目を自由に変更できます（見積金額も自動で追随します）。</t>
@@ -3155,49 +3353,49 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="16" customWidth="1" style="89" min="1" max="1"/>
-    <col width="32" customWidth="1" style="89" min="2" max="2"/>
-    <col width="16" customWidth="1" style="89" min="3" max="3"/>
-    <col width="66" customWidth="1" style="89" min="4" max="4"/>
+    <col width="16" customWidth="1" style="91" min="1" max="1"/>
+    <col width="32" customWidth="1" style="91" min="2" max="2"/>
+    <col width="16" customWidth="1" style="91" min="3" max="3"/>
+    <col width="66" customWidth="1" style="91" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="89">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>月額費用と別途費用</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="89">
+    <row r="2" ht="17" customHeight="1" s="91">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>初期費用（シート01）とは別に、下記が発生します。金額はすべて税抜です。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="89">
-      <c r="A4" s="104" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="91">
+      <c r="A4" s="97" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B4" s="104" t="inlineStr">
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="97" t="inlineStr">
         <is>
           <t>月額／単価</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="97" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1" s="89">
+    <row r="5" ht="46" customHeight="1" s="91">
       <c r="A5" s="75" t="inlineStr">
         <is>
           <t>弊社へ
@@ -3210,15 +3408,15 @@
         </is>
       </c>
       <c r="C5" s="126" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D5" s="90" t="inlineStr">
-        <is>
-          <t>システムの死活監視とエラー監視、障害対応、軽微な改修、受講者からの問い合わせ一次対応、月次レポート。受講中のランダム照合を実装しないため、照合結果の目視確認が不要となり、前回の80,000円から減額しています</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1" s="89">
+        <v>65000</v>
+      </c>
+      <c r="D5" s="95" t="inlineStr">
+        <is>
+          <t>システムの死活監視とエラー監視、障害対応、軽微な改修、受講者からの問い合わせ一次対応、月次レポート。在席確認の離席ログの確認と、カメラが認識しない等の問い合わせ対応が加わるため、前回の60,000円から5,000円増としています</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" s="91">
       <c r="A6" s="16" t="n"/>
       <c r="B6" s="65" t="inlineStr">
         <is>
@@ -3228,13 +3426,13 @@
       <c r="C6" s="126" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="90" t="inlineStr">
+      <c r="D6" s="95" t="inlineStr">
         <is>
           <t>月2回（月初・月中）、官報・厚生労働省の通達・パブリックコメントを確認。対象6科目に影響しうる改正を検知したら、聖建様と弊社の双方へ自動でメール通知。月次で「該当なし」も含めて報告</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="89">
+    <row r="7" ht="20" customHeight="1" s="91">
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="51" t="inlineStr">
         <is>
@@ -3247,11 +3445,11 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>聖建様のご指定額です</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" s="89">
+          <t>聖建様のご指定額です（85,000円／月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="91">
       <c r="A9" s="75" t="inlineStr">
         <is>
           <t>お客様
@@ -3266,13 +3464,13 @@
       <c r="C9" s="126" t="n">
         <v>22800</v>
       </c>
-      <c r="D9" s="90" t="inlineStr">
+      <c r="D9" s="95" t="inlineStr">
         <is>
           <t>EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch。聖建様名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" s="89">
+    <row r="10" ht="28" customHeight="1" s="91">
       <c r="A10" s="16" t="n"/>
       <c r="B10" s="65" t="inlineStr">
         <is>
@@ -3284,13 +3482,13 @@
           <t>実費</t>
         </is>
       </c>
-      <c r="D10" s="90" t="inlineStr">
+      <c r="D10" s="95" t="inlineStr">
         <is>
           <t>顔照合API、ライブネス判定、CDN転送、メール送信。受講者100名／月で約600円（AWS利用料に含まれます）</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1" s="89">
+    <row r="11" ht="32" customHeight="1" s="91">
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="65" t="inlineStr">
         <is>
@@ -3300,13 +3498,13 @@
       <c r="C11" s="126" t="n">
         <v>3000</v>
       </c>
-      <c r="D11" s="90" t="inlineStr">
+      <c r="D11" s="95" t="inlineStr">
         <is>
           <t>初期費用は無料。月額3,000円。クレジットカード決済手数料は最大3.5%（売上に応じて発生）。聖建様が直接ご契約いただきます</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="89">
+    <row r="13" ht="30" customHeight="1" s="91">
       <c r="A13" s="75" t="inlineStr">
         <is>
           <t>都度
@@ -3322,13 +3520,13 @@
         <f>'04_教材科目'!D4</f>
         <v/>
       </c>
-      <c r="D13" s="90" t="inlineStr">
+      <c r="D13" s="95" t="inlineStr">
         <is>
           <t>1科目あたり。新規制作と同額です。台本の修正、該当部分の動画の再生成と差し替え、教材の版の更新を含みます</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1" s="89">
+    <row r="14" ht="28" customHeight="1" s="91">
       <c r="A14" s="16" t="n"/>
       <c r="B14" s="65" t="inlineStr">
         <is>
@@ -3339,20 +3537,20 @@
         <f>'04_教材科目'!D4</f>
         <v/>
       </c>
-      <c r="D14" s="90" t="inlineStr">
+      <c r="D14" s="95" t="inlineStr">
         <is>
           <t>低圧電気、第2種酸欠、高所作業車、玉掛けの4科目。1科目あたり300,000円</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1" s="89">
+    <row r="16" ht="19" customHeight="1" s="91">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>参考：月額の合計（聖建様のご負担総額）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" s="89">
+    <row r="17" ht="20" customHeight="1" s="91">
       <c r="B17" s="65" t="inlineStr">
         <is>
           <t>弊社サービス ＋ AWS ＋ ゼウス月額</t>
@@ -3368,73 +3566,73 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1" s="89">
+    <row r="19" ht="17" customHeight="1" s="91">
       <c r="A19" s="55" t="inlineStr">
         <is>
-          <t>■ 月額80,000円の根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1" s="89">
+          <t>■ 月額85,000円の根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1" s="91">
       <c r="A20" s="54" t="inlineStr">
         <is>
-          <t>聖建様のご指定額（サーバー費を除く月額80,000円）にあわせ、内訳を次のとおり組みました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="17" customHeight="1" s="89">
+          <t>聖建様のご指定額（サーバー費を除く月額85,000円）にあわせ、内訳を次のとおり組みました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="91">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>・保守・運用サービス　60,000円　… 受講中のランダム照合を実装しないため、照合結果の</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1" s="89">
+          <t>・保守・運用サービス　65,000円　… 在席確認の離席ログ確認と問い合わせ対応の増加分を反映しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1" s="91">
       <c r="A22" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　目視確認という運用作業がなくなります。その分を減額しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1" s="89">
+          <t xml:space="preserve">　　ランダム顔照合の目視確認は在席確認の画面で一括して行えるため、+20,000円ではなく+5,000円に収まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1" s="91">
       <c r="A23" s="54" t="inlineStr">
         <is>
           <t>・法令改正監視・通知サービス　20,000円　… 前回から変更ありません。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="17" customHeight="1" s="89">
+    <row r="24" ht="17" customHeight="1" s="91">
       <c r="A24" s="54" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1" s="89">
+    <row r="25" ht="17" customHeight="1" s="91">
       <c r="A25" s="55" t="inlineStr">
         <is>
           <t>■ ゼウスについて</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="17" customHeight="1" s="89">
+    <row r="26" ht="17" customHeight="1" s="91">
       <c r="A26" s="54" t="inlineStr">
         <is>
           <t>・株式会社ゼウス（1994年設立・国内の決済代行事業者）との契約は聖建様が直接行っていただきます。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="89">
+    <row r="27" ht="17" customHeight="1" s="91">
       <c r="A27" s="54" t="inlineStr">
         <is>
           <t>・初期費用は無料、月額3,000円、クレジットカード決済手数料は最大3.5%です（2026年9月時点）。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1" s="89">
+    <row r="28" ht="17" customHeight="1" s="91">
       <c r="A28" s="54" t="inlineStr">
         <is>
           <t>・接続方式はデータ転送（API）型を想定しています。申込から入金確認、受講開始までを自動化します。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1" s="89">
+    <row r="29" ht="17" customHeight="1" s="91">
       <c r="A29" s="53" t="inlineStr">
         <is>
           <t>・最新の料金と条件は、ご契約前にゼウス社へ直接ご確認ください。</t>
@@ -3457,36 +3655,36 @@
   <dimension ref="B2:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" style="89" min="1" max="1"/>
-    <col width="20" customWidth="1" style="89" min="2" max="2"/>
-    <col width="24" customWidth="1" style="89" min="3" max="3"/>
-    <col width="14" customWidth="1" style="89" min="4" max="4"/>
-    <col width="16" customWidth="1" style="89" min="5" max="5"/>
-    <col width="18" customWidth="1" style="89" min="6" max="6"/>
-    <col width="3" customWidth="1" style="89" min="7" max="7"/>
+    <col width="3" customWidth="1" style="91" min="1" max="1"/>
+    <col width="20" customWidth="1" style="91" min="2" max="2"/>
+    <col width="24" customWidth="1" style="91" min="3" max="3"/>
+    <col width="14" customWidth="1" style="91" min="4" max="4"/>
+    <col width="16" customWidth="1" style="91" min="5" max="5"/>
+    <col width="18" customWidth="1" style="91" min="6" max="6"/>
+    <col width="3" customWidth="1" style="91" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" s="89">
-      <c r="B2" s="97" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="91">
+      <c r="B2" s="100" t="inlineStr">
         <is>
           <t>注　文　書</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="89">
-      <c r="B4" s="93" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="91">
+      <c r="B4" s="102" t="inlineStr">
         <is>
           <t>注文番号</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SP-2026-0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="89">
-      <c r="B5" s="93" t="inlineStr">
+          <t>SP-2026-0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="91">
+      <c r="B5" s="102" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
@@ -3497,121 +3695,121 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1" s="89">
-      <c r="B7" s="99" t="inlineStr">
+    <row r="7" ht="25" customHeight="1" s="91">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>株式会社スペリオル　御中</t>
         </is>
       </c>
-      <c r="E7" s="95" t="inlineStr">
+      <c r="E7" s="101" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" s="89">
-      <c r="B8" s="93" t="inlineStr">
+    <row r="8" ht="22" customHeight="1" s="91">
+      <c r="B8" s="102" t="inlineStr">
         <is>
           <t>〒464-0075　名古屋市千種区内山3-18-10</t>
         </is>
       </c>
-      <c r="E8" s="100" t="inlineStr">
+      <c r="E8" s="110" t="inlineStr">
         <is>
           <t>株式会社聖建</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="89">
-      <c r="B9" s="93" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="91">
+      <c r="B9" s="102" t="inlineStr">
         <is>
           <t>TEL 052-745-6607　／　登録番号 T9180001048541</t>
         </is>
       </c>
-      <c r="E9" s="95" t="inlineStr">
+      <c r="E9" s="101" t="inlineStr">
         <is>
           <t>〒475-0805　愛知県半田市浜田町1丁目7番地</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17" customHeight="1" s="89">
+    <row r="10" ht="17" customHeight="1" s="91">
       <c r="B10" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
       </c>
-      <c r="E10" s="95" t="inlineStr">
+      <c r="E10" s="101" t="inlineStr">
         <is>
           <t>TEL 0569-84-9669</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="89">
-      <c r="E11" s="98" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="91">
+      <c r="E11" s="109" t="inlineStr">
         <is>
           <t>ご担当　　　　　　　　　　　　　　印</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="17" customHeight="1" s="89">
-      <c r="B13" s="96" t="inlineStr">
+    <row r="13" ht="17" customHeight="1" s="91">
+      <c r="B13" s="103" t="inlineStr">
         <is>
           <t>下記のとおり注文いたします。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="89">
+    <row r="15" ht="30" customHeight="1" s="91">
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C15" s="106" t="inlineStr">
         <is>
           <t>建設業 特別教育 eラーニング配信システム 構築 および 教材制作（6科目）一式</t>
         </is>
       </c>
-      <c r="D15" s="91" t="n"/>
-      <c r="E15" s="91" t="n"/>
-      <c r="F15" s="92" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1" s="89">
+      <c r="D15" s="93" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="94" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="91">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>根拠見積</t>
         </is>
       </c>
-      <c r="C16" s="90">
+      <c r="C16" s="95">
         <f>'01_見積書'!C4&amp;"（"&amp;'01_見積書'!C5&amp;" 発行）"</f>
         <v/>
       </c>
-      <c r="D16" s="91" t="n"/>
-      <c r="E16" s="91" t="n"/>
-      <c r="F16" s="92" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" s="89">
-      <c r="B18" s="104" t="inlineStr">
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="94" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="91">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C18" s="104" t="inlineStr">
+      <c r="C18" s="97" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D18" s="104" t="inlineStr">
+      <c r="D18" s="97" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E18" s="104" t="n"/>
-      <c r="F18" s="104" t="inlineStr">
+      <c r="E18" s="97" t="n"/>
+      <c r="F18" s="97" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" s="89">
+    <row r="19" ht="28" customHeight="1" s="91">
       <c r="B19" s="9" t="inlineStr">
         <is>
           <t>システム開発</t>
@@ -3619,7 +3817,7 @@
       </c>
       <c r="C19" s="78" t="inlineStr">
         <is>
-          <t>配信基盤・視聴整合性・本人確認・修了証発行・決済</t>
+          <t>配信基盤・視聴整合性・本人確認・在席確認・修了証発行</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -3629,11 +3827,11 @@
       </c>
       <c r="E19" s="19" t="n"/>
       <c r="F19" s="112">
-        <f>'03_見積明細'!F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" s="89">
+        <f>'03_見積明細'!F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" s="91">
       <c r="B20" s="9" t="inlineStr">
         <is>
           <t>教材制作</t>
@@ -3654,7 +3852,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1" s="89">
+    <row r="21" ht="17" customHeight="1" s="91">
       <c r="B21" s="29" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
@@ -3668,7 +3866,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1" s="89">
+    <row r="22" ht="17" customHeight="1" s="91">
       <c r="B22" s="64" t="inlineStr">
         <is>
           <t>特別値引き</t>
@@ -3678,11 +3876,11 @@
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="19" t="n"/>
       <c r="F22" s="115">
-        <f>'03_見積明細'!F27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1" s="89">
+        <f>'03_見積明細'!F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1" s="91">
       <c r="B23" s="65" t="inlineStr">
         <is>
           <t>消費税</t>
@@ -3690,7 +3888,7 @@
       </c>
       <c r="C23" s="79" t="n"/>
       <c r="D23" s="80">
-        <f>'03_見積明細'!D29</f>
+        <f>'03_見積明細'!D31</f>
         <v/>
       </c>
       <c r="E23" s="19" t="n"/>
@@ -3699,7 +3897,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1" s="89">
+    <row r="24" ht="26" customHeight="1" s="91">
       <c r="B24" s="39" t="inlineStr">
         <is>
           <t>ご注文金額（税込）</t>
@@ -3713,89 +3911,89 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1" s="89">
+    <row r="26" ht="42" customHeight="1" s="91">
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>納期</t>
         </is>
       </c>
-      <c r="C26" s="90" t="inlineStr">
+      <c r="C26" s="95" t="inlineStr">
         <is>
           <t>システム：ご発注後 約4か月　／　教材：第1次3科目 約4か月、第2次3科目 約7か月</t>
         </is>
       </c>
-      <c r="D26" s="91" t="n"/>
-      <c r="E26" s="91" t="n"/>
-      <c r="F26" s="92" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" s="89">
+      <c r="D26" s="93" t="n"/>
+      <c r="E26" s="93" t="n"/>
+      <c r="F26" s="94" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="91">
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>納入場所</t>
         </is>
       </c>
-      <c r="C27" s="90" t="inlineStr">
+      <c r="C27" s="95" t="inlineStr">
         <is>
           <t>貴社ご指定のサーバー環境</t>
         </is>
       </c>
-      <c r="D27" s="91" t="n"/>
-      <c r="E27" s="91" t="n"/>
-      <c r="F27" s="92" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" s="89">
+      <c r="D27" s="93" t="n"/>
+      <c r="E27" s="93" t="n"/>
+      <c r="F27" s="94" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="91">
       <c r="B28" s="4" t="inlineStr">
         <is>
           <t>検収条件</t>
         </is>
       </c>
-      <c r="C28" s="90" t="inlineStr">
+      <c r="C28" s="95" t="inlineStr">
         <is>
           <t>納品後14日以内に検収。期間内にご連絡なき場合は検収完了とみなします。</t>
         </is>
       </c>
-      <c r="D28" s="91" t="n"/>
-      <c r="E28" s="91" t="n"/>
-      <c r="F28" s="92" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1" s="89">
+      <c r="D28" s="93" t="n"/>
+      <c r="E28" s="93" t="n"/>
+      <c r="F28" s="94" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="91">
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
-      <c r="C29" s="90" t="inlineStr">
+      <c r="C29" s="95" t="inlineStr">
         <is>
           <t>2026年9月29日までに、上記ご注文金額の全額を一括でお支払いいたします。</t>
         </is>
       </c>
-      <c r="D29" s="91" t="n"/>
-      <c r="E29" s="91" t="n"/>
-      <c r="F29" s="92" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="89">
+      <c r="D29" s="93" t="n"/>
+      <c r="E29" s="93" t="n"/>
+      <c r="F29" s="94" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="91">
       <c r="B31" s="26" t="inlineStr">
         <is>
           <t>■ 別途ご負担いただく費用（いずれも税抜）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1" s="89">
-      <c r="B32" s="88" t="inlineStr">
-        <is>
-          <t>・月額 保守・運用サービス 60,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 80,000円／月</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1" s="89">
-      <c r="B33" s="88" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="91">
+      <c r="B32" s="104" t="inlineStr">
+        <is>
+          <t>・月額 保守・運用サービス 65,000円 ＋ 法令改正監視・通知サービス 20,000円　合計 85,000円／月</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="91">
+      <c r="B33" s="104" t="inlineStr">
         <is>
           <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1" s="89">
-      <c r="B34" s="88" t="inlineStr">
+    <row r="34" ht="17" customHeight="1" s="91">
+      <c r="B34" s="104" t="inlineStr">
         <is>
           <t>・法令改正にともなう教材の改訂　1科目 300,000円（都度発注）</t>
         </is>
@@ -3815,12 +4013,12 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -3837,12 +4035,12 @@
   <dimension ref="B1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="3" customWidth="1" style="89" min="1" max="1"/>
-    <col width="30" customWidth="1" style="89" min="2" max="2"/>
-    <col width="88" customWidth="1" style="89" min="3" max="3"/>
+    <col width="3" customWidth="1" style="91" min="1" max="1"/>
+    <col width="30" customWidth="1" style="91" min="2" max="2"/>
+    <col width="88" customWidth="1" style="91" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="89">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="B1" s="85" t="inlineStr">
         <is>
           <t>聖建様　見積前提条件</t>
@@ -3854,7 +4052,7 @@
       <c r="B2" s="86" t="n"/>
       <c r="C2" s="86" t="n"/>
     </row>
-    <row r="3" ht="20" customHeight="1" s="89">
+    <row r="3" ht="20" customHeight="1" s="91">
       <c r="B3" s="82" t="inlineStr">
         <is>
           <t>■ 1. 本見積に含まれるもの</t>
@@ -3862,49 +4060,49 @@
       </c>
       <c r="C3" s="83" t="n"/>
     </row>
-    <row r="4" ht="31" customHeight="1" s="89">
+    <row r="4" ht="31" customHeight="1" s="91">
       <c r="B4" s="87" t="inlineStr">
         <is>
           <t>システム開発</t>
         </is>
       </c>
-      <c r="C4" s="90" t="inlineStr">
-        <is>
-          <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、確認問題、修了判定、修了証の発行、決済機能、受講者ポータル、運営管理画面の基本機能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" s="89">
+      <c r="C4" s="95" t="inlineStr">
+        <is>
+          <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、在席確認（カメラ前からの離席検知）、受講中のランダム顔照合、確認問題、修了判定、修了証の発行、受講者ポータル、運営管理画面の基本機能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" s="91">
       <c r="B5" s="87" t="inlineStr">
         <is>
           <t>教材制作</t>
         </is>
       </c>
-      <c r="C5" s="90" t="inlineStr">
+      <c r="C5" s="95" t="inlineStr">
         <is>
           <t>特別教育 学科教材 6科目。構成台本、スライド、図解、ナレーション、章末問題・修了確認。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" s="89">
+    <row r="6" ht="34" customHeight="1" s="91">
       <c r="B6" s="87" t="inlineStr">
         <is>
           <t>修了証</t>
         </is>
       </c>
-      <c r="C6" s="90" t="inlineStr">
+      <c r="C6" s="95" t="inlineStr">
         <is>
           <t>修了証PDFの自動発行、再発行、受講者によるダウンロード。記載項目は受講者氏名、科目、法定学科時間、有効視聴時間、テスト得点、講師名、発行者、証明書番号。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" s="89">
+    <row r="7" ht="22" customHeight="1" s="91">
       <c r="B7" s="87" t="inlineStr">
         <is>
           <t>サーバー環境の構築</t>
         </is>
       </c>
-      <c r="C7" s="90" t="inlineStr">
+      <c r="C7" s="95" t="inlineStr">
         <is>
           <t>本番運用に耐える構成で構築します。データベースは冗長化し、日次のバックアップを取得します。</t>
         </is>
@@ -3914,70 +4112,70 @@
       <c r="B8" s="86" t="n"/>
       <c r="C8" s="86" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1" s="89">
+    <row r="9" ht="20" customHeight="1" s="91">
       <c r="B9" s="84" t="inlineStr">
         <is>
-          <t>■ 2. 本見積に含まれないもの（別途）</t>
+          <t>■ 2. 在席確認について／本見積に含まれないもの（別途）</t>
         </is>
       </c>
       <c r="C9" s="83" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1" s="89">
-      <c r="B10" s="109" t="inlineStr">
-        <is>
-          <t>受講中のランダム顔照合</t>
-        </is>
-      </c>
-      <c r="C10" s="110" t="inlineStr">
-        <is>
-          <t>受講の途中で予告なく撮影し、本人が継続して受講しているかを確認する機能は含みません。
-登録時の本人確認と受講開始時の顔照合は実装します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="23" customHeight="1" s="89">
+    <row r="10" ht="34" customHeight="1" s="91">
+      <c r="B10" s="88" t="inlineStr">
+        <is>
+          <t>在席確認の方式</t>
+        </is>
+      </c>
+      <c r="C10" s="89" t="inlineStr">
+        <is>
+          <t>カメラ映像の判定は受講者の端末内で行い、映像・画像をサーバーへ送信しません。
+離席を検知すると再生を自動停止し、離席していた時間は有効視聴時間から除外します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1" s="91">
       <c r="B11" s="87" t="inlineStr">
         <is>
           <t>月額サービス</t>
         </is>
       </c>
-      <c r="C11" s="90" t="inlineStr">
-        <is>
-          <t>保守・運用サービス 60,000円／月、法令改正監視・通知サービス 20,000円／月。合計80,000円／月（税抜）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" s="89">
+      <c r="C11" s="95" t="inlineStr">
+        <is>
+          <t>保守・運用サービス 65,000円／月、法令改正監視・通知サービス 20,000円／月。合計85,000円／月（税抜）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="91">
       <c r="B12" s="87" t="inlineStr">
         <is>
           <t>サーバー利用料</t>
         </is>
       </c>
-      <c r="C12" s="90" t="inlineStr">
+      <c r="C12" s="95" t="inlineStr">
         <is>
           <t>貴社のご負担とします。月額20,000円程度（税抜）。貴社名義でのご契約をお願いします。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" s="89">
+    <row r="13" ht="22" customHeight="1" s="91">
       <c r="B13" s="87" t="inlineStr">
         <is>
           <t>教材の改訂・追加</t>
         </is>
       </c>
-      <c r="C13" s="90" t="inlineStr">
+      <c r="C13" s="95" t="inlineStr">
         <is>
           <t>1科目300,000円（都度発注）。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" s="89">
+    <row r="14" ht="22" customHeight="1" s="91">
       <c r="B14" s="87" t="inlineStr">
         <is>
           <t>教材の監修</t>
         </is>
       </c>
-      <c r="C14" s="90" t="inlineStr">
+      <c r="C14" s="95" t="inlineStr">
         <is>
           <t>内容の監修は貴社の社内有資格者が担われる前提です。</t>
         </is>
@@ -3987,7 +4185,7 @@
       <c r="B15" s="86" t="n"/>
       <c r="C15" s="86" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1" s="89">
+    <row r="16" ht="20" customHeight="1" s="91">
       <c r="B16" s="82" t="inlineStr">
         <is>
           <t>■ 3. 責任の分担</t>
@@ -3995,37 +4193,37 @@
       </c>
       <c r="C16" s="83" t="n"/>
     </row>
-    <row r="17" ht="34" customHeight="1" s="89">
+    <row r="17" ht="34" customHeight="1" s="91">
       <c r="B17" s="87" t="inlineStr">
         <is>
           <t>弊社が保証すること</t>
         </is>
       </c>
-      <c r="C17" s="90" t="inlineStr">
+      <c r="C17" s="95" t="inlineStr">
         <is>
           <t>教材が安全衛生特別教育規程の定める科目・範囲・時間を満たすこと（監修者名を明示）。受講記録を証明可能な形で保存・出力できること。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1" s="89">
+    <row r="18" ht="34" customHeight="1" s="91">
       <c r="B18" s="87" t="inlineStr">
         <is>
           <t>弊社が保証しないこと</t>
         </is>
       </c>
-      <c r="C18" s="90" t="inlineStr">
+      <c r="C18" s="95" t="inlineStr">
         <is>
           <t>受講者の所属事業者が負う労働安全衛生法第59条第3項の実施義務が果たされたこと。労働災害が発生しないこと。行政機関が個別の事案において本教材を適法と判断すること。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1" s="89">
+    <row r="19" ht="34" customHeight="1" s="91">
       <c r="B19" s="87" t="inlineStr">
         <is>
           <t>法令改正への対応</t>
         </is>
       </c>
-      <c r="C19" s="90" t="inlineStr">
+      <c r="C19" s="95" t="inlineStr">
         <is>
           <t>弊社は官報・通達を監視し、該当しうる改正を自動でメール通知します。その改正が教材のどこに影響するかの判断は、貴社の監修者が行うものとします。</t>
         </is>
@@ -4035,7 +4233,7 @@
       <c r="B20" s="86" t="n"/>
       <c r="C20" s="86" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1" s="89">
+    <row r="21" ht="20" customHeight="1" s="91">
       <c r="B21" s="82" t="inlineStr">
         <is>
           <t>■ 4. 金額の前提</t>
@@ -4043,37 +4241,37 @@
       </c>
       <c r="C21" s="83" t="n"/>
     </row>
-    <row r="22" ht="22" customHeight="1" s="89">
+    <row r="22" ht="22" customHeight="1" s="91">
       <c r="B22" s="87" t="inlineStr">
         <is>
           <t>教材制作単価</t>
         </is>
       </c>
-      <c r="C22" s="90" t="inlineStr">
+      <c r="C22" s="95" t="inlineStr">
         <is>
           <t>300,000円／科目。貴社ご指定の単価です。改訂・追加時も同額を適用します。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1" s="89">
+    <row r="23" ht="22" customHeight="1" s="91">
       <c r="B23" s="87" t="inlineStr">
         <is>
           <t>支払条件</t>
         </is>
       </c>
-      <c r="C23" s="90" t="inlineStr">
+      <c r="C23" s="95" t="inlineStr">
         <is>
           <t>2026年9月29日までに全額を一括でお支払いいただくことを前提とした金額です。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1" s="89">
+    <row r="24" ht="22" customHeight="1" s="91">
       <c r="B24" s="87" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
       </c>
-      <c r="C24" s="90" t="inlineStr">
+      <c r="C24" s="95" t="inlineStr">
         <is>
           <t>発行日より30日間。</t>
         </is>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -16,12 +16,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'01_見積書'!$A$1:$F$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$49</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'04_教材科目'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05_月額・別途費用'!$A$1:$D$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$28</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="C17" s="111">
-        <f>'03_見積明細'!F30</f>
+        <f>'03_見積明細'!F29</f>
         <v/>
       </c>
       <c r="D17" s="93" t="n"/>
@@ -1384,7 +1384,7 @@
     <row r="18" ht="20" customHeight="1" s="91">
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="99">
-        <f>"消費税 ¥"&amp;TEXT('03_見積明細'!F31,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT('03_見積明細'!F32,"#,##0")</f>
+        <f>"消費税 ¥"&amp;TEXT('03_見積明細'!F30,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT('03_見積明細'!F31,"#,##0")</f>
         <v/>
       </c>
       <c r="D18" s="93" t="n"/>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="F27" s="112">
-        <f>'03_見積明細'!F23</f>
+        <f>'03_見積明細'!F22</f>
         <v/>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       <c r="D29" s="16" t="n"/>
       <c r="E29" s="16" t="n"/>
       <c r="F29" s="114">
-        <f>'03_見積明細'!F28</f>
+        <f>'03_見積明細'!F27</f>
         <v/>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="D30" s="19" t="n"/>
       <c r="E30" s="19" t="n"/>
       <c r="F30" s="115">
-        <f>'03_見積明細'!F29</f>
+        <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="D31" s="19" t="n"/>
       <c r="E31" s="19" t="n"/>
       <c r="F31" s="116">
-        <f>'03_見積明細'!F30</f>
+        <f>'03_見積明細'!F29</f>
         <v/>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="n"/>
       <c r="F32" s="116">
-        <f>'03_見積明細'!F31</f>
+        <f>'03_見積明細'!F30</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="117">
-        <f>'03_見積明細'!F32</f>
+        <f>'03_見積明細'!F31</f>
         <v/>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" style="91" min="1" max="1"/>
@@ -1764,25 +1764,25 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" s="91">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>決済機能（ゼウス連携）の追加</t>
-        </is>
-      </c>
-      <c r="C7" s="115" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D7" s="121" t="n">
-        <v>10</v>
+          <t>受講中のランダム顔照合を除外</t>
+        </is>
+      </c>
+      <c r="C7" s="119" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="D7" s="122" t="n">
+        <v>-7</v>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>株式会社ゼウスのAPI型決済を組み込み。申込から入金確認、受講開始までを自動化。今回の新規ご要望</t>
+          <t>受講の途中で予告なく撮影する機能を今回の範囲から外します。登録時の本人確認と受講開始時の照合は維持</t>
         </is>
       </c>
     </row>
@@ -1794,18 +1794,16 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>受講中のランダム顔照合を除外</t>
+          <t>全額一括前払いによる調整</t>
         </is>
       </c>
       <c r="C8" s="119" t="n">
         <v>-350000</v>
       </c>
-      <c r="D8" s="122" t="n">
-        <v>-7</v>
-      </c>
+      <c r="D8" s="120" t="n"/>
       <c r="E8" s="35" t="inlineStr">
         <is>
-          <t>受講の途中で予告なく撮影する機能を今回の範囲から外します。登録時の本人確認と受講開始時の照合は維持</t>
+          <t>ご発注時に全額をお支払いいただく条件に対する調整。分割回収に比べ資金負担と与信リスクが下がるため</t>
         </is>
       </c>
     </row>
@@ -1817,16 +1815,18 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>全額一括前払いによる調整</t>
+          <t>在席確認（カメラ前からの離席検知）の追加</t>
         </is>
       </c>
       <c r="C9" s="119" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="D9" s="120" t="n"/>
+        <v>900000</v>
+      </c>
+      <c r="D9" s="122" t="n">
+        <v>18</v>
+      </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>ご発注時に全額をお支払いいただく条件に対する調整。分割回収に比べ資金負担と与信リスクが下がるため</t>
+          <t>受講中はカメラ映像を端末内で判定し、離席したら再生を自動停止。離席時間は有効視聴時間から除外。今回の新規ご要望</t>
         </is>
       </c>
     </row>
@@ -1838,103 +1838,94 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>在席確認（カメラ前からの離席検知）の追加</t>
+          <t>受講中のランダム顔照合を再度組み入れ</t>
         </is>
       </c>
       <c r="C10" s="119" t="n">
-        <v>900000</v>
+        <v>200000</v>
       </c>
       <c r="D10" s="122" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>受講中はカメラ映像を端末内で判定し、離席したら再生を自動停止。離席時間は有効視聴時間から除外。今回の新規ご要望</t>
+          <t>②でいったん外したが、④のカメラ基盤を共用できるため7人日→4人日で実装可能。単独実装より350,000円→200,000円と安く戻せる</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" s="91">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>⑥</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>受講中のランダム顔照合を再度組み入れ</t>
-        </is>
-      </c>
-      <c r="C11" s="119" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D11" s="122" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="35" t="inlineStr">
-        <is>
-          <t>③でいったん外したが、⑤のカメラ基盤を共用できるため7人日→4人日で実装可能。単独実装より350,000円→200,000円と安く戻せる</t>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>今回のお見積り（税抜）</t>
+        </is>
+      </c>
+      <c r="C11" s="123">
+        <f>C5+SUM(C6:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="124">
+        <f>'03_見積明細'!D22</f>
+        <v/>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>教材6科目＋システム115人日</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>今回のお見積り（税抜）</t>
-        </is>
-      </c>
-      <c r="C12" s="123">
-        <f>C5+SUM(C6:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="124">
-        <f>'03_見積明細'!D23</f>
-        <v/>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>教材6科目＋システム125人日</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="91">
-      <c r="B13" s="102" t="inlineStr">
+      <c r="B12" s="102" t="inlineStr">
         <is>
           <t>（検算）見積明細の小計＋調整額</t>
         </is>
       </c>
-      <c r="C13" s="125">
-        <f>'03_見積明細'!F30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1" s="91"/>
+      <c r="C12" s="125">
+        <f>'03_見積明細'!F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="91"/>
+    <row r="14" ht="17" customHeight="1" s="91">
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>増減の内訳（金額の動き）</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="17" customHeight="1" s="91">
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>増減の内訳（金額の動き）</t>
-        </is>
-      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>減額の要因</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1" s="91">
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>減額の要因</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
+      <c r="B16" s="105" t="inlineStr">
+        <is>
+          <t>教材 4科目の削減</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>▲1,200,000</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1" s="91">
       <c r="B17" s="105" t="inlineStr">
         <is>
-          <t>教材 4科目の削減</t>
+          <t>受講中ランダム照合の除外（②）</t>
         </is>
       </c>
       <c r="C17" s="45" t="inlineStr">
         <is>
-          <t>▲1,200,000</t>
+          <t>▲350,000</t>
         </is>
       </c>
       <c r="D17" s="19" t="n"/>
@@ -1943,7 +1934,7 @@
     <row r="18" ht="17" customHeight="1" s="91">
       <c r="B18" s="105" t="inlineStr">
         <is>
-          <t>受講中ランダム照合の除外（③）</t>
+          <t>全額一括前払いによる調整</t>
         </is>
       </c>
       <c r="C18" s="45" t="inlineStr">
@@ -1955,237 +1946,232 @@
       <c r="E18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="105" t="inlineStr">
-        <is>
-          <t>全額一括前払いによる調整</t>
-        </is>
-      </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>▲350,000</t>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>▲1,900,000</t>
         </is>
       </c>
       <c r="D19" s="19" t="n"/>
       <c r="E19" s="19" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1" s="91">
-      <c r="B20" s="46" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>▲1,900,000</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1" s="91"/>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>増額の要因</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="91">
+      <c r="B21" s="105" t="inlineStr">
+        <is>
+          <t>在席確認の追加</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>＋900,000</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+    </row>
     <row r="22" ht="17" customHeight="1" s="91">
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>増額の要因</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
+      <c r="B22" s="105" t="inlineStr">
+        <is>
+          <t>受講中ランダム照合の再組入れ（⑤）</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>＋200,000</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="105" t="inlineStr">
         <is>
-          <t>決済機能（ゼウス連携）の追加</t>
+          <t>小計</t>
         </is>
       </c>
       <c r="C23" s="45" t="inlineStr">
         <is>
-          <t>＋500,000</t>
+          <t>＋1,100,000</t>
         </is>
       </c>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="91">
-      <c r="B24" s="105" t="inlineStr">
-        <is>
-          <t>在席確認の追加</t>
-        </is>
-      </c>
-      <c r="C24" s="45" t="inlineStr">
-        <is>
-          <t>＋900,000</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-    </row>
+    <row r="24" ht="19" customHeight="1" s="91"/>
     <row r="25">
-      <c r="B25" s="105" t="inlineStr">
-        <is>
-          <t>受講中ランダム照合の再組入れ（⑥）</t>
-        </is>
-      </c>
-      <c r="C25" s="45" t="inlineStr">
-        <is>
-          <t>＋200,000</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>差引</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>▲800,000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8,000,000 − 800,000 ＝ 7,200,000</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1" s="91">
-      <c r="B26" s="46" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C26" s="47" t="inlineStr">
-        <is>
-          <t>＋1,600,000</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1" s="91"/>
+      <c r="B26" s="53" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1" s="91">
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>■ このシートは社内資料です（先方には提出しません）</t>
+        </is>
+      </c>
+    </row>
     <row r="28" ht="17" customHeight="1" s="91">
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t>差引</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>▲300,000</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>8,000,000 − 300,000 ＝ 7,700,000</t>
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1" s="91">
-      <c r="B29" s="54" t="n"/>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>②で外したランダム顔照合が⑤で戻っています。単純な出し戻しに見せないため、</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1" s="91">
       <c r="B30" s="54" t="inlineStr">
         <is>
-          <t>■ このシートは社内資料です（先方には提出しません）</t>
+          <t>「在席確認を入れるので、そのカメラを使ってランダム照合も安く足せる」という順序で説明してください。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1" s="91">
-      <c r="B31" s="54" t="inlineStr">
-        <is>
-          <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
-        </is>
-      </c>
+      <c r="B31" s="54" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1" s="91">
       <c r="B32" s="54" t="inlineStr">
         <is>
-          <t>③で外したランダム顔照合が⑥で戻っています。単純な出し戻しに見せないため、</t>
+          <t>■ 決済機能について</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1" s="91">
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>「在席確認を入れるので、そのカメラを使ってランダム照合も安く足せる」という順序で説明してください。</t>
+          <t>決済は今回の範囲から外しました（将来的にご導入予定）。前回計上していた10人日・500,000円を落としています。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1" s="91">
-      <c r="B34" s="54" t="n"/>
+      <c r="B34" s="54" t="inlineStr">
+        <is>
+          <t>導入時は決済代行会社との接続方式が決まってからの見積となります。目安は10人日・500,000円です。</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1" s="91">
-      <c r="B35" s="54" t="inlineStr">
-        <is>
-          <t>■ この表の使い方（社内の根拠整理）</t>
-        </is>
-      </c>
+      <c r="B35" s="54" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1" s="91">
       <c r="B36" s="54" t="inlineStr">
         <is>
-          <t>値上げの根拠は次の2点です。どちらも先方の新しいご要望に対応するものです。</t>
+          <t>■ この表の使い方（社内の根拠整理）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1" s="91">
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　⑤ カメラ前からの離席を検知して再生を止める機能（18人日）</t>
+          <t>値上げの根拠は次の2点です。どちらも先方の新しいご要望に対応するものです。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1" s="91">
       <c r="B38" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　⑥ 受講中のランダム顔照合（4人日）</t>
+          <t xml:space="preserve">　④ カメラ前からの離席を検知して再生を止める機能（18人日）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1" s="91">
-      <c r="B39" s="54" t="n"/>
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 受講中のランダム顔照合（4人日）</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1" s="91">
-      <c r="B40" s="54" t="inlineStr">
-        <is>
-          <t>⑥は単独なら7人日・350,000円ですが、⑤のカメラ基盤を共用するため4人日・200,000円で済みます。</t>
-        </is>
-      </c>
+      <c r="B40" s="55" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1" s="91">
       <c r="B41" s="54" t="inlineStr">
         <is>
+          <t>⑤は単独なら7人日・350,000円ですが、④のカメラ基盤を共用するため4人日・200,000円で済みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1" s="91">
+      <c r="B42" s="54" t="inlineStr">
+        <is>
           <t>「離席検知をやるなら、顔照合は半額強で付けられます」が一番の売り文句です。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1" s="91">
-      <c r="B42" s="55" t="n"/>
-    </row>
     <row r="43" ht="17" customHeight="1" s="91">
-      <c r="B43" s="54" t="inlineStr">
-        <is>
-          <t>■ 月額費用の変更</t>
-        </is>
-      </c>
+      <c r="B43" s="54" t="n"/>
     </row>
     <row r="44" ht="17" customHeight="1" s="91">
       <c r="B44" s="54" t="inlineStr">
         <is>
-          <t>保守・運用サービス　60,000円 → 65,000円（＋5,000円）</t>
+          <t>■ 月額費用の変更</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1" s="91">
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　在席確認の離席ログ確認と、カメラが認識しない等の問い合わせ対応が増えるためです。</t>
+          <t>保守・運用サービス　60,000円 → 65,000円（＋5,000円）</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　ランダム照合の目視確認は在席確認の画面で一括して行えるため、＋20,000円ではなく＋5,000円で収まります。</t>
+          <t xml:space="preserve">　在席確認の離席ログ確認と、カメラが認識しない等の問い合わせ対応が増えるためです。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
+          <t xml:space="preserve">　ランダム照合の目視確認は在席確認の画面で一括して行えるため、＋20,000円ではなく＋5,000円で収まります。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="54" t="inlineStr">
+        <is>
+          <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　　　　　　合計 85,000円／月（サーバー費を除く・税抜）</t>
         </is>
@@ -2470,7 +2456,7 @@
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>各章の再生開始時に1:1照合を実施。受講中のランダム照合は今回の範囲外とします</t>
+          <t>各章の再生開始時に1:1照合を実施。受講中の照合は在席確認およびランダム顔照合で行います</t>
         </is>
       </c>
       <c r="D14" s="127" t="n">
@@ -2549,16 +2535,16 @@
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>決済機能（ゼウス連携）</t>
+          <t>受講者ポータル</t>
         </is>
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>株式会社ゼウスのデータ転送（API）型による決済組み込み。申込から入金確認、受講開始までの自動化。領収書の発行</t>
+          <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応</t>
         </is>
       </c>
       <c r="D17" s="127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="112">
         <f>$C$4</f>
@@ -2577,16 +2563,16 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>受講者ポータル</t>
+          <t>運営管理画面（基本機能）</t>
         </is>
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応</t>
+          <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理</t>
         </is>
       </c>
       <c r="D18" s="127" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E18" s="112">
         <f>$C$4</f>
@@ -2605,16 +2591,16 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>運営管理画面（基本機能）</t>
+          <t>結合テスト・E2E・受入支援</t>
         </is>
       </c>
       <c r="C19" s="35" t="inlineStr">
         <is>
-          <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理</t>
+          <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成</t>
         </is>
       </c>
       <c r="D19" s="127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="112">
         <f>$C$4</f>
@@ -2633,16 +2619,16 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>結合テスト・E2E・受入支援</t>
+          <t>在席確認（カメラ前からの離席検知）</t>
         </is>
       </c>
       <c r="C20" s="35" t="inlineStr">
         <is>
-          <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成</t>
+          <t>受講中はカメラ映像を端末内で判定し、受講者が画面前から離れたら再生を自動停止。離席の開始と終了を記録し、有効視聴時間から除外。画像はサーバーへ送信しません</t>
         </is>
       </c>
       <c r="D20" s="127" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E20" s="112">
         <f>$C$4</f>
@@ -2661,16 +2647,16 @@
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>在席確認（カメラ前からの離席検知）</t>
+          <t>受講中のランダム顔照合</t>
         </is>
       </c>
       <c r="C21" s="35" t="inlineStr">
         <is>
-          <t>受講中はカメラ映像を端末内で判定し、受講者が画面前から離れたら再生を自動停止。離席の開始と終了を記録し、有効視聴時間から除外。画像はサーバーへ送信しません</t>
+          <t>受講中に予告なく静止画を取得し、登録時の顔と1:1照合。在席確認のカメラ基盤を共用するため、単独で実装する場合（7人日）より少ない工数で実現できます</t>
         </is>
       </c>
       <c r="D21" s="127" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E21" s="112">
         <f>$C$4</f>
@@ -2681,227 +2667,202 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" s="91">
-      <c r="A22" s="59" t="inlineStr">
-        <is>
-          <t>システム</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>受講中のランダム顔照合</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>受講中に予告なく静止画を取得し、登録時の顔と1:1照合。在席確認のカメラ基盤を共用するため、単独で実装する場合（7人日）より少ない工数で実現できます</t>
-        </is>
-      </c>
-      <c r="D22" s="127" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="112">
-        <f>$C$4</f>
-        <v/>
-      </c>
-      <c r="F22" s="112">
-        <f>D22*E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1" s="91">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="51" t="inlineStr">
+    <row r="22" ht="17" customHeight="1" s="91">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="51" t="inlineStr">
         <is>
           <t>システム開発 小計</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="124">
-        <f>SUM(D8:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="117">
-        <f>SUM(F8:F22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1" s="91"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="124">
+        <f>SUM(D8:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="117">
+        <f>SUM(F8:F21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1" s="91"/>
+    <row r="24" ht="36" customHeight="1" s="91">
+      <c r="A24" s="108" t="inlineStr">
+        <is>
+          <t>2. eラーニング教材の制作</t>
+        </is>
+      </c>
+      <c r="B24" s="93" t="n"/>
+      <c r="C24" s="93" t="n"/>
+      <c r="D24" s="93" t="n"/>
+      <c r="E24" s="93" t="n"/>
+      <c r="F24" s="94" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="108" t="inlineStr">
-        <is>
-          <t>2. eラーニング教材の制作</t>
-        </is>
-      </c>
-      <c r="B25" s="93" t="n"/>
-      <c r="C25" s="93" t="n"/>
-      <c r="D25" s="93" t="n"/>
-      <c r="E25" s="93" t="n"/>
-      <c r="F25" s="94" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1" s="91">
-      <c r="A26" s="59" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>教材</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>特別教育 学科教材の制作</t>
         </is>
       </c>
-      <c r="C26" s="35">
+      <c r="C25" s="35">
         <f>"6科目・学科"&amp;TEXT('04_教材科目'!$D$17,"0.0")&amp;"時間分。構成台本の書き起こし、スライド、図解、ナレーション、バーチャル講師映像、章末問題・修了確認テストの作成"</f>
         <v/>
       </c>
-      <c r="D26" s="129">
+      <c r="D25" s="129">
         <f>'04_教材科目'!$A$17</f>
         <v/>
       </c>
-      <c r="E26" s="130">
+      <c r="E25" s="130">
         <f>'04_教材科目'!$D$4</f>
         <v/>
       </c>
-      <c r="F26" s="112">
+      <c r="F25" s="112">
         <f>'04_教材科目'!$F$17</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1" s="91"/>
+    <row r="26" ht="19" customHeight="1" s="91"/>
+    <row r="27" ht="17" customHeight="1" s="91">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t>小計（税抜）</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="124">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="117">
+        <f>F22+F25</f>
+        <v/>
+      </c>
+    </row>
     <row r="28" ht="17" customHeight="1" s="91">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="51" t="inlineStr">
-        <is>
-          <t>小計（税抜）</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="124">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="117">
-        <f>F23+F26</f>
-        <v/>
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>全額一括前払いによる調整</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>ご発注時に全額をお支払いいただく条件に対する調整額です</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="126" t="n">
+        <v>-350000</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1" s="91">
-      <c r="B29" s="64" t="inlineStr">
-        <is>
-          <t>全額一括前払いによる調整</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>ご発注時に全額をお支払いいただく条件に対する調整額です</t>
-        </is>
-      </c>
+      <c r="B29" s="65" t="inlineStr">
+        <is>
+          <t>差引 小計（税抜）</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="n"/>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="19" t="n"/>
-      <c r="F29" s="126" t="n">
-        <v>-350000</v>
+      <c r="F29" s="116">
+        <f>F27+F28</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="91">
       <c r="B30" s="65" t="inlineStr">
         <is>
-          <t>差引 小計（税抜）</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
+          <t>消費税</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>税率</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="n">
+        <v>0.1</v>
+      </c>
       <c r="E30" s="19" t="n"/>
       <c r="F30" s="116">
-        <f>F28+F29</f>
+        <f>ROUND(F29*D30,0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="65" t="inlineStr">
-        <is>
-          <t>消費税</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>税率</t>
-        </is>
-      </c>
-      <c r="D31" s="66" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="116">
-        <f>ROUND(F30*D31,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1" s="91">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>合計（税込）</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="123">
-        <f>F30+F31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1" s="91"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="123">
+        <f>F29+F30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="91"/>
+    <row r="33" ht="17" customHeight="1" s="91">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t>■ 今回の範囲から外したもの（第2次発注のご相談）</t>
+        </is>
+      </c>
+    </row>
     <row r="34" ht="17" customHeight="1" s="91">
-      <c r="A34" s="55" t="inlineStr">
-        <is>
-          <t>■ 今回の範囲から外したもの（第2次発注のご相談）</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>・決済機能（クレジットカード決済代行サービスとの連携）※将来のご導入を予定</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1" s="91">
       <c r="A35" s="54" t="inlineStr">
         <is>
-          <t>・受講者どうしの掲示板・質疑応答機能（当面はメールで対応）</t>
+          <t>・企業管理ポータル（従業員の一括申込、進捗確認、修了者一覧のCSV出力）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1" s="91">
       <c r="A36" s="54" t="inlineStr">
         <is>
-          <t>・企業管理ポータル（従業員の一括申込、進捗確認、修了者一覧のCSV出力）</t>
+          <t>・運営管理画面の拡張（監査レポート出力、組織管理、売上・入金管理）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1" s="91">
       <c r="A37" s="54" t="inlineStr">
         <is>
-          <t>・運営管理画面の拡張（監査レポート出力、組織管理、売上・入金管理）</t>
+          <t>・受講画面からの質疑応答機能（当面はメールで対応）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1" s="91">
       <c r="A38" s="54" t="inlineStr">
         <is>
-          <t>・受講画面からの質疑応答機能（当面はメールで対応）</t>
+          <t>・修了証の真正性検証ページ（QRコード）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1" s="91">
       <c r="A39" s="54" t="inlineStr">
         <is>
-          <t>・修了証の真正性検証ページ（QRコード）</t>
+          <t>・教材 4科目（低圧電気、第2種酸欠、高所作業車、玉掛け）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1" s="91">
-      <c r="A40" s="54" t="inlineStr">
-        <is>
-          <t>・教材 4科目（低圧電気、第2種酸欠、高所作業車、玉掛け）</t>
-        </is>
-      </c>
+      <c r="A40" s="54" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1" s="91">
       <c r="A41" s="54" t="n"/>
@@ -2923,7 +2884,7 @@
     <row r="44">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>・AWSの利用料（聖建様のご負担）、株式会社ゼウスとのご契約（初期費用無料・月額3,000円・決済手数料）</t>
+          <t>・サーバーの利用料（聖建様のご負担）</t>
         </is>
       </c>
     </row>
@@ -2937,8 +2898,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -3492,15 +3453,15 @@
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="65" t="inlineStr">
         <is>
-          <t>株式会社ゼウス（決済代行）</t>
+          <t>株式会社ゼウス（決済代行）※今回は範囲外</t>
         </is>
       </c>
       <c r="C11" s="126" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D11" s="95" t="inlineStr">
         <is>
-          <t>初期費用は無料。月額3,000円。クレジットカード決済手数料は最大3.5%（売上に応じて発生）。聖建様が直接ご契約いただきます</t>
+          <t>決済は今回の見積の範囲外です。将来ご導入の際は初期費用無料・月額3,000円・クレジットカード決済手数料 最大3.5%。聖建様が直接ご契約いただきます</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3514,7 @@
     <row r="17" ht="20" customHeight="1" s="91">
       <c r="B17" s="65" t="inlineStr">
         <is>
-          <t>弊社サービス ＋ AWS ＋ ゼウス月額</t>
+          <t>弊社サービス ＋ サーバー</t>
         </is>
       </c>
       <c r="C17" s="136">
@@ -3562,7 +3523,7 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>税抜。決済手数料は売上に応じて別途発生します</t>
+          <t>税抜。決済を導入された場合はゼウスの月額3,000円と決済手数料が加わります</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3788,7 @@
       </c>
       <c r="E19" s="19" t="n"/>
       <c r="F19" s="112">
-        <f>'03_見積明細'!F23</f>
+        <f>'03_見積明細'!F22</f>
         <v/>
       </c>
     </row>
@@ -3876,7 +3837,7 @@
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="19" t="n"/>
       <c r="F22" s="115">
-        <f>'03_見積明細'!F29</f>
+        <f>'03_見積明細'!F28</f>
         <v/>
       </c>
     </row>
@@ -3888,7 +3849,7 @@
       </c>
       <c r="C23" s="79" t="n"/>
       <c r="D23" s="80">
-        <f>'03_見積明細'!D31</f>
+        <f>'03_見積明細'!D30</f>
         <v/>
       </c>
       <c r="E23" s="19" t="n"/>
@@ -4032,7 +3993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C24"/>
+  <dimension ref="B1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="3" customWidth="1" style="91" min="1" max="1"/>
@@ -4133,145 +4094,157 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="23" customHeight="1" s="91">
+    <row r="11" ht="22" customHeight="1" s="91">
       <c r="B11" s="87" t="inlineStr">
         <is>
-          <t>月額サービス</t>
+          <t>決済機能</t>
         </is>
       </c>
       <c r="C11" s="95" t="inlineStr">
         <is>
-          <t>保守・運用サービス 65,000円／月、法令改正監視・通知サービス 20,000円／月。合計85,000円／月（税抜）。</t>
+          <t>オンラインでの受講料決済は今回の範囲に含みません。将来ご導入の際に別途お見積りいたします。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="91">
       <c r="B12" s="87" t="inlineStr">
         <is>
-          <t>サーバー利用料</t>
+          <t>月額サービス</t>
         </is>
       </c>
       <c r="C12" s="95" t="inlineStr">
         <is>
-          <t>貴社のご負担とします。月額20,000円程度（税抜）。貴社名義でのご契約をお願いします。</t>
+          <t>保守・運用サービス 65,000円／月、法令改正監視・通知サービス 20,000円／月。合計85,000円／月（税抜）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" s="91">
       <c r="B13" s="87" t="inlineStr">
         <is>
-          <t>教材の改訂・追加</t>
+          <t>サーバー利用料</t>
         </is>
       </c>
       <c r="C13" s="95" t="inlineStr">
         <is>
-          <t>1科目300,000円（都度発注）。</t>
+          <t>貴社のご負担とします。月額20,000円程度（税抜）。貴社名義でのご契約をお願いします。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" s="91">
       <c r="B14" s="87" t="inlineStr">
         <is>
+          <t>教材の改訂・追加</t>
+        </is>
+      </c>
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t>1科目300,000円（都度発注）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="87" t="inlineStr">
+        <is>
           <t>教材の監修</t>
         </is>
       </c>
-      <c r="C14" s="95" t="inlineStr">
+      <c r="C15" s="95" t="inlineStr">
         <is>
           <t>内容の監修は貴社の社内有資格者が担われる前提です。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="86" t="n"/>
-      <c r="C15" s="86" t="n"/>
-    </row>
     <row r="16" ht="20" customHeight="1" s="91">
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="86" t="n"/>
+      <c r="C16" s="86" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1" s="91">
+      <c r="B17" s="82" t="inlineStr">
         <is>
           <t>■ 3. 責任の分担</t>
         </is>
       </c>
-      <c r="C16" s="83" t="n"/>
-    </row>
-    <row r="17" ht="34" customHeight="1" s="91">
-      <c r="B17" s="87" t="inlineStr">
-        <is>
-          <t>弊社が保証すること</t>
-        </is>
-      </c>
-      <c r="C17" s="95" t="inlineStr">
-        <is>
-          <t>教材が安全衛生特別教育規程の定める科目・範囲・時間を満たすこと（監修者名を明示）。受講記録を証明可能な形で保存・出力できること。</t>
-        </is>
-      </c>
+      <c r="C17" s="83" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1" s="91">
       <c r="B18" s="87" t="inlineStr">
         <is>
-          <t>弊社が保証しないこと</t>
+          <t>弊社が保証すること</t>
         </is>
       </c>
       <c r="C18" s="95" t="inlineStr">
         <is>
-          <t>受講者の所属事業者が負う労働安全衛生法第59条第3項の実施義務が果たされたこと。労働災害が発生しないこと。行政機関が個別の事案において本教材を適法と判断すること。</t>
+          <t>教材が安全衛生特別教育規程の定める科目・範囲・時間を満たすこと（監修者名を明示）。受講記録を証明可能な形で保存・出力できること。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" s="91">
       <c r="B19" s="87" t="inlineStr">
         <is>
+          <t>弊社が保証しないこと</t>
+        </is>
+      </c>
+      <c r="C19" s="95" t="inlineStr">
+        <is>
+          <t>受講者の所属事業者が負う労働安全衛生法第59条第3項の実施義務が果たされたこと。労働災害が発生しないこと。行政機関が個別の事案において本教材を適法と判断すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="87" t="inlineStr">
+        <is>
           <t>法令改正への対応</t>
         </is>
       </c>
-      <c r="C19" s="95" t="inlineStr">
+      <c r="C20" s="95" t="inlineStr">
         <is>
           <t>弊社は官報・通達を監視し、該当しうる改正を自動でメール通知します。その改正が教材のどこに影響するかの判断は、貴社の監修者が行うものとします。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="86" t="n"/>
-      <c r="C20" s="86" t="n"/>
-    </row>
     <row r="21" ht="20" customHeight="1" s="91">
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="86" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="91">
+      <c r="B22" s="82" t="inlineStr">
         <is>
           <t>■ 4. 金額の前提</t>
         </is>
       </c>
-      <c r="C21" s="83" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1" s="91">
-      <c r="B22" s="87" t="inlineStr">
-        <is>
-          <t>教材制作単価</t>
-        </is>
-      </c>
-      <c r="C22" s="95" t="inlineStr">
-        <is>
-          <t>300,000円／科目。貴社ご指定の単価です。改訂・追加時も同額を適用します。</t>
-        </is>
-      </c>
+      <c r="C22" s="83" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1" s="91">
       <c r="B23" s="87" t="inlineStr">
         <is>
-          <t>支払条件</t>
+          <t>教材制作単価</t>
         </is>
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>2026年9月29日までに全額を一括でお支払いいただくことを前提とした金額です。</t>
+          <t>300,000円／科目。貴社ご指定の単価です。改訂・追加時も同額を適用します。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" s="91">
       <c r="B24" s="87" t="inlineStr">
         <is>
+          <t>支払条件</t>
+        </is>
+      </c>
+      <c r="C24" s="95" t="inlineStr">
+        <is>
+          <t>2026年9月29日までに全額を一括でお支払いいただくことを前提とした金額です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="87" t="inlineStr">
+        <is>
           <t>有効期限</t>
         </is>
       </c>
-      <c r="C24" s="95" t="inlineStr">
+      <c r="C25" s="95" t="inlineStr">
         <is>
           <t>発行日より30日間。</t>
         </is>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'01_見積書'!$A$1:$F$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_増減内訳'!$A$1:$E$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_見積明細'!$A$1:$F$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'04_教材科目'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05_月額・別途費用'!$A$1:$D$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$35</definedName>
@@ -1676,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" style="91" min="1" max="1"/>
@@ -1854,78 +1854,87 @@
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" s="91">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>在席確認にともなう既存機能の改修</t>
+        </is>
+      </c>
+      <c r="C11" s="119" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D11" s="122" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>視聴整合性＋3、受講者ポータル＋2、運営管理画面＋2、結合テスト＋3。離席時間の除外処理、カメラ許可の導線、離席ログの確認画面、端末別検証の追加分</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>今回のお見積り（税抜）</t>
         </is>
       </c>
-      <c r="C11" s="123">
-        <f>C5+SUM(C6:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="124">
+      <c r="C12" s="123">
+        <f>C5+SUM(C6:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="124">
         <f>'03_見積明細'!D22</f>
         <v/>
       </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>教材6科目＋システム115人日</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="102" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>教材6科目＋システム125人日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="91">
+      <c r="B13" s="102" t="inlineStr">
         <is>
           <t>（検算）見積明細の小計＋調整額</t>
         </is>
       </c>
-      <c r="C12" s="125">
+      <c r="C13" s="125">
         <f>'03_見積明細'!F29</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="91"/>
-    <row r="14" ht="17" customHeight="1" s="91">
-      <c r="B14" s="43" t="inlineStr">
+    <row r="14" ht="17" customHeight="1" s="91"/>
+    <row r="15" ht="17" customHeight="1" s="91">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>増減の内訳（金額の動き）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="17" customHeight="1" s="91">
-      <c r="B15" s="44" t="inlineStr">
+    <row r="16" ht="17" customHeight="1" s="91">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>減額の要因</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1" s="91">
-      <c r="B16" s="105" t="inlineStr">
-        <is>
-          <t>教材 4科目の削減</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>▲1,200,000</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1" s="91">
       <c r="B17" s="105" t="inlineStr">
         <is>
-          <t>受講中ランダム照合の除外（②）</t>
+          <t>教材 4科目の削減</t>
         </is>
       </c>
       <c r="C17" s="45" t="inlineStr">
         <is>
-          <t>▲350,000</t>
+          <t>▲1,200,000</t>
         </is>
       </c>
       <c r="D17" s="19" t="n"/>
@@ -1934,7 +1943,7 @@
     <row r="18" ht="17" customHeight="1" s="91">
       <c r="B18" s="105" t="inlineStr">
         <is>
-          <t>全額一括前払いによる調整</t>
+          <t>受講中ランダム照合の除外（②）</t>
         </is>
       </c>
       <c r="C18" s="45" t="inlineStr">
@@ -1946,52 +1955,52 @@
       <c r="E18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>▲1,900,000</t>
+      <c r="B19" s="105" t="inlineStr">
+        <is>
+          <t>全額一括前払いによる調整</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>▲350,000</t>
         </is>
       </c>
       <c r="D19" s="19" t="n"/>
       <c r="E19" s="19" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1" s="91">
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>▲1,900,000</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="91">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>増額の要因</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1" s="91">
-      <c r="B21" s="105" t="inlineStr">
-        <is>
-          <t>在席確認の追加</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="inlineStr">
-        <is>
-          <t>＋900,000</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1" s="91">
       <c r="B22" s="105" t="inlineStr">
         <is>
-          <t>受講中ランダム照合の再組入れ（⑤）</t>
+          <t>在席確認の追加</t>
         </is>
       </c>
       <c r="C22" s="45" t="inlineStr">
         <is>
-          <t>＋200,000</t>
+          <t>＋900,000</t>
         </is>
       </c>
       <c r="D22" s="19" t="n"/>
@@ -2000,178 +2009,227 @@
     <row r="23">
       <c r="B23" s="105" t="inlineStr">
         <is>
-          <t>小計</t>
+          <t>受講中ランダム照合の再組入れ（⑤）</t>
         </is>
       </c>
       <c r="C23" s="45" t="inlineStr">
         <is>
-          <t>＋1,100,000</t>
+          <t>＋200,000</t>
         </is>
       </c>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="91"/>
+    <row r="24" ht="19" customHeight="1" s="91">
+      <c r="B24" s="105" t="inlineStr">
+        <is>
+          <t>在席確認にともなう既存機能の改修（⑥）</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>＋500,000</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+    </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="105" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>＋1,600,000</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1" s="91"/>
+    <row r="27" ht="17" customHeight="1" s="91">
+      <c r="B27" t="inlineStr">
         <is>
           <t>差引</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>▲800,000</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>8,000,000 − 800,000 ＝ 7,200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1" s="91">
-      <c r="B26" s="53" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1" s="91">
-      <c r="B27" s="54" t="inlineStr">
-        <is>
-          <t>■ このシートは社内資料です（先方には提出しません）</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>▲300,000</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8,000,000 − 300,000 ＝ 7,700,000</t>
         </is>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1" s="91">
-      <c r="B28" s="54" t="inlineStr">
-        <is>
-          <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
-        </is>
-      </c>
+      <c r="B28" s="53" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1" s="91">
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>②で外したランダム顔照合が⑤で戻っています。単純な出し戻しに見せないため、</t>
+          <t>■ このシートは社内資料です（先方には提出しません）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1" s="91">
       <c r="B30" s="54" t="inlineStr">
         <is>
-          <t>「在席確認を入れるので、そのカメラを使ってランダム照合も安く足せる」という順序で説明してください。</t>
+          <t>提出するのは 01_見積書 ／ 06_注文書 ／ 07_前提条件 の3点のみです。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1" s="91">
-      <c r="B31" s="54" t="n"/>
+      <c r="B31" s="54" t="inlineStr">
+        <is>
+          <t>②で外したランダム顔照合が⑤で戻っています。単純な出し戻しに見せないため、</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1" s="91">
       <c r="B32" s="54" t="inlineStr">
         <is>
-          <t>■ 決済機能について</t>
+          <t>「在席確認を入れるので、そのカメラを使ってランダム照合も安く足せる」という順序で説明してください。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1" s="91">
-      <c r="B33" s="54" t="inlineStr">
-        <is>
-          <t>決済は今回の範囲から外しました（将来的にご導入予定）。前回計上していた10人日・500,000円を落としています。</t>
-        </is>
-      </c>
+      <c r="B33" s="54" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1" s="91">
       <c r="B34" s="54" t="inlineStr">
         <is>
-          <t>導入時は決済代行会社との接続方式が決まってからの見積となります。目安は10人日・500,000円です。</t>
+          <t>■ 決済機能について</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1" s="91">
-      <c r="B35" s="54" t="n"/>
+      <c r="B35" s="54" t="inlineStr">
+        <is>
+          <t>決済は今回の範囲から外しました（将来的にご導入予定）。前回計上していた10人日・500,000円を落としています。</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1" s="91">
       <c r="B36" s="54" t="inlineStr">
         <is>
-          <t>■ この表の使い方（社内の根拠整理）</t>
+          <t>導入時は決済代行会社との接続方式が決まってからの見積となります。目安は10人日・500,000円です。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1" s="91">
-      <c r="B37" s="54" t="inlineStr">
-        <is>
-          <t>値上げの根拠は次の2点です。どちらも先方の新しいご要望に対応するものです。</t>
-        </is>
-      </c>
+      <c r="B37" s="54" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1" s="91">
       <c r="B38" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　④ カメラ前からの離席を検知して再生を止める機能（18人日）</t>
+          <t>■ 総額7,700,000円を維持している理由（⑥）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1" s="91">
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　⑤ 受講中のランダム顔照合（4人日）</t>
+          <t>決済を外した500,000円は、在席確認が既存機能へ波及する分（10人日）に振り替えています。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1" s="91">
-      <c r="B40" s="55" t="n"/>
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　視聴整合性 15→18人日　… 離席していた時間を有効視聴時間から除外する処理</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1" s="91">
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>⑤は単独なら7人日・350,000円ですが、④のカメラ基盤を共用するため4人日・200,000円で済みます。</t>
+          <t xml:space="preserve">　受講者ポータル 9→11人日　… カメラ許可の取得導線と、離席中の画面表示</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1" s="91">
       <c r="B42" s="54" t="inlineStr">
         <is>
-          <t>「離席検知をやるなら、顔照合は半額強で付けられます」が一番の売り文句です。</t>
+          <t xml:space="preserve">　運営管理画面 4→6人日　… 離席ログと顔照合結果の確認画面</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1" s="91">
-      <c r="B43" s="54" t="n"/>
+      <c r="B43" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　結合テスト 9人日（＋3）　… カメラを使う工程の端末別・ブラウザ別検証</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1" s="91">
-      <c r="B44" s="54" t="inlineStr">
-        <is>
-          <t>■ 月額費用の変更</t>
-        </is>
-      </c>
+      <c r="B44" s="54" t="n"/>
     </row>
     <row r="45" ht="17" customHeight="1" s="91">
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>保守・運用サービス　60,000円 → 65,000円（＋5,000円）</t>
+          <t>当初18人日で見ていた在席確認は、この機能単体の工数です。実際にはカメラを常時動かすことで</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　在席確認の離席ログ確認と、カメラが認識しない等の問い合わせ対応が増えるためです。</t>
+          <t>上の4項目に手が入ります。項目を増やさず既存項目の人日を上げているのはこのためです。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　ランダム照合の目視確認は在席確認の画面で一括して行えるため、＋20,000円ではなく＋5,000円で収まります。</t>
+          <t>先方から内訳を求められた場合も、この4項目の増加として説明できます。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="54" t="inlineStr">
-        <is>
-          <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
-        </is>
-      </c>
+      <c r="B48" s="54" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="54" t="inlineStr">
+        <is>
+          <t>■ 月額費用の変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="54" t="inlineStr">
+        <is>
+          <t>保守・運用サービス　60,000円 → 65,000円（＋5,000円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　在席確認の離席ログ確認と、カメラが認識しない等の問い合わせ対応が増えるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ランダム照合の目視確認は在席確認の画面で一括して行えるため、＋20,000円ではなく＋5,000円で収まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="54" t="inlineStr">
+        <is>
+          <t>法令改正監視・通知サービス　20,000円（変更なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　　　　　　合計 85,000円／月（サーバー費を除く・税抜）</t>
         </is>
@@ -2372,11 +2430,11 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>heartbeatの受信と検証、未視聴位置へのシーク制限、倍速検知、可視状態の判定、サーバー側での検証済み秒数の集計、異常検知</t>
+          <t>heartbeatの受信と検証、未視聴位置へのシーク制限、倍速検知、可視状態の判定、サーバー側での検証済み秒数の集計、異常検知。離席していた時間の除外処理を含む</t>
         </is>
       </c>
       <c r="D11" s="127" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11" s="112">
         <f>$C$4</f>
@@ -2540,11 +2598,11 @@
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応</t>
+          <t>申込、マイページ、受講画面、進捗表示、スマートフォン対応。カメラ許可の取得導線と離席時の画面表示を含む</t>
         </is>
       </c>
       <c r="D17" s="127" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="112">
         <f>$C$4</f>
@@ -2568,11 +2626,11 @@
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理</t>
+          <t>本人確認の承認キュー、受講状況の一覧、受講ログの照会、修了証の発行管理、離席ログと顔照合結果の確認</t>
         </is>
       </c>
       <c r="D18" s="127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="112">
         <f>$C$4</f>
@@ -2596,11 +2654,11 @@
       </c>
       <c r="C19" s="35" t="inlineStr">
         <is>
-          <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成</t>
+          <t>必須E2Eシナリオの実施、受入条件の確認、リリース判定資料の作成。カメラを使う工程の端末別検証を含む</t>
         </is>
       </c>
       <c r="D19" s="127" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="112">
         <f>$C$4</f>
@@ -2667,7 +2725,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1" s="91">
+    <row r="22" ht="30" customHeight="1" s="91">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="51" t="inlineStr">
         <is>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'04_教材科目'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05_月額・別途費用'!$A$1:$D$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'06_注文書'!$A$1:$F$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_前提条件'!$A$1:$C$27</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -936,7 +936,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6549120" y="1464479"/>
+    <pos x="6351480" y="1288800"/>
     <ext cx="878040" cy="878040"/>
     <pic>
       <nvPicPr>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>2026年9月29日までに全額を一括でお支払いください。</t>
+          <t>2026年9月28日までに全額を一括でお支払いください。</t>
         </is>
       </c>
       <c r="D23" s="93" t="n"/>
@@ -1627,7 +1627,7 @@
     <row r="37" ht="17" customHeight="1" s="91">
       <c r="B37" s="104" t="inlineStr">
         <is>
-          <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
+          <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約をお願いします</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="D9" s="95" t="inlineStr">
         <is>
-          <t>EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch。聖建様名義でのご契約を推奨します</t>
+          <t>EC2、RDS PostgreSQL（Multi-AZ・自動バックアップ・PITR）、ElastiCache、ALB、S3、CloudFront、CloudWatch。聖建様名義でのご契約をお願いします</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="C29" s="95" t="inlineStr">
         <is>
-          <t>2026年9月29日までに、上記ご注文金額の全額を一括でお支払いいたします。</t>
+          <t>2026年9月28日までに、上記ご注文金額の全額を一括でお支払いいたします。</t>
         </is>
       </c>
       <c r="D29" s="93" t="n"/>
@@ -4007,7 +4007,7 @@
     <row r="33" ht="17" customHeight="1" s="91">
       <c r="B33" s="104" t="inlineStr">
         <is>
-          <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約を推奨します</t>
+          <t>・サーバー利用料　月額 20,000円程度（受講者数により変動）。貴社名義でのご契約をお願いします</t>
         </is>
       </c>
     </row>
@@ -4087,70 +4087,69 @@
       </c>
       <c r="C4" s="95" t="inlineStr">
         <is>
-          <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、在席確認（カメラ前からの離席検知）、受講中のランダム顔照合、確認問題、修了判定、修了証の発行、受講者ポータル、運営管理画面の基本機能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" s="91">
+          <t>配信基盤、視聴整合性、登録時の本人確認、受講開始時の顔照合、受講中のランダム顔照合、確認問題、修了判定、修了証の発行、受講者ポータル、運営管理画面の基本機能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1" s="91">
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>教材制作</t>
+          <t>在席確認</t>
         </is>
       </c>
       <c r="C5" s="95" t="inlineStr">
         <is>
-          <t>特別教育 学科教材 6科目。構成台本、スライド、図解、ナレーション、章末問題・修了確認。</t>
+          <t>受講中にカメラ前からの離席を検知し、再生を自動停止します。離席していた時間は有効視聴時間から除外し、離席の開始と終了を記録します。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" s="91">
       <c r="B6" s="87" t="inlineStr">
         <is>
-          <t>修了証</t>
+          <t>教材制作</t>
         </is>
       </c>
       <c r="C6" s="95" t="inlineStr">
         <is>
-          <t>修了証PDFの自動発行、再発行、受講者によるダウンロード。記載項目は受講者氏名、科目、法定学科時間、有効視聴時間、テスト得点、講師名、発行者、証明書番号。</t>
+          <t>特別教育 学科教材 6科目。構成台本、スライド、図解、ナレーション、章末問題・修了確認。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" s="91">
       <c r="B7" s="87" t="inlineStr">
         <is>
+          <t>修了証</t>
+        </is>
+      </c>
+      <c r="C7" s="95" t="inlineStr">
+        <is>
+          <t>修了証PDFの自動発行、再発行、受講者によるダウンロード。記載項目は受講者氏名、科目、法定学科時間、有効視聴時間、テスト得点、講師名、発行者、証明書番号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="87" t="inlineStr">
+        <is>
           <t>サーバー環境の構築</t>
         </is>
       </c>
-      <c r="C7" s="95" t="inlineStr">
+      <c r="C8" s="95" t="inlineStr">
         <is>
           <t>本番運用に耐える構成で構築します。データベースは冗長化し、日次のバックアップを取得します。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="86" t="n"/>
-      <c r="C8" s="86" t="n"/>
-    </row>
     <row r="9" ht="20" customHeight="1" s="91">
-      <c r="B9" s="84" t="inlineStr">
-        <is>
-          <t>■ 2. 在席確認について／本見積に含まれないもの（別途）</t>
-        </is>
-      </c>
-      <c r="C9" s="83" t="n"/>
+      <c r="B9" s="86" t="n"/>
+      <c r="C9" s="86" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1" s="91">
-      <c r="B10" s="88" t="inlineStr">
-        <is>
-          <t>在席確認の方式</t>
-        </is>
-      </c>
-      <c r="C10" s="89" t="inlineStr">
-        <is>
-          <t>カメラ映像の判定は受講者の端末内で行い、映像・画像をサーバーへ送信しません。
-離席を検知すると再生を自動停止し、離席していた時間は有効視聴時間から除外します。</t>
-        </is>
-      </c>
+      <c r="B10" s="84" t="inlineStr">
+        <is>
+          <t>■ 2. 本見積に含まれないもの（別途）</t>
+        </is>
+      </c>
+      <c r="C10" s="83" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1" s="91">
       <c r="B11" s="87" t="inlineStr">
@@ -4292,7 +4291,7 @@
       </c>
       <c r="C24" s="95" t="inlineStr">
         <is>
-          <t>2026年9月29日までに全額を一括でお支払いいただくことを前提とした金額です。</t>
+          <t>2026年9月28日までに全額を一括でお支払いいただくことを前提とした金額です。</t>
         </is>
       </c>
     </row>
